--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6175D4-E88C-4EF7-8DCB-C7E428C43A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F471E4-A7BE-47A2-9699-FDFA73DFA3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45510" yWindow="3030" windowWidth="24600" windowHeight="15750" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="38400" yWindow="0" windowWidth="38400" windowHeight="21150" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="340">
   <si>
     <t>BGC10</t>
   </si>
@@ -1044,7 +1044,7 @@
     <t>RS10</t>
   </si>
   <si>
-    <t>TikTok</t>
+    <t>BL25</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K700"/>
+  <dimension ref="A1:K695"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -5866,14 +5866,14 @@
       <c r="A309" t="s">
         <v>175</v>
       </c>
-      <c r="B309" t="s">
-        <v>244</v>
+      <c r="B309" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="C309" s="6">
-        <v>42.9</v>
+        <v>16.5</v>
       </c>
       <c r="D309" t="s">
-        <v>268</v>
+        <v>136</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -5881,7 +5881,7 @@
         <v>175</v>
       </c>
       <c r="B310" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C310" s="6">
         <v>42.9</v>
@@ -5894,14 +5894,14 @@
       <c r="A311" t="s">
         <v>175</v>
       </c>
-      <c r="B311" s="3" t="s">
-        <v>26</v>
+      <c r="B311" t="s">
+        <v>247</v>
       </c>
       <c r="C311" s="6">
-        <v>98.5</v>
+        <v>42.9</v>
       </c>
       <c r="D311" t="s">
-        <v>142</v>
+        <v>268</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -5909,10 +5909,10 @@
         <v>175</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C312" s="6">
-        <v>105</v>
+        <v>98.5</v>
       </c>
       <c r="D312" t="s">
         <v>142</v>
@@ -5923,10 +5923,10 @@
         <v>175</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C313" s="6">
-        <v>98.5</v>
+        <v>105</v>
       </c>
       <c r="D313" t="s">
         <v>142</v>
@@ -5937,10 +5937,10 @@
         <v>175</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C314" s="6">
-        <v>105</v>
+        <v>98.5</v>
       </c>
       <c r="D314" t="s">
         <v>142</v>
@@ -5951,10 +5951,10 @@
         <v>175</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C315" s="6">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="D315" t="s">
         <v>142</v>
@@ -5965,10 +5965,10 @@
         <v>175</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C316" s="6">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="D316" t="s">
         <v>142</v>
@@ -5979,10 +5979,10 @@
         <v>175</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C317" s="6">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="D317" t="s">
         <v>142</v>
@@ -5993,10 +5993,10 @@
         <v>175</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C318" s="6">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="D318" t="s">
         <v>142</v>
@@ -6007,10 +6007,10 @@
         <v>175</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C319" s="6">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D319" t="s">
         <v>142</v>
@@ -6021,10 +6021,10 @@
         <v>175</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C320" s="6">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="D320" t="s">
         <v>142</v>
@@ -6035,10 +6035,10 @@
         <v>175</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="C321" s="6">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D321" t="s">
         <v>142</v>
@@ -6049,10 +6049,10 @@
         <v>175</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="C322" s="6">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="D322" t="s">
         <v>142</v>
@@ -6063,13 +6063,13 @@
         <v>175</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C323" s="6">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D323" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -6077,13 +6077,13 @@
         <v>175</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C324" s="6">
-        <v>475</v>
+        <v>18</v>
       </c>
       <c r="D324" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -6091,10 +6091,13 @@
         <v>175</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>338</v>
+        <v>47</v>
+      </c>
+      <c r="C325" s="6">
+        <v>475</v>
       </c>
       <c r="D325" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6102,10 +6105,7 @@
         <v>175</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C326" s="6">
-        <v>15.58</v>
+        <v>338</v>
       </c>
       <c r="D326" t="s">
         <v>144</v>
@@ -6116,13 +6116,13 @@
         <v>175</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>55</v>
+        <v>337</v>
       </c>
       <c r="C327" s="6">
-        <v>12</v>
+        <v>15.58</v>
       </c>
       <c r="D327" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -6130,10 +6130,10 @@
         <v>175</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C328" s="6">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D328" t="s">
         <v>145</v>
@@ -6144,10 +6144,10 @@
         <v>175</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C329" s="6">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D329" t="s">
         <v>145</v>
@@ -6158,10 +6158,10 @@
         <v>175</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C330" s="6">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D330" t="s">
         <v>145</v>
@@ -6171,11 +6171,11 @@
       <c r="A331" t="s">
         <v>175</v>
       </c>
-      <c r="B331" t="s">
-        <v>255</v>
+      <c r="B331" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C331" s="6">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="D331" t="s">
         <v>145</v>
@@ -6186,10 +6186,10 @@
         <v>175</v>
       </c>
       <c r="B332" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C332" s="6">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D332" t="s">
         <v>145</v>
@@ -6200,10 +6200,10 @@
         <v>175</v>
       </c>
       <c r="B333" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C333" s="6">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="D333" t="s">
         <v>145</v>
@@ -6213,14 +6213,14 @@
       <c r="A334" t="s">
         <v>175</v>
       </c>
-      <c r="B334" s="3" t="s">
-        <v>59</v>
+      <c r="B334" t="s">
+        <v>257</v>
       </c>
       <c r="C334" s="6">
-        <v>33.5</v>
+        <v>102</v>
       </c>
       <c r="D334" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -6228,10 +6228,10 @@
         <v>175</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C335" s="6">
-        <v>15.1</v>
+        <v>33.5</v>
       </c>
       <c r="D335" t="s">
         <v>146</v>
@@ -6241,11 +6241,11 @@
       <c r="A336" t="s">
         <v>175</v>
       </c>
-      <c r="B336" t="s">
-        <v>61</v>
+      <c r="B336" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C336" s="6">
-        <v>38.28</v>
+        <v>15.1</v>
       </c>
       <c r="D336" t="s">
         <v>146</v>
@@ -6255,11 +6255,11 @@
       <c r="A337" t="s">
         <v>175</v>
       </c>
-      <c r="B337" s="3" t="s">
-        <v>62</v>
+      <c r="B337" t="s">
+        <v>61</v>
       </c>
       <c r="C337" s="6">
-        <v>22.36</v>
+        <v>38.28</v>
       </c>
       <c r="D337" t="s">
         <v>146</v>
@@ -6270,10 +6270,10 @@
         <v>175</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="C338" s="6">
-        <v>23.68</v>
+        <v>22.36</v>
       </c>
       <c r="D338" t="s">
         <v>146</v>
@@ -6284,10 +6284,10 @@
         <v>175</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>65</v>
+        <v>176</v>
       </c>
       <c r="C339" s="6">
-        <v>10</v>
+        <v>23.68</v>
       </c>
       <c r="D339" t="s">
         <v>146</v>
@@ -6298,13 +6298,13 @@
         <v>175</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="C340" s="6">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="D340" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -6312,10 +6312,10 @@
         <v>175</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C341" s="6">
-        <v>225</v>
+        <v>87</v>
       </c>
       <c r="D341" t="s">
         <v>147</v>
@@ -6326,10 +6326,10 @@
         <v>175</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C342" s="6">
-        <v>421.08</v>
+        <v>225</v>
       </c>
       <c r="D342" t="s">
         <v>147</v>
@@ -6340,10 +6340,13 @@
         <v>175</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>92</v>
+        <v>179</v>
+      </c>
+      <c r="C343" s="6">
+        <v>421.08</v>
       </c>
       <c r="D343" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -6351,13 +6354,10 @@
         <v>175</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C344" s="6">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="D344" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -6365,10 +6365,13 @@
         <v>175</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="C345" s="6">
+        <v>60</v>
       </c>
       <c r="D345" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -6376,7 +6379,7 @@
         <v>175</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D346" t="s">
         <v>148</v>
@@ -6386,11 +6389,8 @@
       <c r="A347" t="s">
         <v>175</v>
       </c>
-      <c r="B347" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C347" s="6">
-        <v>15.25</v>
+      <c r="B347" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D347" t="s">
         <v>148</v>
@@ -6401,10 +6401,10 @@
         <v>175</v>
       </c>
       <c r="B348" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C348" s="6">
-        <v>18.899999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="D348" t="s">
         <v>148</v>
@@ -6414,11 +6414,11 @@
       <c r="A349" t="s">
         <v>175</v>
       </c>
-      <c r="B349" s="3" t="s">
-        <v>96</v>
+      <c r="B349" s="3">
+        <v>4442</v>
       </c>
       <c r="C349" s="6">
-        <v>193</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D349" t="s">
         <v>148</v>
@@ -6429,7 +6429,10 @@
         <v>175</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="C350" s="6">
+        <v>193</v>
       </c>
       <c r="D350" t="s">
         <v>148</v>
@@ -6439,11 +6442,8 @@
       <c r="A351" t="s">
         <v>175</v>
       </c>
-      <c r="B351" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C351" s="6">
-        <v>20.8</v>
+      <c r="B351" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D351" t="s">
         <v>148</v>
@@ -6453,8 +6453,11 @@
       <c r="A352" t="s">
         <v>175</v>
       </c>
-      <c r="B352" s="3" t="s">
-        <v>98</v>
+      <c r="B352" s="3">
+        <v>4642</v>
+      </c>
+      <c r="C352" s="6">
+        <v>20.8</v>
       </c>
       <c r="D352" t="s">
         <v>148</v>
@@ -6464,11 +6467,8 @@
       <c r="A353" t="s">
         <v>175</v>
       </c>
-      <c r="B353" s="3">
-        <v>4660</v>
-      </c>
-      <c r="C353" s="6">
-        <v>24.7</v>
+      <c r="B353" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="D353" t="s">
         <v>148</v>
@@ -6479,10 +6479,10 @@
         <v>175</v>
       </c>
       <c r="B354" s="3">
-        <v>6642</v>
+        <v>4660</v>
       </c>
       <c r="C354" s="6">
-        <v>26.8</v>
+        <v>24.7</v>
       </c>
       <c r="D354" t="s">
         <v>148</v>
@@ -6492,11 +6492,11 @@
       <c r="A355" t="s">
         <v>175</v>
       </c>
-      <c r="B355" s="3" t="s">
-        <v>99</v>
+      <c r="B355" s="3">
+        <v>6642</v>
       </c>
       <c r="C355" s="6">
-        <v>115</v>
+        <v>26.8</v>
       </c>
       <c r="D355" t="s">
         <v>148</v>
@@ -6506,11 +6506,11 @@
       <c r="A356" t="s">
         <v>175</v>
       </c>
-      <c r="B356" s="3">
-        <v>6660</v>
+      <c r="B356" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C356" s="6">
-        <v>27.05</v>
+        <v>115</v>
       </c>
       <c r="D356" t="s">
         <v>148</v>
@@ -6520,11 +6520,11 @@
       <c r="A357" t="s">
         <v>175</v>
       </c>
-      <c r="B357" s="3" t="s">
-        <v>100</v>
+      <c r="B357" s="3">
+        <v>6660</v>
       </c>
       <c r="C357" s="6">
-        <v>160</v>
+        <v>27.05</v>
       </c>
       <c r="D357" t="s">
         <v>148</v>
@@ -6535,13 +6535,13 @@
         <v>175</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="C358" s="6">
-        <v>30.5</v>
+        <v>160</v>
       </c>
       <c r="D358" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -6549,13 +6549,13 @@
         <v>175</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>271</v>
+        <v>180</v>
       </c>
       <c r="C359" s="6">
-        <v>12.75</v>
+        <v>30.5</v>
       </c>
       <c r="D359" t="s">
-        <v>270</v>
+        <v>149</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -6563,7 +6563,7 @@
         <v>175</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C360" s="6">
         <v>12.75</v>
@@ -6577,10 +6577,10 @@
         <v>175</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C361" s="6">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="D361" t="s">
         <v>270</v>
@@ -6591,10 +6591,10 @@
         <v>175</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C362" s="6">
-        <v>10.3</v>
+        <v>13.25</v>
       </c>
       <c r="D362" t="s">
         <v>270</v>
@@ -6605,10 +6605,10 @@
         <v>175</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C363" s="6">
-        <v>11.85</v>
+        <v>10.3</v>
       </c>
       <c r="D363" t="s">
         <v>270</v>
@@ -6619,10 +6619,10 @@
         <v>175</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C364" s="6">
-        <v>12.75</v>
+        <v>11.85</v>
       </c>
       <c r="D364" t="s">
         <v>270</v>
@@ -6633,10 +6633,10 @@
         <v>175</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C365" s="6">
-        <v>10.3</v>
+        <v>12.75</v>
       </c>
       <c r="D365" t="s">
         <v>270</v>
@@ -6647,10 +6647,10 @@
         <v>175</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C366" s="6">
-        <v>13.25</v>
+        <v>10.3</v>
       </c>
       <c r="D366" t="s">
         <v>270</v>
@@ -6661,10 +6661,10 @@
         <v>175</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C367" s="6">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="D367" t="s">
         <v>270</v>
@@ -6675,13 +6675,13 @@
         <v>175</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>107</v>
+        <v>272</v>
       </c>
       <c r="C368" s="6">
-        <v>21.5</v>
+        <v>12.75</v>
       </c>
       <c r="D368" t="s">
-        <v>152</v>
+        <v>270</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -6689,10 +6689,10 @@
         <v>175</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C369" s="6">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="D369" t="s">
         <v>152</v>
@@ -6703,10 +6703,10 @@
         <v>175</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C370" s="6">
-        <v>10.5</v>
+        <v>22.5</v>
       </c>
       <c r="D370" t="s">
         <v>152</v>
@@ -6717,7 +6717,7 @@
         <v>175</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C371" s="6">
         <v>10.5</v>
@@ -6731,7 +6731,7 @@
         <v>175</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C372" s="6">
         <v>10.5</v>
@@ -6745,10 +6745,13 @@
         <v>175</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>277</v>
+        <v>117</v>
+      </c>
+      <c r="C373" s="6">
+        <v>10.5</v>
       </c>
       <c r="D373" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -6756,10 +6759,7 @@
         <v>175</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C374" s="6">
-        <v>23</v>
+        <v>277</v>
       </c>
       <c r="D374" t="s">
         <v>173</v>
@@ -6770,7 +6770,10 @@
         <v>175</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
+      </c>
+      <c r="C375" s="6">
+        <v>23</v>
       </c>
       <c r="D375" t="s">
         <v>173</v>
@@ -6781,13 +6784,10 @@
         <v>175</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C376" s="6">
-        <v>23.15</v>
+        <v>279</v>
       </c>
       <c r="D376" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -6795,10 +6795,10 @@
         <v>175</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C377" s="6">
-        <v>42.65</v>
+        <v>23.15</v>
       </c>
       <c r="D377" t="s">
         <v>153</v>
@@ -6809,10 +6809,10 @@
         <v>175</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C378" s="6">
-        <v>82</v>
+        <v>42.65</v>
       </c>
       <c r="D378" t="s">
         <v>153</v>
@@ -6823,10 +6823,10 @@
         <v>175</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C379" s="6">
-        <v>33.5</v>
+        <v>82</v>
       </c>
       <c r="D379" t="s">
         <v>153</v>
@@ -6837,10 +6837,10 @@
         <v>175</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C380" s="6">
-        <v>60.9</v>
+        <v>33.5</v>
       </c>
       <c r="D380" t="s">
         <v>153</v>
@@ -6851,10 +6851,10 @@
         <v>175</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C381" s="6">
-        <v>118</v>
+        <v>60.9</v>
       </c>
       <c r="D381" t="s">
         <v>153</v>
@@ -6865,10 +6865,10 @@
         <v>175</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C382" s="6">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D382" t="s">
         <v>153</v>
@@ -6879,7 +6879,7 @@
         <v>175</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C383" s="6">
         <v>16</v>
@@ -6893,10 +6893,10 @@
         <v>175</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C384" s="6">
-        <v>21.32</v>
+        <v>16</v>
       </c>
       <c r="D384" t="s">
         <v>153</v>
@@ -6907,13 +6907,13 @@
         <v>175</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C385" s="6">
-        <v>26</v>
+        <v>21.32</v>
       </c>
       <c r="D385" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -6921,7 +6921,10 @@
         <v>175</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
+      </c>
+      <c r="C386" s="6">
+        <v>26</v>
       </c>
       <c r="D386" t="s">
         <v>154</v>
@@ -6932,10 +6935,7 @@
         <v>175</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C387" s="6">
-        <v>13.42</v>
+        <v>128</v>
       </c>
       <c r="D387" t="s">
         <v>154</v>
@@ -6946,7 +6946,10 @@
         <v>175</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="C388" s="6">
+        <v>13.42</v>
       </c>
       <c r="D388" t="s">
         <v>154</v>
@@ -6957,7 +6960,7 @@
         <v>175</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D389" t="s">
         <v>154</v>
@@ -6968,27 +6971,24 @@
         <v>175</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C390" s="6">
-        <v>9.5399999999999991</v>
+        <v>131</v>
       </c>
       <c r="D390" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A393" t="s">
-        <v>181</v>
-      </c>
-      <c r="B393" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C393" s="6">
-        <v>14.5</v>
-      </c>
-      <c r="D393" t="s">
-        <v>320</v>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>175</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C391" s="6">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="D391" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -6996,13 +6996,13 @@
         <v>181</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="C394" s="6">
-        <v>24.99</v>
+        <v>14.5</v>
       </c>
       <c r="D394" t="s">
-        <v>138</v>
+        <v>320</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -7010,10 +7010,10 @@
         <v>181</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C395" s="6">
-        <v>34.99</v>
+        <v>24.99</v>
       </c>
       <c r="D395" t="s">
         <v>138</v>
@@ -7024,13 +7024,13 @@
         <v>181</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C396" s="6">
-        <v>19.989999999999998</v>
+        <v>34.99</v>
       </c>
       <c r="D396" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -7038,10 +7038,10 @@
         <v>181</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C397" s="6">
-        <v>29.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D397" t="s">
         <v>140</v>
@@ -7052,13 +7052,13 @@
         <v>181</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C398" s="6">
-        <v>189.99</v>
+        <v>29.99</v>
       </c>
       <c r="D398" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -7066,10 +7066,10 @@
         <v>181</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C399" s="6">
-        <v>229.99</v>
+        <v>189.99</v>
       </c>
       <c r="D399" t="s">
         <v>142</v>
@@ -7080,10 +7080,10 @@
         <v>181</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>182</v>
+        <v>29</v>
       </c>
       <c r="C400" s="6">
-        <v>299.99</v>
+        <v>229.99</v>
       </c>
       <c r="D400" t="s">
         <v>142</v>
@@ -7094,10 +7094,10 @@
         <v>181</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="C401" s="6">
-        <v>189.99</v>
+        <v>299.99</v>
       </c>
       <c r="D401" t="s">
         <v>142</v>
@@ -7108,10 +7108,10 @@
         <v>181</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C402" s="6">
-        <v>229</v>
+        <v>189.99</v>
       </c>
       <c r="D402" t="s">
         <v>142</v>
@@ -7122,10 +7122,10 @@
         <v>181</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="C403" s="6">
-        <v>299.99</v>
+        <v>229</v>
       </c>
       <c r="D403" t="s">
         <v>142</v>
@@ -7136,10 +7136,10 @@
         <v>181</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="C404" s="6">
-        <v>309</v>
+        <v>299.99</v>
       </c>
       <c r="D404" t="s">
         <v>142</v>
@@ -7150,10 +7150,10 @@
         <v>181</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C405" s="6">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="D405" t="s">
         <v>142</v>
@@ -7164,10 +7164,10 @@
         <v>181</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C406" s="6">
-        <v>409</v>
+        <v>345</v>
       </c>
       <c r="D406" t="s">
         <v>142</v>
@@ -7178,10 +7178,10 @@
         <v>181</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C407" s="6">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="D407" t="s">
         <v>142</v>
@@ -7192,10 +7192,10 @@
         <v>181</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>184</v>
+        <v>33</v>
       </c>
       <c r="C408" s="6">
-        <v>389.99</v>
+        <v>389</v>
       </c>
       <c r="D408" t="s">
         <v>142</v>
@@ -7206,10 +7206,10 @@
         <v>181</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="C409" s="6">
-        <v>399.99</v>
+        <v>389.99</v>
       </c>
       <c r="D409" t="s">
         <v>142</v>
@@ -7220,7 +7220,7 @@
         <v>181</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C410" s="6">
         <v>399.99</v>
@@ -7234,10 +7234,10 @@
         <v>181</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="C411" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D411" t="s">
         <v>142</v>
@@ -7248,7 +7248,10 @@
         <v>181</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="C412" s="6">
+        <v>89.23</v>
       </c>
       <c r="D412" t="s">
         <v>142</v>
@@ -7259,10 +7262,7 @@
         <v>181</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C413" s="6">
-        <v>219.99</v>
+        <v>36</v>
       </c>
       <c r="D413" t="s">
         <v>142</v>
@@ -7273,10 +7273,10 @@
         <v>181</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="C414" s="6">
-        <v>429</v>
+        <v>219.99</v>
       </c>
       <c r="D414" t="s">
         <v>142</v>
@@ -7287,10 +7287,10 @@
         <v>181</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C415" s="6">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D415" t="s">
         <v>142</v>
@@ -7301,10 +7301,10 @@
         <v>181</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C416" s="6">
-        <v>199</v>
+        <v>439</v>
       </c>
       <c r="D416" t="s">
         <v>142</v>
@@ -7315,10 +7315,10 @@
         <v>181</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C417" s="6">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="D417" t="s">
         <v>142</v>
@@ -7329,10 +7329,10 @@
         <v>181</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C418" s="6">
-        <v>670</v>
+        <v>249</v>
       </c>
       <c r="D418" t="s">
         <v>142</v>
@@ -7343,10 +7343,10 @@
         <v>181</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C419" s="6">
-        <v>49.99</v>
+        <v>670</v>
       </c>
       <c r="D419" t="s">
         <v>142</v>
@@ -7357,7 +7357,7 @@
         <v>181</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C420" s="6">
         <v>49.99</v>
@@ -7371,13 +7371,13 @@
         <v>181</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>335</v>
+        <v>192</v>
       </c>
       <c r="C421" s="6">
-        <v>15.99</v>
+        <v>49.99</v>
       </c>
       <c r="D421" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -7385,10 +7385,10 @@
         <v>181</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C422" s="6">
-        <v>29.99</v>
+        <v>15.99</v>
       </c>
       <c r="D422" t="s">
         <v>144</v>
@@ -7399,10 +7399,10 @@
         <v>181</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C423" s="6">
-        <v>16.989999999999998</v>
+        <v>29.99</v>
       </c>
       <c r="D423" t="s">
         <v>144</v>
@@ -7413,10 +7413,10 @@
         <v>181</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C424" s="6">
-        <v>29.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D424" t="s">
         <v>144</v>
@@ -7427,10 +7427,10 @@
         <v>181</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>193</v>
+        <v>334</v>
       </c>
       <c r="C425" s="6">
-        <v>11.49</v>
+        <v>29.99</v>
       </c>
       <c r="D425" t="s">
         <v>144</v>
@@ -7441,10 +7441,10 @@
         <v>181</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C426" s="6">
-        <v>18.95</v>
+        <v>11.49</v>
       </c>
       <c r="D426" t="s">
         <v>144</v>
@@ -7455,10 +7455,10 @@
         <v>181</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C427" s="6">
-        <v>39.99</v>
+        <v>18.95</v>
       </c>
       <c r="D427" t="s">
         <v>144</v>
@@ -7468,11 +7468,11 @@
       <c r="A428" t="s">
         <v>181</v>
       </c>
-      <c r="B428" s="3">
-        <v>6102</v>
+      <c r="B428" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="C428" s="6">
-        <v>44.5</v>
+        <v>39.99</v>
       </c>
       <c r="D428" t="s">
         <v>144</v>
@@ -7482,11 +7482,11 @@
       <c r="A429" t="s">
         <v>181</v>
       </c>
-      <c r="B429" s="3" t="s">
-        <v>196</v>
+      <c r="B429" s="3">
+        <v>6102</v>
       </c>
       <c r="C429" s="6">
-        <v>112</v>
+        <v>44.5</v>
       </c>
       <c r="D429" t="s">
         <v>144</v>
@@ -7497,10 +7497,10 @@
         <v>181</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C430" s="6">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="D430" t="s">
         <v>144</v>
@@ -7511,7 +7511,7 @@
         <v>181</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C431" s="6">
         <v>139</v>
@@ -7525,7 +7525,10 @@
         <v>181</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="C432" s="6">
+        <v>139</v>
       </c>
       <c r="D432" t="s">
         <v>144</v>
@@ -7536,7 +7539,7 @@
         <v>181</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D433" t="s">
         <v>144</v>
@@ -7547,10 +7550,7 @@
         <v>181</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C434" s="6">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D434" t="s">
         <v>144</v>
@@ -7561,7 +7561,10 @@
         <v>181</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
+      </c>
+      <c r="C435" s="6">
+        <v>209</v>
       </c>
       <c r="D435" t="s">
         <v>144</v>
@@ -7572,7 +7575,7 @@
         <v>181</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D436" t="s">
         <v>144</v>
@@ -7583,10 +7586,7 @@
         <v>181</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C437" s="6">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D437" t="s">
         <v>144</v>
@@ -7597,10 +7597,10 @@
         <v>181</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C438" s="6">
-        <v>299.99</v>
+        <v>179</v>
       </c>
       <c r="D438" t="s">
         <v>144</v>
@@ -7611,10 +7611,10 @@
         <v>181</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C439" s="6">
-        <v>220</v>
+        <v>299.99</v>
       </c>
       <c r="D439" t="s">
         <v>144</v>
@@ -7625,10 +7625,10 @@
         <v>181</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C440" s="6">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="D440" t="s">
         <v>144</v>
@@ -7639,10 +7639,10 @@
         <v>181</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C441" s="6">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D441" t="s">
         <v>144</v>
@@ -7653,10 +7653,10 @@
         <v>181</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C442" s="6">
-        <v>399</v>
+        <v>240</v>
       </c>
       <c r="D442" t="s">
         <v>144</v>
@@ -7667,10 +7667,10 @@
         <v>181</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C443" s="6">
-        <v>209</v>
+        <v>399</v>
       </c>
       <c r="D443" t="s">
         <v>144</v>
@@ -7681,10 +7681,10 @@
         <v>181</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C444" s="6">
-        <v>345</v>
+        <v>209</v>
       </c>
       <c r="D444" t="s">
         <v>144</v>
@@ -7695,10 +7695,10 @@
         <v>181</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C445" s="6">
-        <v>209</v>
+        <v>345</v>
       </c>
       <c r="D445" t="s">
         <v>144</v>
@@ -7709,10 +7709,10 @@
         <v>181</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C446" s="6">
-        <v>369</v>
+        <v>209</v>
       </c>
       <c r="D446" t="s">
         <v>144</v>
@@ -7723,10 +7723,10 @@
         <v>181</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C447" s="6">
-        <v>315</v>
+        <v>369</v>
       </c>
       <c r="D447" t="s">
         <v>144</v>
@@ -7737,10 +7737,10 @@
         <v>181</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C448" s="6">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="D448" t="s">
         <v>144</v>
@@ -7751,10 +7751,10 @@
         <v>181</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C449" s="6">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="D449" t="s">
         <v>144</v>
@@ -7765,10 +7765,10 @@
         <v>181</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C450" s="6">
-        <v>420</v>
+        <v>251</v>
       </c>
       <c r="D450" t="s">
         <v>144</v>
@@ -7779,10 +7779,10 @@
         <v>181</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C451" s="6">
-        <v>315</v>
+        <v>420</v>
       </c>
       <c r="D451" t="s">
         <v>144</v>
@@ -7793,10 +7793,10 @@
         <v>181</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C452" s="6">
-        <v>365</v>
+        <v>315</v>
       </c>
       <c r="D452" t="s">
         <v>144</v>
@@ -7807,10 +7807,10 @@
         <v>181</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C453" s="6">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="D453" t="s">
         <v>144</v>
@@ -7821,13 +7821,13 @@
         <v>181</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>54</v>
+        <v>220</v>
       </c>
       <c r="C454" s="6">
-        <v>55.99</v>
+        <v>285</v>
       </c>
       <c r="D454" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
@@ -7835,10 +7835,10 @@
         <v>181</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C455" s="6">
-        <v>39.99</v>
+        <v>55.99</v>
       </c>
       <c r="D455" t="s">
         <v>145</v>
@@ -7849,10 +7849,10 @@
         <v>181</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C456" s="6">
-        <v>68</v>
+        <v>39.99</v>
       </c>
       <c r="D456" t="s">
         <v>145</v>
@@ -7863,10 +7863,10 @@
         <v>181</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C457" s="6">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="D457" t="s">
         <v>145</v>
@@ -7877,10 +7877,10 @@
         <v>181</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>255</v>
+        <v>58</v>
       </c>
       <c r="C458" s="6">
-        <v>30.99</v>
+        <v>129</v>
       </c>
       <c r="D458" t="s">
         <v>145</v>
@@ -7891,10 +7891,10 @@
         <v>181</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C459" s="6">
-        <v>42.99</v>
+        <v>30.99</v>
       </c>
       <c r="D459" t="s">
         <v>145</v>
@@ -7905,10 +7905,10 @@
         <v>181</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C460" s="6">
-        <v>159</v>
+        <v>42.99</v>
       </c>
       <c r="D460" t="s">
         <v>145</v>
@@ -7919,10 +7919,10 @@
         <v>181</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C461" s="6">
-        <v>49.99</v>
+        <v>159</v>
       </c>
       <c r="D461" t="s">
         <v>145</v>
@@ -7933,10 +7933,10 @@
         <v>181</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C462" s="6">
-        <v>129</v>
+        <v>49.99</v>
       </c>
       <c r="D462" t="s">
         <v>145</v>
@@ -7947,13 +7947,13 @@
         <v>181</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>59</v>
+        <v>275</v>
       </c>
       <c r="C463" s="6">
-        <v>47.99</v>
+        <v>129</v>
       </c>
       <c r="D463" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -7961,13 +7961,13 @@
         <v>181</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>221</v>
+        <v>59</v>
       </c>
       <c r="C464" s="6">
-        <v>34.99</v>
+        <v>47.99</v>
       </c>
       <c r="D464" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -7975,10 +7975,10 @@
         <v>181</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="C465" s="6">
-        <v>89.99</v>
+        <v>34.99</v>
       </c>
       <c r="D465" t="s">
         <v>172</v>
@@ -7989,13 +7989,13 @@
         <v>181</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="C466" s="6">
-        <v>45</v>
+        <v>89.99</v>
       </c>
       <c r="D466" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
@@ -8003,10 +8003,10 @@
         <v>181</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="C467" s="6">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D467" t="s">
         <v>149</v>
@@ -8017,10 +8017,10 @@
         <v>181</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C468" s="6">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D468" t="s">
         <v>149</v>
@@ -8031,13 +8031,13 @@
         <v>181</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="C469" s="6">
-        <v>79.989999999999995</v>
+        <v>125</v>
       </c>
       <c r="D469" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -8045,13 +8045,13 @@
         <v>181</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="C470" s="6">
-        <v>7.95</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D470" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -8059,10 +8059,10 @@
         <v>181</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C471" s="6">
-        <v>18.95</v>
+        <v>7.95</v>
       </c>
       <c r="D471" t="s">
         <v>173</v>
@@ -8073,10 +8073,10 @@
         <v>181</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C472" s="6">
-        <v>36.950000000000003</v>
+        <v>18.95</v>
       </c>
       <c r="D472" t="s">
         <v>173</v>
@@ -8087,13 +8087,13 @@
         <v>181</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>127</v>
+        <v>278</v>
       </c>
       <c r="C473" s="6">
-        <v>39.99</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D473" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -8101,13 +8101,13 @@
         <v>181</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="C474" s="6">
-        <v>19.5</v>
+        <v>39.99</v>
       </c>
       <c r="D474" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -8115,10 +8115,10 @@
         <v>181</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="C475" s="6">
-        <v>110</v>
+        <v>19.5</v>
       </c>
       <c r="D475" t="s">
         <v>139</v>
@@ -8129,10 +8129,10 @@
         <v>181</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C476" s="6">
-        <v>98.45</v>
+        <v>110</v>
       </c>
       <c r="D476" t="s">
         <v>139</v>
@@ -8143,10 +8143,10 @@
         <v>181</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C477" s="6">
-        <v>139</v>
+        <v>98.45</v>
       </c>
       <c r="D477" t="s">
         <v>139</v>
@@ -8157,10 +8157,10 @@
         <v>181</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C478" s="6">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="D478" t="s">
         <v>139</v>
@@ -8171,10 +8171,10 @@
         <v>181</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C479" s="6">
-        <v>169.99</v>
+        <v>199</v>
       </c>
       <c r="D479" t="s">
         <v>139</v>
@@ -8185,10 +8185,10 @@
         <v>181</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C480" s="6">
-        <v>239.08</v>
+        <v>169.99</v>
       </c>
       <c r="D480" t="s">
         <v>139</v>
@@ -8199,10 +8199,10 @@
         <v>181</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C481" s="6">
-        <v>219</v>
+        <v>239.08</v>
       </c>
       <c r="D481" t="s">
         <v>139</v>
@@ -8213,10 +8213,10 @@
         <v>181</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C482" s="6">
-        <v>189.99</v>
+        <v>219</v>
       </c>
       <c r="D482" t="s">
         <v>139</v>
@@ -8227,10 +8227,10 @@
         <v>181</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C483" s="6">
-        <v>248</v>
+        <v>189.99</v>
       </c>
       <c r="D483" t="s">
         <v>139</v>
@@ -8241,10 +8241,10 @@
         <v>181</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C484" s="6">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="D484" t="s">
         <v>139</v>
@@ -8255,26 +8255,26 @@
         <v>181</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C485" s="6">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="D485" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
-        <v>224</v>
-      </c>
-      <c r="B495" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C495" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D495" t="s">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>181</v>
+      </c>
+      <c r="B486" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C486" s="6">
+        <v>322</v>
+      </c>
+      <c r="D486" t="s">
         <v>139</v>
       </c>
     </row>
@@ -8283,10 +8283,10 @@
         <v>224</v>
       </c>
       <c r="B496" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C496" s="6">
-        <v>79.47</v>
+        <v>42.75</v>
       </c>
       <c r="D496" t="s">
         <v>139</v>
@@ -8297,10 +8297,10 @@
         <v>224</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C497" s="6">
-        <v>92.85</v>
+        <v>79.47</v>
       </c>
       <c r="D497" t="s">
         <v>139</v>
@@ -8310,14 +8310,14 @@
       <c r="A498" t="s">
         <v>224</v>
       </c>
-      <c r="B498" s="3">
-        <v>4430</v>
+      <c r="B498" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="C498" s="6">
-        <v>15.25</v>
+        <v>92.85</v>
       </c>
       <c r="D498" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
@@ -8325,10 +8325,10 @@
         <v>224</v>
       </c>
       <c r="B499" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C499" s="6">
-        <v>18.899999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="D499" t="s">
         <v>148</v>
@@ -8339,10 +8339,10 @@
         <v>224</v>
       </c>
       <c r="B500" s="3">
-        <v>6642</v>
+        <v>4442</v>
       </c>
       <c r="C500" s="6">
-        <v>26.8</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D500" t="s">
         <v>148</v>
@@ -8353,27 +8353,27 @@
         <v>224</v>
       </c>
       <c r="B501" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C501" s="6">
-        <v>27.05</v>
+        <v>26.8</v>
       </c>
       <c r="D501" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
-        <v>228</v>
-      </c>
-      <c r="B504" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C504" s="6">
-        <v>47.95</v>
-      </c>
-      <c r="D504" t="s">
-        <v>139</v>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>224</v>
+      </c>
+      <c r="B502" s="3">
+        <v>6660</v>
+      </c>
+      <c r="C502" s="6">
+        <v>27.05</v>
+      </c>
+      <c r="D502" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -8381,10 +8381,10 @@
         <v>228</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C505" s="6">
-        <v>59.07</v>
+        <v>47.95</v>
       </c>
       <c r="D505" t="s">
         <v>139</v>
@@ -8395,10 +8395,10 @@
         <v>228</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C506" s="6">
-        <v>83.8</v>
+        <v>59.07</v>
       </c>
       <c r="D506" t="s">
         <v>139</v>
@@ -8409,10 +8409,10 @@
         <v>228</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C507" s="6">
-        <v>115.4</v>
+        <v>83.8</v>
       </c>
       <c r="D507" t="s">
         <v>139</v>
@@ -8423,10 +8423,10 @@
         <v>228</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C508" s="6">
-        <v>107.15</v>
+        <v>115.4</v>
       </c>
       <c r="D508" t="s">
         <v>139</v>
@@ -8437,13 +8437,13 @@
         <v>228</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C509" s="6">
-        <v>13</v>
+        <v>107.15</v>
       </c>
       <c r="D509" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
@@ -8451,10 +8451,10 @@
         <v>228</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C510" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D510" t="s">
         <v>140</v>
@@ -8465,27 +8465,27 @@
         <v>228</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C511" s="6">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D511" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>228</v>
       </c>
-      <c r="B512" s="3">
-        <v>4430</v>
+      <c r="B512" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="C512" s="6">
-        <v>15.25</v>
+        <v>30</v>
       </c>
       <c r="D512" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
@@ -8493,10 +8493,10 @@
         <v>228</v>
       </c>
       <c r="B513" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C513" s="6">
-        <v>18.899999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="D513" t="s">
         <v>148</v>
@@ -8507,10 +8507,10 @@
         <v>228</v>
       </c>
       <c r="B514" s="3">
-        <v>6642</v>
+        <v>4442</v>
       </c>
       <c r="C514" s="6">
-        <v>26.8</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D514" t="s">
         <v>148</v>
@@ -8520,28 +8520,28 @@
       <c r="A515" t="s">
         <v>228</v>
       </c>
-      <c r="B515" s="3" t="s">
+      <c r="B515" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C515" s="6">
+        <v>26.8</v>
+      </c>
+      <c r="D515" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>228</v>
+      </c>
+      <c r="B516" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C515" s="6">
+      <c r="C516" s="6">
         <v>39.950000000000003</v>
       </c>
-      <c r="D515" t="s">
+      <c r="D516" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A518" t="s">
-        <v>229</v>
-      </c>
-      <c r="B518" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C518" s="6">
-        <v>9.92</v>
-      </c>
-      <c r="D518" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
@@ -8549,13 +8549,13 @@
         <v>229</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>9</v>
+        <v>230</v>
       </c>
       <c r="C519" s="6">
-        <v>47.95</v>
+        <v>9.92</v>
       </c>
       <c r="D519" t="s">
-        <v>139</v>
+        <v>231</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
@@ -8563,10 +8563,10 @@
         <v>229</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C520" s="6">
-        <v>55.73</v>
+        <v>47.95</v>
       </c>
       <c r="D520" t="s">
         <v>139</v>
@@ -8577,10 +8577,10 @@
         <v>229</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C521" s="6">
-        <v>79.06</v>
+        <v>55.73</v>
       </c>
       <c r="D521" t="s">
         <v>139</v>
@@ -8591,10 +8591,10 @@
         <v>229</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C522" s="6">
-        <v>108.86</v>
+        <v>79.06</v>
       </c>
       <c r="D522" t="s">
         <v>139</v>
@@ -8605,10 +8605,10 @@
         <v>229</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C523" s="6">
-        <v>101.09</v>
+        <v>108.86</v>
       </c>
       <c r="D523" t="s">
         <v>139</v>
@@ -8619,10 +8619,10 @@
         <v>229</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C524" s="6">
-        <v>160.69999999999999</v>
+        <v>101.09</v>
       </c>
       <c r="D524" t="s">
         <v>139</v>
@@ -8633,10 +8633,10 @@
         <v>229</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C525" s="6">
-        <v>121.82</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="D525" t="s">
         <v>139</v>
@@ -8647,10 +8647,10 @@
         <v>229</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C526" s="6">
-        <v>122.49</v>
+        <v>121.82</v>
       </c>
       <c r="D526" t="s">
         <v>139</v>
@@ -8661,7 +8661,10 @@
         <v>229</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="C527" s="6">
+        <v>122.49</v>
       </c>
       <c r="D527" t="s">
         <v>139</v>
@@ -8672,7 +8675,7 @@
         <v>229</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D528" t="s">
         <v>139</v>
@@ -8683,7 +8686,7 @@
         <v>229</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D529" t="s">
         <v>139</v>
@@ -8694,10 +8697,7 @@
         <v>229</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C530" s="6">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D530" t="s">
         <v>139</v>
@@ -8708,10 +8708,10 @@
         <v>229</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C531" s="6">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D531" t="s">
         <v>139</v>
@@ -8722,10 +8722,10 @@
         <v>229</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C532" s="6">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D532" t="s">
         <v>139</v>
@@ -8736,18 +8736,21 @@
         <v>229</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>92</v>
+        <v>227</v>
+      </c>
+      <c r="C533" s="6">
+        <v>79</v>
       </c>
       <c r="D533" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>229</v>
       </c>
-      <c r="B534" s="3">
-        <v>4430</v>
+      <c r="B534" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D534" t="s">
         <v>148</v>
@@ -8758,10 +8761,7 @@
         <v>229</v>
       </c>
       <c r="B535" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C535" s="6">
-        <v>15</v>
+        <v>4430</v>
       </c>
       <c r="D535" t="s">
         <v>148</v>
@@ -8771,11 +8771,11 @@
       <c r="A536" t="s">
         <v>229</v>
       </c>
-      <c r="B536" s="3" t="s">
-        <v>96</v>
+      <c r="B536" s="3">
+        <v>4442</v>
       </c>
       <c r="C536" s="6">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="D536" t="s">
         <v>148</v>
@@ -8786,7 +8786,10 @@
         <v>229</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="C537" s="6">
+        <v>171</v>
       </c>
       <c r="D537" t="s">
         <v>148</v>
@@ -8796,11 +8799,8 @@
       <c r="A538" t="s">
         <v>229</v>
       </c>
-      <c r="B538" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C538" s="6">
-        <v>16.5</v>
+      <c r="B538" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D538" t="s">
         <v>148</v>
@@ -8810,11 +8810,11 @@
       <c r="A539" t="s">
         <v>229</v>
       </c>
-      <c r="B539" s="3" t="s">
-        <v>98</v>
+      <c r="B539" s="3">
+        <v>4642</v>
       </c>
       <c r="C539" s="6">
-        <v>126</v>
+        <v>16.5</v>
       </c>
       <c r="D539" t="s">
         <v>148</v>
@@ -8824,11 +8824,11 @@
       <c r="A540" t="s">
         <v>229</v>
       </c>
-      <c r="B540" s="3">
-        <v>4660</v>
+      <c r="B540" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C540" s="6">
-        <v>20.25</v>
+        <v>126</v>
       </c>
       <c r="D540" t="s">
         <v>148</v>
@@ -8839,7 +8839,10 @@
         <v>229</v>
       </c>
       <c r="B541" s="3">
-        <v>6630</v>
+        <v>4660</v>
+      </c>
+      <c r="C541" s="6">
+        <v>20.25</v>
       </c>
       <c r="D541" t="s">
         <v>148</v>
@@ -8850,10 +8853,7 @@
         <v>229</v>
       </c>
       <c r="B542" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C542" s="6">
-        <v>18.5</v>
+        <v>6630</v>
       </c>
       <c r="D542" t="s">
         <v>148</v>
@@ -8863,11 +8863,11 @@
       <c r="A543" t="s">
         <v>229</v>
       </c>
-      <c r="B543" s="3" t="s">
-        <v>99</v>
+      <c r="B543" s="3">
+        <v>6642</v>
       </c>
       <c r="C543" s="6">
-        <v>103.5</v>
+        <v>18.5</v>
       </c>
       <c r="D543" t="s">
         <v>148</v>
@@ -8877,11 +8877,11 @@
       <c r="A544" t="s">
         <v>229</v>
       </c>
-      <c r="B544" s="3">
-        <v>6660</v>
+      <c r="B544" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C544" s="6">
-        <v>22.5</v>
+        <v>103.5</v>
       </c>
       <c r="D544" t="s">
         <v>148</v>
@@ -8891,11 +8891,11 @@
       <c r="A545" t="s">
         <v>229</v>
       </c>
-      <c r="B545" s="3" t="s">
-        <v>100</v>
+      <c r="B545" s="3">
+        <v>6660</v>
       </c>
       <c r="C545" s="6">
-        <v>126</v>
+        <v>22.5</v>
       </c>
       <c r="D545" t="s">
         <v>148</v>
@@ -8905,21 +8905,24 @@
       <c r="A546" t="s">
         <v>229</v>
       </c>
-      <c r="B546" s="3">
-        <v>8860</v>
+      <c r="B546" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C546" s="6">
+        <v>126</v>
       </c>
       <c r="D546" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A549" t="s">
-        <v>232</v>
-      </c>
-      <c r="B549" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D549" t="s">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>229</v>
+      </c>
+      <c r="B547" s="3">
+        <v>8860</v>
+      </c>
+      <c r="D547" t="s">
         <v>148</v>
       </c>
     </row>
@@ -8927,11 +8930,8 @@
       <c r="A550" t="s">
         <v>232</v>
       </c>
-      <c r="B550" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C550" s="6">
-        <v>15.25</v>
+      <c r="B550" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="D550" t="s">
         <v>148</v>
@@ -8942,10 +8942,10 @@
         <v>232</v>
       </c>
       <c r="B551" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C551" s="6">
-        <v>15</v>
+        <v>15.25</v>
       </c>
       <c r="D551" t="s">
         <v>148</v>
@@ -8955,11 +8955,11 @@
       <c r="A552" t="s">
         <v>232</v>
       </c>
-      <c r="B552" s="3" t="s">
-        <v>96</v>
+      <c r="B552" s="3">
+        <v>4442</v>
       </c>
       <c r="C552" s="6">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="D552" t="s">
         <v>148</v>
@@ -8970,10 +8970,10 @@
         <v>232</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C553" s="6">
-        <v>972</v>
+        <v>171</v>
       </c>
       <c r="D553" t="s">
         <v>148</v>
@@ -8983,11 +8983,11 @@
       <c r="A554" t="s">
         <v>232</v>
       </c>
-      <c r="B554" s="3">
-        <v>4642</v>
+      <c r="B554" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C554" s="6">
-        <v>16.5</v>
+        <v>972</v>
       </c>
       <c r="D554" t="s">
         <v>148</v>
@@ -8997,11 +8997,11 @@
       <c r="A555" t="s">
         <v>232</v>
       </c>
-      <c r="B555" s="3" t="s">
-        <v>98</v>
+      <c r="B555" s="3">
+        <v>4642</v>
       </c>
       <c r="C555" s="6">
-        <v>126</v>
+        <v>16.5</v>
       </c>
       <c r="D555" t="s">
         <v>148</v>
@@ -9011,11 +9011,11 @@
       <c r="A556" t="s">
         <v>232</v>
       </c>
-      <c r="B556" s="3">
-        <v>4660</v>
+      <c r="B556" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C556" s="6">
-        <v>20.25</v>
+        <v>126</v>
       </c>
       <c r="D556" t="s">
         <v>148</v>
@@ -9026,10 +9026,10 @@
         <v>232</v>
       </c>
       <c r="B557" s="3">
-        <v>6630</v>
+        <v>4660</v>
       </c>
       <c r="C557" s="6">
-        <v>19</v>
+        <v>20.25</v>
       </c>
       <c r="D557" t="s">
         <v>148</v>
@@ -9040,10 +9040,10 @@
         <v>232</v>
       </c>
       <c r="B558" s="3">
-        <v>6642</v>
+        <v>6630</v>
       </c>
       <c r="C558" s="6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="D558" t="s">
         <v>148</v>
@@ -9053,11 +9053,11 @@
       <c r="A559" t="s">
         <v>232</v>
       </c>
-      <c r="B559" s="3" t="s">
-        <v>99</v>
+      <c r="B559" s="3">
+        <v>6642</v>
       </c>
       <c r="C559" s="6">
-        <v>103.5</v>
+        <v>18.5</v>
       </c>
       <c r="D559" t="s">
         <v>148</v>
@@ -9067,11 +9067,11 @@
       <c r="A560" t="s">
         <v>232</v>
       </c>
-      <c r="B560" s="3">
-        <v>6660</v>
+      <c r="B560" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C560" s="6">
-        <v>22.5</v>
+        <v>103.5</v>
       </c>
       <c r="D560" t="s">
         <v>148</v>
@@ -9081,11 +9081,11 @@
       <c r="A561" t="s">
         <v>232</v>
       </c>
-      <c r="B561" s="3" t="s">
-        <v>100</v>
+      <c r="B561" s="3">
+        <v>6660</v>
       </c>
       <c r="C561" s="6">
-        <v>126</v>
+        <v>22.5</v>
       </c>
       <c r="D561" t="s">
         <v>148</v>
@@ -9095,11 +9095,11 @@
       <c r="A562" t="s">
         <v>232</v>
       </c>
-      <c r="B562" s="3">
-        <v>8860</v>
+      <c r="B562" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C562" s="6">
-        <v>42.25</v>
+        <v>126</v>
       </c>
       <c r="D562" t="s">
         <v>148</v>
@@ -9109,14 +9109,14 @@
       <c r="A563" t="s">
         <v>232</v>
       </c>
-      <c r="B563" s="3" t="s">
-        <v>316</v>
+      <c r="B563" s="3">
+        <v>8860</v>
       </c>
       <c r="C563" s="6">
-        <v>5.75</v>
+        <v>42.25</v>
       </c>
       <c r="D563" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
@@ -9124,10 +9124,10 @@
         <v>232</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C564" s="6">
-        <v>20</v>
+        <v>5.75</v>
       </c>
       <c r="D564" t="s">
         <v>309</v>
@@ -9138,10 +9138,10 @@
         <v>232</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C565" s="6">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="D565" t="s">
         <v>309</v>
@@ -9152,10 +9152,10 @@
         <v>232</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C566" s="6">
-        <v>77.5</v>
+        <v>12.5</v>
       </c>
       <c r="D566" t="s">
         <v>309</v>
@@ -9166,27 +9166,27 @@
         <v>232</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C567" s="6">
-        <v>195</v>
+        <v>77.5</v>
       </c>
       <c r="D567" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A571" t="s">
-        <v>276</v>
-      </c>
-      <c r="B571" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C571" s="6">
-        <v>50.35</v>
-      </c>
-      <c r="D571" t="s">
-        <v>139</v>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>232</v>
+      </c>
+      <c r="B568" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C568" s="6">
+        <v>195</v>
+      </c>
+      <c r="D568" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
@@ -9194,10 +9194,10 @@
         <v>276</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C572" s="6">
-        <v>106.14</v>
+        <v>50.35</v>
       </c>
       <c r="D572" t="s">
         <v>139</v>
@@ -9208,13 +9208,13 @@
         <v>276</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C573" s="6">
-        <v>41.99</v>
+        <v>106.14</v>
       </c>
       <c r="D573" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
@@ -9222,13 +9222,13 @@
         <v>276</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C574" s="6">
-        <v>82</v>
+        <v>41.99</v>
       </c>
       <c r="D574" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
@@ -9236,10 +9236,10 @@
         <v>276</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="C575" s="6">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D575" t="s">
         <v>145</v>
@@ -9250,13 +9250,13 @@
         <v>276</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>112</v>
+        <v>256</v>
       </c>
       <c r="C576" s="6">
-        <v>28.05</v>
+        <v>28</v>
       </c>
       <c r="D576" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.25">
@@ -9264,7 +9264,7 @@
         <v>276</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C577" s="6">
         <v>28.05</v>
@@ -9278,7 +9278,7 @@
         <v>276</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C578" s="6">
         <v>28.05</v>
@@ -9292,27 +9292,27 @@
         <v>276</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C579" s="6">
-        <v>11.2</v>
+        <v>28.05</v>
       </c>
       <c r="D579" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A582" t="s">
-        <v>144</v>
-      </c>
-      <c r="B582" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C582" s="6">
-        <v>29.87</v>
-      </c>
-      <c r="D582" t="s">
-        <v>136</v>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>276</v>
+      </c>
+      <c r="B580" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C580" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="D580" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
@@ -9320,13 +9320,13 @@
         <v>144</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C583" s="6">
-        <v>199</v>
+        <v>29.87</v>
       </c>
       <c r="D583" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -9334,13 +9334,13 @@
         <v>144</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C584" s="6">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="D584" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
@@ -9348,10 +9348,10 @@
         <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C585" s="6">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D585" t="s">
         <v>142</v>
@@ -9362,10 +9362,10 @@
         <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C586" s="6">
-        <v>224.1</v>
+        <v>189</v>
       </c>
       <c r="D586" t="s">
         <v>142</v>
@@ -9376,10 +9376,10 @@
         <v>144</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C587" s="6">
-        <v>309</v>
+        <v>224.1</v>
       </c>
       <c r="D587" t="s">
         <v>142</v>
@@ -9390,10 +9390,10 @@
         <v>144</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C588" s="6">
-        <v>85.5</v>
+        <v>309</v>
       </c>
       <c r="D588" t="s">
         <v>142</v>
@@ -9403,25 +9403,25 @@
       <c r="A589" t="s">
         <v>144</v>
       </c>
-      <c r="B589" s="3">
-        <v>6102</v>
+      <c r="B589" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C589" s="6">
-        <v>38.99</v>
+        <v>85.5</v>
       </c>
       <c r="D589" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>144</v>
       </c>
-      <c r="B590" s="3" t="s">
-        <v>212</v>
+      <c r="B590" s="3">
+        <v>6102</v>
       </c>
       <c r="C590" s="6">
-        <v>175</v>
+        <v>38.99</v>
       </c>
       <c r="D590" t="s">
         <v>144</v>
@@ -9432,10 +9432,10 @@
         <v>144</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C591" s="6">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D591" t="s">
         <v>144</v>
@@ -9446,13 +9446,13 @@
         <v>144</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="C592" s="6">
-        <v>59.99</v>
+        <v>134</v>
       </c>
       <c r="D592" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
@@ -9460,10 +9460,10 @@
         <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C593" s="6">
-        <v>32.99</v>
+        <v>59.99</v>
       </c>
       <c r="D593" t="s">
         <v>145</v>
@@ -9474,10 +9474,10 @@
         <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C594" s="6">
-        <v>129</v>
+        <v>32.99</v>
       </c>
       <c r="D594" t="s">
         <v>145</v>
@@ -9488,10 +9488,10 @@
         <v>144</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C595" s="6">
-        <v>149.99</v>
+        <v>129</v>
       </c>
       <c r="D595" t="s">
         <v>145</v>
@@ -9502,13 +9502,13 @@
         <v>144</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C596" s="6">
-        <v>47.99</v>
+        <v>149.99</v>
       </c>
       <c r="D596" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
@@ -9516,10 +9516,10 @@
         <v>144</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C597" s="6">
-        <v>39.99</v>
+        <v>47.99</v>
       </c>
       <c r="D597" t="s">
         <v>146</v>
@@ -9530,13 +9530,13 @@
         <v>144</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C598" s="6">
         <v>39.99</v>
       </c>
       <c r="D598" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
@@ -9544,7 +9544,10 @@
         <v>144</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="C599" s="6">
+        <v>39.99</v>
       </c>
       <c r="D599" t="s">
         <v>151</v>
@@ -9555,27 +9558,24 @@
         <v>144</v>
       </c>
       <c r="B600" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D600" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>144</v>
+      </c>
+      <c r="B601" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C600" s="6">
+      <c r="C601" s="6">
         <v>36.950000000000003</v>
       </c>
-      <c r="D600" t="s">
+      <c r="D601" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A603" t="s">
-        <v>288</v>
-      </c>
-      <c r="B603" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C603" s="6">
-        <v>18</v>
-      </c>
-      <c r="D603" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
@@ -9583,10 +9583,10 @@
         <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C604" s="6">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9597,10 +9597,10 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C605" s="6">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -9611,10 +9611,10 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C606" s="6">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -9625,10 +9625,10 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C607" s="6">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D607" t="s">
         <v>139</v>
@@ -9639,10 +9639,10 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C608" s="6">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="D608" t="s">
         <v>139</v>
@@ -9653,10 +9653,10 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C609" s="6">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="D609" t="s">
         <v>139</v>
@@ -9667,10 +9667,10 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C610" s="6">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="D610" t="s">
         <v>139</v>
@@ -9681,10 +9681,10 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C611" s="6">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D611" t="s">
         <v>139</v>
@@ -9695,10 +9695,10 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C612" s="6">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D612" t="s">
         <v>139</v>
@@ -9709,10 +9709,10 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C613" s="6">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="D613" t="s">
         <v>139</v>
@@ -9723,10 +9723,10 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C614" s="6">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D614" t="s">
         <v>139</v>
@@ -9737,13 +9737,13 @@
         <v>288</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C615" s="6">
-        <v>19.989999999999998</v>
+        <v>250</v>
       </c>
       <c r="D615" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
@@ -9751,10 +9751,10 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C616" s="6">
-        <v>29.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D616" t="s">
         <v>140</v>
@@ -9765,13 +9765,13 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C617" s="6">
-        <v>155</v>
+        <v>29.99</v>
       </c>
       <c r="D617" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.25">
@@ -9779,10 +9779,10 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C618" s="6">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D618" t="s">
         <v>142</v>
@@ -9793,10 +9793,10 @@
         <v>288</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C619" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D619" t="s">
         <v>142</v>
@@ -9807,10 +9807,10 @@
         <v>288</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C620" s="6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D620" t="s">
         <v>142</v>
@@ -9821,10 +9821,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C621" s="6">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D621" t="s">
         <v>142</v>
@@ -9835,10 +9835,10 @@
         <v>288</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C622" s="6">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="D622" t="s">
         <v>142</v>
@@ -9849,10 +9849,10 @@
         <v>288</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C623" s="6">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="D623" t="s">
         <v>142</v>
@@ -9863,10 +9863,10 @@
         <v>288</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C624" s="6">
-        <v>399.99</v>
+        <v>389</v>
       </c>
       <c r="D624" t="s">
         <v>142</v>
@@ -9877,10 +9877,10 @@
         <v>288</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C625" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D625" t="s">
         <v>142</v>
@@ -9890,28 +9890,28 @@
       <c r="A626" t="s">
         <v>288</v>
       </c>
-      <c r="B626" s="3">
-        <v>6102</v>
+      <c r="B626" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C626" s="6">
-        <v>44</v>
+        <v>89.23</v>
       </c>
       <c r="D626" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>288</v>
       </c>
-      <c r="B627" s="3" t="s">
-        <v>281</v>
+      <c r="B627" s="3">
+        <v>6102</v>
       </c>
       <c r="C627" s="6">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D627" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
@@ -9919,10 +9919,10 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C628" s="6">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D628" t="s">
         <v>269</v>
@@ -9933,10 +9933,10 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C629" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D629" t="s">
         <v>269</v>
@@ -9947,10 +9947,10 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C630" s="6">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D630" t="s">
         <v>269</v>
@@ -9961,10 +9961,10 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C631" s="6">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D631" t="s">
         <v>269</v>
@@ -9975,10 +9975,10 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C632" s="6">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D632" t="s">
         <v>269</v>
@@ -9989,13 +9989,13 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="C633" s="6">
-        <v>27.99</v>
+        <v>114</v>
       </c>
       <c r="D633" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.25">
@@ -10003,10 +10003,10 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>255</v>
+        <v>55</v>
       </c>
       <c r="C634" s="6">
-        <v>28.99</v>
+        <v>27.99</v>
       </c>
       <c r="D634" t="s">
         <v>145</v>
@@ -10017,10 +10017,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="C635" s="6">
-        <v>39.99</v>
+        <v>28.99</v>
       </c>
       <c r="D635" t="s">
         <v>145</v>
@@ -10031,10 +10031,10 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C636" s="6">
-        <v>58</v>
+        <v>39.99</v>
       </c>
       <c r="D636" t="s">
         <v>145</v>
@@ -10045,10 +10045,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C637" s="6">
-        <v>42.99</v>
+        <v>58</v>
       </c>
       <c r="D637" t="s">
         <v>145</v>
@@ -10059,10 +10059,10 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C638" s="6">
-        <v>129</v>
+        <v>42.99</v>
       </c>
       <c r="D638" t="s">
         <v>145</v>
@@ -10073,10 +10073,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C639" s="6">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="D639" t="s">
         <v>145</v>
@@ -10087,13 +10087,13 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C640" s="6">
-        <v>54.5</v>
+        <v>180</v>
       </c>
       <c r="D640" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
@@ -10101,10 +10101,10 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C641" s="6">
-        <v>48.99</v>
+        <v>54.5</v>
       </c>
       <c r="D641" t="s">
         <v>146</v>
@@ -10115,10 +10115,10 @@
         <v>288</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C642" s="6">
-        <v>39.99</v>
+        <v>48.99</v>
       </c>
       <c r="D642" t="s">
         <v>146</v>
@@ -10129,10 +10129,10 @@
         <v>288</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C643" s="6">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="D643" t="s">
         <v>146</v>
@@ -10143,10 +10143,10 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C644" s="6">
-        <v>29.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D644" t="s">
         <v>146</v>
@@ -10157,10 +10157,10 @@
         <v>288</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C645" s="6">
-        <v>28.99</v>
+        <v>29.99</v>
       </c>
       <c r="D645" t="s">
         <v>146</v>
@@ -10171,7 +10171,10 @@
         <v>288</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>176</v>
+        <v>66</v>
+      </c>
+      <c r="C646" s="6">
+        <v>28.99</v>
       </c>
       <c r="D646" t="s">
         <v>146</v>
@@ -10182,10 +10185,7 @@
         <v>288</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C647" s="6">
-        <v>29.99</v>
+        <v>176</v>
       </c>
       <c r="D647" t="s">
         <v>146</v>
@@ -10196,10 +10196,10 @@
         <v>288</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C648" s="6">
-        <v>25.99</v>
+        <v>29.99</v>
       </c>
       <c r="D648" t="s">
         <v>146</v>
@@ -10209,28 +10209,28 @@
       <c r="A649" t="s">
         <v>288</v>
       </c>
-      <c r="B649" s="3">
-        <v>6642</v>
+      <c r="B649" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C649" s="6">
-        <v>50</v>
+        <v>25.99</v>
       </c>
       <c r="D649" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>288</v>
       </c>
-      <c r="B650" s="3" t="s">
-        <v>117</v>
+      <c r="B650" s="3">
+        <v>6642</v>
       </c>
       <c r="C650" s="6">
-        <v>19.2</v>
+        <v>50</v>
       </c>
       <c r="D650" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
@@ -10238,10 +10238,10 @@
         <v>288</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C651" s="6">
-        <v>40</v>
+        <v>19.2</v>
       </c>
       <c r="D651" t="s">
         <v>152</v>
@@ -10252,7 +10252,7 @@
         <v>288</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C652" s="6">
         <v>40</v>
@@ -10266,13 +10266,13 @@
         <v>288</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="C653" s="6">
-        <v>30.58</v>
+        <v>40</v>
       </c>
       <c r="D653" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
@@ -10280,10 +10280,10 @@
         <v>288</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C654" s="6">
-        <v>39.99</v>
+        <v>30.58</v>
       </c>
       <c r="D654" t="s">
         <v>154</v>
@@ -10294,27 +10294,27 @@
         <v>288</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="C655" s="6">
-        <v>90</v>
+        <v>39.99</v>
       </c>
       <c r="D655" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A658" t="s">
-        <v>290</v>
-      </c>
-      <c r="B658" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C658" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D658" t="s">
-        <v>139</v>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>288</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C656" s="6">
+        <v>90</v>
+      </c>
+      <c r="D656" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
@@ -10322,10 +10322,10 @@
         <v>290</v>
       </c>
       <c r="B659" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C659" s="6">
-        <v>68</v>
+        <v>42.75</v>
       </c>
       <c r="D659" t="s">
         <v>139</v>
@@ -10336,27 +10336,27 @@
         <v>290</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C660" s="6">
-        <v>82.2</v>
+        <v>68</v>
       </c>
       <c r="D660" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A662" t="s">
-        <v>304</v>
-      </c>
-      <c r="B662" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C662" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="D662" t="s">
-        <v>140</v>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>290</v>
+      </c>
+      <c r="B661" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C661" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D661" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.25">
@@ -10364,10 +10364,10 @@
         <v>304</v>
       </c>
       <c r="B663" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C663" s="6">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="D663" t="s">
         <v>140</v>
@@ -10377,14 +10377,14 @@
       <c r="A664" t="s">
         <v>304</v>
       </c>
-      <c r="B664" s="3">
-        <v>4642</v>
+      <c r="B664" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C664" s="6">
-        <v>18.96</v>
+        <v>3.25</v>
       </c>
       <c r="D664" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
@@ -10392,10 +10392,10 @@
         <v>304</v>
       </c>
       <c r="B665" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C665" s="6">
-        <v>22.37</v>
+        <v>18.96</v>
       </c>
       <c r="D665" t="s">
         <v>148</v>
@@ -10405,14 +10405,14 @@
       <c r="A666" t="s">
         <v>304</v>
       </c>
-      <c r="B666" s="3" t="s">
-        <v>116</v>
+      <c r="B666" s="3">
+        <v>6642</v>
       </c>
       <c r="C666" s="6">
-        <v>9.1</v>
+        <v>22.37</v>
       </c>
       <c r="D666" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.25">
@@ -10420,7 +10420,7 @@
         <v>304</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C667" s="6">
         <v>9.1</v>
@@ -10429,18 +10429,18 @@
         <v>152</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A672" t="s">
-        <v>292</v>
-      </c>
-      <c r="B672" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C672" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="D672" t="s">
-        <v>140</v>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>304</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C668" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D668" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
@@ -10448,27 +10448,27 @@
         <v>292</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C673" s="6">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="D673" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A677" t="s">
-        <v>293</v>
-      </c>
-      <c r="B677" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C677" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D677" t="s">
-        <v>303</v>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>292</v>
+      </c>
+      <c r="B674" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C674" s="6">
+        <v>3.25</v>
+      </c>
+      <c r="D674" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
@@ -10476,10 +10476,10 @@
         <v>293</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C678" s="6">
-        <v>7.65</v>
+        <v>3.15</v>
       </c>
       <c r="D678" t="s">
         <v>303</v>
@@ -10490,10 +10490,10 @@
         <v>293</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C679" s="6">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="D679" t="s">
         <v>303</v>
@@ -10504,10 +10504,10 @@
         <v>293</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C680" s="6">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="D680" t="s">
         <v>303</v>
@@ -10518,10 +10518,10 @@
         <v>293</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C681" s="6">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="D681" t="s">
         <v>303</v>
@@ -10532,10 +10532,10 @@
         <v>293</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C682" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D682" t="s">
         <v>303</v>
@@ -10546,7 +10546,7 @@
         <v>293</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C683" s="6">
         <v>11.25</v>
@@ -10560,7 +10560,7 @@
         <v>293</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C684" s="6">
         <v>11.25</v>
@@ -10569,17 +10569,17 @@
         <v>303</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A687" t="s">
-        <v>294</v>
-      </c>
-      <c r="B687" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C687" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D687" t="s">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>293</v>
+      </c>
+      <c r="B685" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C685" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D685" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10588,10 +10588,10 @@
         <v>294</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C688" s="6">
-        <v>10.19</v>
+        <v>3.36</v>
       </c>
       <c r="D688" t="s">
         <v>303</v>
@@ -10602,10 +10602,10 @@
         <v>294</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C689" s="6">
-        <v>14.4</v>
+        <v>10.19</v>
       </c>
       <c r="D689" t="s">
         <v>303</v>
@@ -10616,10 +10616,10 @@
         <v>294</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C690" s="6">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="D690" t="s">
         <v>303</v>
@@ -10630,10 +10630,10 @@
         <v>294</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C691" s="6">
-        <v>11.52</v>
+        <v>14.39</v>
       </c>
       <c r="D691" t="s">
         <v>303</v>
@@ -10644,10 +10644,10 @@
         <v>294</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C692" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D692" t="s">
         <v>303</v>
@@ -10658,7 +10658,7 @@
         <v>294</v>
       </c>
       <c r="B693" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C693" s="6">
         <v>12</v>
@@ -10672,7 +10672,7 @@
         <v>294</v>
       </c>
       <c r="B694" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C694" s="6">
         <v>12</v>
@@ -10681,60 +10681,18 @@
         <v>303</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A697" t="s">
-        <v>339</v>
-      </c>
-      <c r="B697" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C697" s="6">
-        <v>17.489999999999998</v>
-      </c>
-      <c r="D697" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A698" t="s">
-        <v>339</v>
-      </c>
-      <c r="B698" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C698" s="6">
-        <v>28.99</v>
-      </c>
-      <c r="D698" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A699" t="s">
-        <v>339</v>
-      </c>
-      <c r="B699" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C699" s="6">
-        <v>199.99</v>
-      </c>
-      <c r="D699" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A700" t="s">
-        <v>339</v>
-      </c>
-      <c r="B700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C700" s="6">
-        <v>359.99</v>
-      </c>
-      <c r="D700" t="s">
-        <v>142</v>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>294</v>
+      </c>
+      <c r="B695" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C695" s="6">
+        <v>12</v>
+      </c>
+      <c r="D695" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F471E4-A7BE-47A2-9699-FDFA73DFA3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEF9AA7-AD8E-48F8-9572-C7AE19FF2BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="0" windowWidth="38400" windowHeight="21150" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="47805" yWindow="-16320" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="342">
   <si>
     <t>BGC10</t>
   </si>
@@ -1045,6 +1045,12 @@
   </si>
   <si>
     <t>BL25</t>
+  </si>
+  <si>
+    <t>Display SKU</t>
+  </si>
+  <si>
+    <t>NIBAN4LBSHAKER</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K695"/>
+  <dimension ref="A1:K696"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -1468,6 +1474,9 @@
       <c r="D1" t="s">
         <v>135</v>
       </c>
+      <c r="E1" s="3" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -5193,7 +5202,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>157</v>
       </c>
@@ -5207,208 +5216,211 @@
         <v>146</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>157</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>93</v>
+        <v>341</v>
       </c>
       <c r="C258" s="6">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="D258" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>157</v>
       </c>
-      <c r="B259" s="3">
-        <v>4430</v>
+      <c r="B259" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C259" s="6">
-        <v>12.6</v>
+        <v>60</v>
       </c>
       <c r="D259" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>157</v>
       </c>
       <c r="B260" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C260" s="6">
-        <v>14.53</v>
+        <v>12.6</v>
       </c>
       <c r="D260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>157</v>
       </c>
       <c r="B261" s="3">
-        <v>4642</v>
+        <v>4442</v>
       </c>
       <c r="C261" s="6">
-        <v>20.8</v>
+        <v>14.53</v>
       </c>
       <c r="D261" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>157</v>
       </c>
       <c r="B262" s="3">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C262" s="6">
-        <v>27</v>
+        <v>20.8</v>
       </c>
       <c r="D262" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>157</v>
       </c>
       <c r="B263" s="3">
-        <v>6642</v>
+        <v>4660</v>
       </c>
       <c r="C263" s="6">
-        <v>18.52</v>
+        <v>27</v>
       </c>
       <c r="D263" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>157</v>
       </c>
-      <c r="B264" s="3" t="s">
-        <v>99</v>
+      <c r="B264" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C264" s="6">
+        <v>18.52</v>
       </c>
       <c r="D264" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>157</v>
       </c>
-      <c r="B265" s="3">
-        <v>6660</v>
-      </c>
-      <c r="C265" s="6">
-        <v>27.05</v>
+      <c r="B265" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D265" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>157</v>
       </c>
-      <c r="B266" s="3" t="s">
-        <v>100</v>
+      <c r="B266" s="3">
+        <v>6660</v>
       </c>
       <c r="C266" s="6">
-        <v>160</v>
+        <v>27.05</v>
       </c>
       <c r="D266" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>157</v>
       </c>
-      <c r="B267" s="3">
-        <v>8860</v>
+      <c r="B267" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C267" s="6">
-        <v>63.9</v>
+        <v>160</v>
       </c>
       <c r="D267" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>157</v>
       </c>
-      <c r="B268" s="3" t="s">
-        <v>319</v>
+      <c r="B268" s="3">
+        <v>8860</v>
       </c>
       <c r="C268" s="6">
-        <v>92</v>
+        <v>63.9</v>
       </c>
       <c r="D268" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>157</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C269" s="6">
-        <v>22.75</v>
+        <v>92</v>
       </c>
       <c r="D269" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>157</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C270" s="6">
-        <v>18.25</v>
+        <v>22.75</v>
       </c>
       <c r="D270" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>157</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C271" s="6">
-        <v>115</v>
+        <v>18.25</v>
       </c>
       <c r="D271" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>157</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C272" s="6">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="D272" t="s">
         <v>309</v>
@@ -5419,13 +5431,13 @@
         <v>157</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>104</v>
+        <v>307</v>
       </c>
       <c r="C273" s="6">
-        <v>41.5</v>
+        <v>227</v>
       </c>
       <c r="D273" t="s">
-        <v>150</v>
+        <v>309</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -5433,13 +5445,13 @@
         <v>157</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>277</v>
+        <v>104</v>
       </c>
       <c r="C274" s="6">
-        <v>11</v>
+        <v>41.5</v>
       </c>
       <c r="D274" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -5447,10 +5459,10 @@
         <v>157</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C275" s="6">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D275" t="s">
         <v>173</v>
@@ -5461,10 +5473,10 @@
         <v>157</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C276" s="6">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="D276" t="s">
         <v>173</v>
@@ -5475,13 +5487,13 @@
         <v>157</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>118</v>
+        <v>279</v>
       </c>
       <c r="C277" s="6">
-        <v>23.15</v>
+        <v>78</v>
       </c>
       <c r="D277" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -5489,10 +5501,10 @@
         <v>157</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C278" s="6">
-        <v>42.65</v>
+        <v>23.15</v>
       </c>
       <c r="D278" t="s">
         <v>153</v>
@@ -5503,10 +5515,10 @@
         <v>157</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C279" s="6">
-        <v>82</v>
+        <v>42.65</v>
       </c>
       <c r="D279" t="s">
         <v>153</v>
@@ -5517,10 +5529,10 @@
         <v>157</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C280" s="6">
-        <v>33.5</v>
+        <v>82</v>
       </c>
       <c r="D280" t="s">
         <v>153</v>
@@ -5531,10 +5543,10 @@
         <v>157</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C281" s="6">
-        <v>60.9</v>
+        <v>33.5</v>
       </c>
       <c r="D281" t="s">
         <v>153</v>
@@ -5545,10 +5557,10 @@
         <v>157</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C282" s="6">
-        <v>118</v>
+        <v>60.9</v>
       </c>
       <c r="D282" t="s">
         <v>153</v>
@@ -5559,10 +5571,10 @@
         <v>157</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C283" s="6">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D283" t="s">
         <v>153</v>
@@ -5573,7 +5585,7 @@
         <v>157</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C284" s="6">
         <v>16</v>
@@ -5587,10 +5599,10 @@
         <v>157</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C285" s="6">
-        <v>21.32</v>
+        <v>16</v>
       </c>
       <c r="D285" t="s">
         <v>153</v>
@@ -5601,13 +5613,13 @@
         <v>157</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="C286" s="6">
-        <v>30</v>
+        <v>21.32</v>
       </c>
       <c r="D286" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -5615,10 +5627,10 @@
         <v>157</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C287" s="6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D287" t="s">
         <v>174</v>
@@ -5629,10 +5641,10 @@
         <v>157</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C288" s="6">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D288" t="s">
         <v>174</v>
@@ -5643,10 +5655,10 @@
         <v>157</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C289" s="6">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D289" t="s">
         <v>174</v>
@@ -5657,10 +5669,10 @@
         <v>157</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C290" s="6">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D290" t="s">
         <v>174</v>
@@ -5671,10 +5683,10 @@
         <v>157</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C291" s="6">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="D291" t="s">
         <v>174</v>
@@ -5685,27 +5697,27 @@
         <v>157</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C292" s="6">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D292" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>175</v>
-      </c>
-      <c r="B297" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C297" s="6">
-        <v>9.6</v>
-      </c>
-      <c r="D297" t="s">
-        <v>136</v>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>157</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C293" s="6">
+        <v>126</v>
+      </c>
+      <c r="D293" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -5713,10 +5725,10 @@
         <v>175</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C298" s="6">
-        <v>9.5399999999999991</v>
+        <v>9.6</v>
       </c>
       <c r="D298" t="s">
         <v>136</v>
@@ -5727,10 +5739,10 @@
         <v>175</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C299" s="6">
-        <v>9.6</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="D299" t="s">
         <v>136</v>
@@ -5741,10 +5753,10 @@
         <v>175</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="C300" s="6">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="D300" t="s">
         <v>136</v>
@@ -5755,10 +5767,10 @@
         <v>175</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="C301" s="6">
-        <v>14.99</v>
+        <v>11.5</v>
       </c>
       <c r="D301" t="s">
         <v>136</v>
@@ -5769,10 +5781,10 @@
         <v>175</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C302" s="6">
-        <v>16.5</v>
+        <v>14.99</v>
       </c>
       <c r="D302" t="s">
         <v>136</v>
@@ -5783,10 +5795,10 @@
         <v>175</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C303" s="6">
-        <v>17.97</v>
+        <v>16.5</v>
       </c>
       <c r="D303" t="s">
         <v>136</v>
@@ -5797,10 +5809,10 @@
         <v>175</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>159</v>
+        <v>5</v>
       </c>
       <c r="C304" s="6">
-        <v>20</v>
+        <v>17.97</v>
       </c>
       <c r="D304" t="s">
         <v>136</v>
@@ -5811,10 +5823,10 @@
         <v>175</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C305" s="6">
-        <v>28.5</v>
+        <v>20</v>
       </c>
       <c r="D305" t="s">
         <v>136</v>
@@ -5825,10 +5837,10 @@
         <v>175</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C306" s="6">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="D306" t="s">
         <v>136</v>
@@ -5839,7 +5851,7 @@
         <v>175</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C307" s="6">
         <v>30</v>
@@ -5853,10 +5865,10 @@
         <v>175</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C308" s="6">
-        <v>36.5</v>
+        <v>30</v>
       </c>
       <c r="D308" t="s">
         <v>136</v>
@@ -5867,10 +5879,10 @@
         <v>175</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>339</v>
+        <v>163</v>
       </c>
       <c r="C309" s="6">
-        <v>16.5</v>
+        <v>36.5</v>
       </c>
       <c r="D309" t="s">
         <v>136</v>
@@ -5880,14 +5892,14 @@
       <c r="A310" t="s">
         <v>175</v>
       </c>
-      <c r="B310" t="s">
-        <v>244</v>
+      <c r="B310" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="C310" s="6">
-        <v>42.9</v>
+        <v>16.5</v>
       </c>
       <c r="D310" t="s">
-        <v>268</v>
+        <v>136</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -5895,7 +5907,7 @@
         <v>175</v>
       </c>
       <c r="B311" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C311" s="6">
         <v>42.9</v>
@@ -5908,14 +5920,14 @@
       <c r="A312" t="s">
         <v>175</v>
       </c>
-      <c r="B312" s="3" t="s">
-        <v>26</v>
+      <c r="B312" t="s">
+        <v>247</v>
       </c>
       <c r="C312" s="6">
-        <v>98.5</v>
+        <v>42.9</v>
       </c>
       <c r="D312" t="s">
-        <v>142</v>
+        <v>268</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -5923,10 +5935,10 @@
         <v>175</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C313" s="6">
-        <v>105</v>
+        <v>98.5</v>
       </c>
       <c r="D313" t="s">
         <v>142</v>
@@ -5937,10 +5949,10 @@
         <v>175</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C314" s="6">
-        <v>98.5</v>
+        <v>105</v>
       </c>
       <c r="D314" t="s">
         <v>142</v>
@@ -5951,10 +5963,10 @@
         <v>175</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C315" s="6">
-        <v>105</v>
+        <v>98.5</v>
       </c>
       <c r="D315" t="s">
         <v>142</v>
@@ -5965,10 +5977,10 @@
         <v>175</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C316" s="6">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="D316" t="s">
         <v>142</v>
@@ -5979,10 +5991,10 @@
         <v>175</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C317" s="6">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="D317" t="s">
         <v>142</v>
@@ -5993,10 +6005,10 @@
         <v>175</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C318" s="6">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="D318" t="s">
         <v>142</v>
@@ -6007,10 +6019,10 @@
         <v>175</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C319" s="6">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="D319" t="s">
         <v>142</v>
@@ -6021,10 +6033,10 @@
         <v>175</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C320" s="6">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D320" t="s">
         <v>142</v>
@@ -6035,10 +6047,10 @@
         <v>175</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C321" s="6">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="D321" t="s">
         <v>142</v>
@@ -6049,10 +6061,10 @@
         <v>175</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="C322" s="6">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D322" t="s">
         <v>142</v>
@@ -6063,10 +6075,10 @@
         <v>175</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="C323" s="6">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="D323" t="s">
         <v>142</v>
@@ -6077,13 +6089,13 @@
         <v>175</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C324" s="6">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D324" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -6091,13 +6103,13 @@
         <v>175</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C325" s="6">
-        <v>475</v>
+        <v>18</v>
       </c>
       <c r="D325" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6105,10 +6117,13 @@
         <v>175</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>338</v>
+        <v>47</v>
+      </c>
+      <c r="C326" s="6">
+        <v>475</v>
       </c>
       <c r="D326" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -6116,10 +6131,7 @@
         <v>175</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C327" s="6">
-        <v>15.58</v>
+        <v>338</v>
       </c>
       <c r="D327" t="s">
         <v>144</v>
@@ -6130,13 +6142,13 @@
         <v>175</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>55</v>
+        <v>337</v>
       </c>
       <c r="C328" s="6">
-        <v>12</v>
+        <v>15.58</v>
       </c>
       <c r="D328" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -6144,10 +6156,10 @@
         <v>175</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C329" s="6">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D329" t="s">
         <v>145</v>
@@ -6158,10 +6170,10 @@
         <v>175</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C330" s="6">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D330" t="s">
         <v>145</v>
@@ -6172,10 +6184,10 @@
         <v>175</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C331" s="6">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D331" t="s">
         <v>145</v>
@@ -6185,11 +6197,11 @@
       <c r="A332" t="s">
         <v>175</v>
       </c>
-      <c r="B332" t="s">
-        <v>255</v>
+      <c r="B332" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C332" s="6">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="D332" t="s">
         <v>145</v>
@@ -6200,10 +6212,10 @@
         <v>175</v>
       </c>
       <c r="B333" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C333" s="6">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D333" t="s">
         <v>145</v>
@@ -6214,10 +6226,10 @@
         <v>175</v>
       </c>
       <c r="B334" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C334" s="6">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="D334" t="s">
         <v>145</v>
@@ -6227,14 +6239,14 @@
       <c r="A335" t="s">
         <v>175</v>
       </c>
-      <c r="B335" s="3" t="s">
-        <v>59</v>
+      <c r="B335" t="s">
+        <v>257</v>
       </c>
       <c r="C335" s="6">
-        <v>33.5</v>
+        <v>102</v>
       </c>
       <c r="D335" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -6242,222 +6254,225 @@
         <v>175</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C336" s="6">
-        <v>15.1</v>
+        <v>33.5</v>
       </c>
       <c r="D336" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>175</v>
       </c>
-      <c r="B337" t="s">
-        <v>61</v>
+      <c r="B337" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C337" s="6">
-        <v>38.28</v>
+        <v>15.1</v>
       </c>
       <c r="D337" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>175</v>
       </c>
-      <c r="B338" s="3" t="s">
-        <v>62</v>
+      <c r="B338" t="s">
+        <v>61</v>
       </c>
       <c r="C338" s="6">
-        <v>22.36</v>
+        <v>38.28</v>
       </c>
       <c r="D338" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>175</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="C339" s="6">
-        <v>23.68</v>
+        <v>22.36</v>
       </c>
       <c r="D339" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>175</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>65</v>
+        <v>176</v>
       </c>
       <c r="C340" s="6">
-        <v>10</v>
+        <v>23.68</v>
       </c>
       <c r="D340" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E340" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>175</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="C341" s="6">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="D341" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>175</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C342" s="6">
-        <v>225</v>
+        <v>87</v>
       </c>
       <c r="D342" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>175</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C343" s="6">
-        <v>421.08</v>
+        <v>225</v>
       </c>
       <c r="D343" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>175</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>92</v>
+        <v>179</v>
+      </c>
+      <c r="C344" s="6">
+        <v>421.08</v>
       </c>
       <c r="D344" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>175</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C345" s="6">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="D345" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>175</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="C346" s="6">
+        <v>60</v>
       </c>
       <c r="D346" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>175</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D347" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>175</v>
       </c>
-      <c r="B348" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C348" s="6">
-        <v>15.25</v>
+      <c r="B348" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D348" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>175</v>
       </c>
       <c r="B349" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C349" s="6">
-        <v>18.899999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="D349" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>175</v>
       </c>
-      <c r="B350" s="3" t="s">
-        <v>96</v>
+      <c r="B350" s="3">
+        <v>4442</v>
       </c>
       <c r="C350" s="6">
-        <v>193</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D350" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>175</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="C351" s="6">
+        <v>193</v>
       </c>
       <c r="D351" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>175</v>
       </c>
-      <c r="B352" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C352" s="6">
-        <v>20.8</v>
+      <c r="B352" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D352" t="s">
         <v>148</v>
@@ -6467,8 +6482,11 @@
       <c r="A353" t="s">
         <v>175</v>
       </c>
-      <c r="B353" s="3" t="s">
-        <v>98</v>
+      <c r="B353" s="3">
+        <v>4642</v>
+      </c>
+      <c r="C353" s="6">
+        <v>20.8</v>
       </c>
       <c r="D353" t="s">
         <v>148</v>
@@ -6478,11 +6496,8 @@
       <c r="A354" t="s">
         <v>175</v>
       </c>
-      <c r="B354" s="3">
-        <v>4660</v>
-      </c>
-      <c r="C354" s="6">
-        <v>24.7</v>
+      <c r="B354" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="D354" t="s">
         <v>148</v>
@@ -6493,10 +6508,10 @@
         <v>175</v>
       </c>
       <c r="B355" s="3">
-        <v>6642</v>
+        <v>4660</v>
       </c>
       <c r="C355" s="6">
-        <v>26.8</v>
+        <v>24.7</v>
       </c>
       <c r="D355" t="s">
         <v>148</v>
@@ -6506,11 +6521,11 @@
       <c r="A356" t="s">
         <v>175</v>
       </c>
-      <c r="B356" s="3" t="s">
-        <v>99</v>
+      <c r="B356" s="3">
+        <v>6642</v>
       </c>
       <c r="C356" s="6">
-        <v>115</v>
+        <v>26.8</v>
       </c>
       <c r="D356" t="s">
         <v>148</v>
@@ -6520,11 +6535,11 @@
       <c r="A357" t="s">
         <v>175</v>
       </c>
-      <c r="B357" s="3">
-        <v>6660</v>
+      <c r="B357" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C357" s="6">
-        <v>27.05</v>
+        <v>115</v>
       </c>
       <c r="D357" t="s">
         <v>148</v>
@@ -6534,11 +6549,11 @@
       <c r="A358" t="s">
         <v>175</v>
       </c>
-      <c r="B358" s="3" t="s">
-        <v>100</v>
+      <c r="B358" s="3">
+        <v>6660</v>
       </c>
       <c r="C358" s="6">
-        <v>160</v>
+        <v>27.05</v>
       </c>
       <c r="D358" t="s">
         <v>148</v>
@@ -6549,13 +6564,13 @@
         <v>175</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="C359" s="6">
-        <v>30.5</v>
+        <v>160</v>
       </c>
       <c r="D359" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -6563,13 +6578,13 @@
         <v>175</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>271</v>
+        <v>180</v>
       </c>
       <c r="C360" s="6">
-        <v>12.75</v>
+        <v>30.5</v>
       </c>
       <c r="D360" t="s">
-        <v>270</v>
+        <v>149</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -6577,7 +6592,7 @@
         <v>175</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C361" s="6">
         <v>12.75</v>
@@ -6591,10 +6606,10 @@
         <v>175</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C362" s="6">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="D362" t="s">
         <v>270</v>
@@ -6605,10 +6620,10 @@
         <v>175</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C363" s="6">
-        <v>10.3</v>
+        <v>13.25</v>
       </c>
       <c r="D363" t="s">
         <v>270</v>
@@ -6619,10 +6634,10 @@
         <v>175</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C364" s="6">
-        <v>11.85</v>
+        <v>10.3</v>
       </c>
       <c r="D364" t="s">
         <v>270</v>
@@ -6633,10 +6648,10 @@
         <v>175</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C365" s="6">
-        <v>12.75</v>
+        <v>11.85</v>
       </c>
       <c r="D365" t="s">
         <v>270</v>
@@ -6647,10 +6662,10 @@
         <v>175</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C366" s="6">
-        <v>10.3</v>
+        <v>12.75</v>
       </c>
       <c r="D366" t="s">
         <v>270</v>
@@ -6661,10 +6676,10 @@
         <v>175</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C367" s="6">
-        <v>13.25</v>
+        <v>10.3</v>
       </c>
       <c r="D367" t="s">
         <v>270</v>
@@ -6675,10 +6690,10 @@
         <v>175</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C368" s="6">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
       <c r="D368" t="s">
         <v>270</v>
@@ -6689,13 +6704,13 @@
         <v>175</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>107</v>
+        <v>272</v>
       </c>
       <c r="C369" s="6">
-        <v>21.5</v>
+        <v>12.75</v>
       </c>
       <c r="D369" t="s">
-        <v>152</v>
+        <v>270</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -6703,10 +6718,10 @@
         <v>175</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C370" s="6">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="D370" t="s">
         <v>152</v>
@@ -6717,10 +6732,10 @@
         <v>175</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C371" s="6">
-        <v>10.5</v>
+        <v>22.5</v>
       </c>
       <c r="D371" t="s">
         <v>152</v>
@@ -6731,7 +6746,7 @@
         <v>175</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C372" s="6">
         <v>10.5</v>
@@ -6745,7 +6760,7 @@
         <v>175</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C373" s="6">
         <v>10.5</v>
@@ -6759,10 +6774,13 @@
         <v>175</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>277</v>
+        <v>117</v>
+      </c>
+      <c r="C374" s="6">
+        <v>10.5</v>
       </c>
       <c r="D374" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -6770,10 +6788,7 @@
         <v>175</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C375" s="6">
-        <v>23</v>
+        <v>277</v>
       </c>
       <c r="D375" t="s">
         <v>173</v>
@@ -6784,7 +6799,10 @@
         <v>175</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
+      </c>
+      <c r="C376" s="6">
+        <v>23</v>
       </c>
       <c r="D376" t="s">
         <v>173</v>
@@ -6795,13 +6813,10 @@
         <v>175</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C377" s="6">
-        <v>23.15</v>
+        <v>279</v>
       </c>
       <c r="D377" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -6809,10 +6824,10 @@
         <v>175</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C378" s="6">
-        <v>42.65</v>
+        <v>23.15</v>
       </c>
       <c r="D378" t="s">
         <v>153</v>
@@ -6823,10 +6838,10 @@
         <v>175</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C379" s="6">
-        <v>82</v>
+        <v>42.65</v>
       </c>
       <c r="D379" t="s">
         <v>153</v>
@@ -6837,10 +6852,10 @@
         <v>175</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C380" s="6">
-        <v>33.5</v>
+        <v>82</v>
       </c>
       <c r="D380" t="s">
         <v>153</v>
@@ -6851,10 +6866,10 @@
         <v>175</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C381" s="6">
-        <v>60.9</v>
+        <v>33.5</v>
       </c>
       <c r="D381" t="s">
         <v>153</v>
@@ -6865,10 +6880,10 @@
         <v>175</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C382" s="6">
-        <v>118</v>
+        <v>60.9</v>
       </c>
       <c r="D382" t="s">
         <v>153</v>
@@ -6879,10 +6894,10 @@
         <v>175</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C383" s="6">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D383" t="s">
         <v>153</v>
@@ -6893,7 +6908,7 @@
         <v>175</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C384" s="6">
         <v>16</v>
@@ -6907,10 +6922,10 @@
         <v>175</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C385" s="6">
-        <v>21.32</v>
+        <v>16</v>
       </c>
       <c r="D385" t="s">
         <v>153</v>
@@ -6921,13 +6936,13 @@
         <v>175</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C386" s="6">
-        <v>26</v>
+        <v>21.32</v>
       </c>
       <c r="D386" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -6935,7 +6950,10 @@
         <v>175</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
+      </c>
+      <c r="C387" s="6">
+        <v>26</v>
       </c>
       <c r="D387" t="s">
         <v>154</v>
@@ -6946,10 +6964,7 @@
         <v>175</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C388" s="6">
-        <v>13.42</v>
+        <v>128</v>
       </c>
       <c r="D388" t="s">
         <v>154</v>
@@ -6960,7 +6975,10 @@
         <v>175</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="C389" s="6">
+        <v>13.42</v>
       </c>
       <c r="D389" t="s">
         <v>154</v>
@@ -6971,7 +6989,7 @@
         <v>175</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D390" t="s">
         <v>154</v>
@@ -6982,27 +7000,24 @@
         <v>175</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C391" s="6">
-        <v>9.5399999999999991</v>
+        <v>131</v>
       </c>
       <c r="D391" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A394" t="s">
-        <v>181</v>
-      </c>
-      <c r="B394" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C394" s="6">
-        <v>14.5</v>
-      </c>
-      <c r="D394" t="s">
-        <v>320</v>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>175</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C392" s="6">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="D392" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -7010,13 +7025,13 @@
         <v>181</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="C395" s="6">
-        <v>24.99</v>
+        <v>14.5</v>
       </c>
       <c r="D395" t="s">
-        <v>138</v>
+        <v>320</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -7024,10 +7039,10 @@
         <v>181</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C396" s="6">
-        <v>34.99</v>
+        <v>24.99</v>
       </c>
       <c r="D396" t="s">
         <v>138</v>
@@ -7038,13 +7053,13 @@
         <v>181</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C397" s="6">
-        <v>19.989999999999998</v>
+        <v>34.99</v>
       </c>
       <c r="D397" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -7052,10 +7067,10 @@
         <v>181</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C398" s="6">
-        <v>29.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D398" t="s">
         <v>140</v>
@@ -7066,13 +7081,13 @@
         <v>181</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C399" s="6">
-        <v>189.99</v>
+        <v>29.99</v>
       </c>
       <c r="D399" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
@@ -7080,10 +7095,10 @@
         <v>181</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C400" s="6">
-        <v>229.99</v>
+        <v>189.99</v>
       </c>
       <c r="D400" t="s">
         <v>142</v>
@@ -7094,10 +7109,10 @@
         <v>181</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>182</v>
+        <v>29</v>
       </c>
       <c r="C401" s="6">
-        <v>299.99</v>
+        <v>229.99</v>
       </c>
       <c r="D401" t="s">
         <v>142</v>
@@ -7108,10 +7123,10 @@
         <v>181</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="C402" s="6">
-        <v>189.99</v>
+        <v>299.99</v>
       </c>
       <c r="D402" t="s">
         <v>142</v>
@@ -7122,10 +7137,10 @@
         <v>181</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C403" s="6">
-        <v>229</v>
+        <v>189.99</v>
       </c>
       <c r="D403" t="s">
         <v>142</v>
@@ -7136,10 +7151,10 @@
         <v>181</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="C404" s="6">
-        <v>299.99</v>
+        <v>229</v>
       </c>
       <c r="D404" t="s">
         <v>142</v>
@@ -7150,10 +7165,10 @@
         <v>181</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="C405" s="6">
-        <v>309</v>
+        <v>299.99</v>
       </c>
       <c r="D405" t="s">
         <v>142</v>
@@ -7164,10 +7179,10 @@
         <v>181</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C406" s="6">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="D406" t="s">
         <v>142</v>
@@ -7178,10 +7193,10 @@
         <v>181</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C407" s="6">
-        <v>409</v>
+        <v>345</v>
       </c>
       <c r="D407" t="s">
         <v>142</v>
@@ -7192,10 +7207,10 @@
         <v>181</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C408" s="6">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="D408" t="s">
         <v>142</v>
@@ -7206,10 +7221,10 @@
         <v>181</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>184</v>
+        <v>33</v>
       </c>
       <c r="C409" s="6">
-        <v>389.99</v>
+        <v>389</v>
       </c>
       <c r="D409" t="s">
         <v>142</v>
@@ -7220,10 +7235,10 @@
         <v>181</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="C410" s="6">
-        <v>399.99</v>
+        <v>389.99</v>
       </c>
       <c r="D410" t="s">
         <v>142</v>
@@ -7234,7 +7249,7 @@
         <v>181</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>185</v>
+        <v>34</v>
       </c>
       <c r="C411" s="6">
         <v>399.99</v>
@@ -7248,10 +7263,10 @@
         <v>181</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="C412" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D412" t="s">
         <v>142</v>
@@ -7262,7 +7277,10 @@
         <v>181</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="C413" s="6">
+        <v>89.23</v>
       </c>
       <c r="D413" t="s">
         <v>142</v>
@@ -7273,10 +7291,7 @@
         <v>181</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C414" s="6">
-        <v>219.99</v>
+        <v>36</v>
       </c>
       <c r="D414" t="s">
         <v>142</v>
@@ -7287,10 +7302,10 @@
         <v>181</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="C415" s="6">
-        <v>429</v>
+        <v>219.99</v>
       </c>
       <c r="D415" t="s">
         <v>142</v>
@@ -7301,10 +7316,10 @@
         <v>181</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C416" s="6">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D416" t="s">
         <v>142</v>
@@ -7315,10 +7330,10 @@
         <v>181</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C417" s="6">
-        <v>199</v>
+        <v>439</v>
       </c>
       <c r="D417" t="s">
         <v>142</v>
@@ -7329,10 +7344,10 @@
         <v>181</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C418" s="6">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="D418" t="s">
         <v>142</v>
@@ -7343,10 +7358,10 @@
         <v>181</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C419" s="6">
-        <v>670</v>
+        <v>249</v>
       </c>
       <c r="D419" t="s">
         <v>142</v>
@@ -7357,10 +7372,10 @@
         <v>181</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C420" s="6">
-        <v>49.99</v>
+        <v>670</v>
       </c>
       <c r="D420" t="s">
         <v>142</v>
@@ -7371,7 +7386,7 @@
         <v>181</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C421" s="6">
         <v>49.99</v>
@@ -7385,13 +7400,13 @@
         <v>181</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>335</v>
+        <v>192</v>
       </c>
       <c r="C422" s="6">
-        <v>15.99</v>
+        <v>49.99</v>
       </c>
       <c r="D422" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -7399,10 +7414,10 @@
         <v>181</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C423" s="6">
-        <v>29.99</v>
+        <v>15.99</v>
       </c>
       <c r="D423" t="s">
         <v>144</v>
@@ -7413,10 +7428,10 @@
         <v>181</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C424" s="6">
-        <v>16.989999999999998</v>
+        <v>29.99</v>
       </c>
       <c r="D424" t="s">
         <v>144</v>
@@ -7427,10 +7442,10 @@
         <v>181</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C425" s="6">
-        <v>29.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D425" t="s">
         <v>144</v>
@@ -7441,10 +7456,10 @@
         <v>181</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>193</v>
+        <v>334</v>
       </c>
       <c r="C426" s="6">
-        <v>11.49</v>
+        <v>29.99</v>
       </c>
       <c r="D426" t="s">
         <v>144</v>
@@ -7455,10 +7470,10 @@
         <v>181</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C427" s="6">
-        <v>18.95</v>
+        <v>11.49</v>
       </c>
       <c r="D427" t="s">
         <v>144</v>
@@ -7469,10 +7484,10 @@
         <v>181</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C428" s="6">
-        <v>39.99</v>
+        <v>18.95</v>
       </c>
       <c r="D428" t="s">
         <v>144</v>
@@ -7482,11 +7497,11 @@
       <c r="A429" t="s">
         <v>181</v>
       </c>
-      <c r="B429" s="3">
-        <v>6102</v>
+      <c r="B429" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="C429" s="6">
-        <v>44.5</v>
+        <v>39.99</v>
       </c>
       <c r="D429" t="s">
         <v>144</v>
@@ -7496,11 +7511,11 @@
       <c r="A430" t="s">
         <v>181</v>
       </c>
-      <c r="B430" s="3" t="s">
-        <v>196</v>
+      <c r="B430" s="3">
+        <v>6102</v>
       </c>
       <c r="C430" s="6">
-        <v>112</v>
+        <v>44.5</v>
       </c>
       <c r="D430" t="s">
         <v>144</v>
@@ -7511,10 +7526,10 @@
         <v>181</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C431" s="6">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="D431" t="s">
         <v>144</v>
@@ -7525,7 +7540,7 @@
         <v>181</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C432" s="6">
         <v>139</v>
@@ -7539,7 +7554,10 @@
         <v>181</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="C433" s="6">
+        <v>139</v>
       </c>
       <c r="D433" t="s">
         <v>144</v>
@@ -7550,7 +7568,7 @@
         <v>181</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D434" t="s">
         <v>144</v>
@@ -7561,10 +7579,7 @@
         <v>181</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C435" s="6">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D435" t="s">
         <v>144</v>
@@ -7575,7 +7590,10 @@
         <v>181</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
+      </c>
+      <c r="C436" s="6">
+        <v>209</v>
       </c>
       <c r="D436" t="s">
         <v>144</v>
@@ -7586,7 +7604,7 @@
         <v>181</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D437" t="s">
         <v>144</v>
@@ -7597,10 +7615,7 @@
         <v>181</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C438" s="6">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D438" t="s">
         <v>144</v>
@@ -7611,10 +7626,10 @@
         <v>181</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C439" s="6">
-        <v>299.99</v>
+        <v>179</v>
       </c>
       <c r="D439" t="s">
         <v>144</v>
@@ -7625,10 +7640,10 @@
         <v>181</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C440" s="6">
-        <v>220</v>
+        <v>299.99</v>
       </c>
       <c r="D440" t="s">
         <v>144</v>
@@ -7639,10 +7654,10 @@
         <v>181</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C441" s="6">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="D441" t="s">
         <v>144</v>
@@ -7653,10 +7668,10 @@
         <v>181</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C442" s="6">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D442" t="s">
         <v>144</v>
@@ -7667,10 +7682,10 @@
         <v>181</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C443" s="6">
-        <v>399</v>
+        <v>240</v>
       </c>
       <c r="D443" t="s">
         <v>144</v>
@@ -7681,10 +7696,10 @@
         <v>181</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C444" s="6">
-        <v>209</v>
+        <v>399</v>
       </c>
       <c r="D444" t="s">
         <v>144</v>
@@ -7695,10 +7710,10 @@
         <v>181</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C445" s="6">
-        <v>345</v>
+        <v>209</v>
       </c>
       <c r="D445" t="s">
         <v>144</v>
@@ -7709,10 +7724,10 @@
         <v>181</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C446" s="6">
-        <v>209</v>
+        <v>345</v>
       </c>
       <c r="D446" t="s">
         <v>144</v>
@@ -7723,10 +7738,10 @@
         <v>181</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C447" s="6">
-        <v>369</v>
+        <v>209</v>
       </c>
       <c r="D447" t="s">
         <v>144</v>
@@ -7737,10 +7752,10 @@
         <v>181</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C448" s="6">
-        <v>315</v>
+        <v>369</v>
       </c>
       <c r="D448" t="s">
         <v>144</v>
@@ -7751,10 +7766,10 @@
         <v>181</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C449" s="6">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="D449" t="s">
         <v>144</v>
@@ -7765,10 +7780,10 @@
         <v>181</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C450" s="6">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="D450" t="s">
         <v>144</v>
@@ -7779,10 +7794,10 @@
         <v>181</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C451" s="6">
-        <v>420</v>
+        <v>251</v>
       </c>
       <c r="D451" t="s">
         <v>144</v>
@@ -7793,10 +7808,10 @@
         <v>181</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C452" s="6">
-        <v>315</v>
+        <v>420</v>
       </c>
       <c r="D452" t="s">
         <v>144</v>
@@ -7807,10 +7822,10 @@
         <v>181</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C453" s="6">
-        <v>365</v>
+        <v>315</v>
       </c>
       <c r="D453" t="s">
         <v>144</v>
@@ -7821,10 +7836,10 @@
         <v>181</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C454" s="6">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="D454" t="s">
         <v>144</v>
@@ -7835,13 +7850,13 @@
         <v>181</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>54</v>
+        <v>220</v>
       </c>
       <c r="C455" s="6">
-        <v>55.99</v>
+        <v>285</v>
       </c>
       <c r="D455" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
@@ -7849,10 +7864,10 @@
         <v>181</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C456" s="6">
-        <v>39.99</v>
+        <v>55.99</v>
       </c>
       <c r="D456" t="s">
         <v>145</v>
@@ -7863,10 +7878,10 @@
         <v>181</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C457" s="6">
-        <v>68</v>
+        <v>39.99</v>
       </c>
       <c r="D457" t="s">
         <v>145</v>
@@ -7877,10 +7892,10 @@
         <v>181</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C458" s="6">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="D458" t="s">
         <v>145</v>
@@ -7891,10 +7906,10 @@
         <v>181</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>255</v>
+        <v>58</v>
       </c>
       <c r="C459" s="6">
-        <v>30.99</v>
+        <v>129</v>
       </c>
       <c r="D459" t="s">
         <v>145</v>
@@ -7905,10 +7920,10 @@
         <v>181</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C460" s="6">
-        <v>42.99</v>
+        <v>30.99</v>
       </c>
       <c r="D460" t="s">
         <v>145</v>
@@ -7919,10 +7934,10 @@
         <v>181</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C461" s="6">
-        <v>159</v>
+        <v>42.99</v>
       </c>
       <c r="D461" t="s">
         <v>145</v>
@@ -7933,10 +7948,10 @@
         <v>181</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C462" s="6">
-        <v>49.99</v>
+        <v>159</v>
       </c>
       <c r="D462" t="s">
         <v>145</v>
@@ -7947,10 +7962,10 @@
         <v>181</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C463" s="6">
-        <v>129</v>
+        <v>49.99</v>
       </c>
       <c r="D463" t="s">
         <v>145</v>
@@ -7961,13 +7976,13 @@
         <v>181</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>59</v>
+        <v>275</v>
       </c>
       <c r="C464" s="6">
-        <v>47.99</v>
+        <v>129</v>
       </c>
       <c r="D464" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -7975,13 +7990,13 @@
         <v>181</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>221</v>
+        <v>59</v>
       </c>
       <c r="C465" s="6">
-        <v>34.99</v>
+        <v>47.99</v>
       </c>
       <c r="D465" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -7989,10 +8004,10 @@
         <v>181</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="C466" s="6">
-        <v>89.99</v>
+        <v>34.99</v>
       </c>
       <c r="D466" t="s">
         <v>172</v>
@@ -8003,13 +8018,13 @@
         <v>181</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="C467" s="6">
-        <v>45</v>
+        <v>89.99</v>
       </c>
       <c r="D467" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -8017,10 +8032,10 @@
         <v>181</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="C468" s="6">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D468" t="s">
         <v>149</v>
@@ -8031,10 +8046,10 @@
         <v>181</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C469" s="6">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D469" t="s">
         <v>149</v>
@@ -8045,13 +8060,13 @@
         <v>181</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="C470" s="6">
-        <v>79.989999999999995</v>
+        <v>125</v>
       </c>
       <c r="D470" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -8059,13 +8074,13 @@
         <v>181</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="C471" s="6">
-        <v>7.95</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D471" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -8073,10 +8088,10 @@
         <v>181</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C472" s="6">
-        <v>18.95</v>
+        <v>7.95</v>
       </c>
       <c r="D472" t="s">
         <v>173</v>
@@ -8087,10 +8102,10 @@
         <v>181</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C473" s="6">
-        <v>36.950000000000003</v>
+        <v>18.95</v>
       </c>
       <c r="D473" t="s">
         <v>173</v>
@@ -8101,13 +8116,13 @@
         <v>181</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>127</v>
+        <v>278</v>
       </c>
       <c r="C474" s="6">
-        <v>39.99</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D474" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -8115,13 +8130,13 @@
         <v>181</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="C475" s="6">
-        <v>19.5</v>
+        <v>39.99</v>
       </c>
       <c r="D475" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
@@ -8129,10 +8144,10 @@
         <v>181</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="C476" s="6">
-        <v>110</v>
+        <v>19.5</v>
       </c>
       <c r="D476" t="s">
         <v>139</v>
@@ -8143,10 +8158,10 @@
         <v>181</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C477" s="6">
-        <v>98.45</v>
+        <v>110</v>
       </c>
       <c r="D477" t="s">
         <v>139</v>
@@ -8157,10 +8172,10 @@
         <v>181</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C478" s="6">
-        <v>139</v>
+        <v>98.45</v>
       </c>
       <c r="D478" t="s">
         <v>139</v>
@@ -8171,10 +8186,10 @@
         <v>181</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C479" s="6">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="D479" t="s">
         <v>139</v>
@@ -8185,10 +8200,10 @@
         <v>181</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C480" s="6">
-        <v>169.99</v>
+        <v>199</v>
       </c>
       <c r="D480" t="s">
         <v>139</v>
@@ -8199,10 +8214,10 @@
         <v>181</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C481" s="6">
-        <v>239.08</v>
+        <v>169.99</v>
       </c>
       <c r="D481" t="s">
         <v>139</v>
@@ -8213,10 +8228,10 @@
         <v>181</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C482" s="6">
-        <v>219</v>
+        <v>239.08</v>
       </c>
       <c r="D482" t="s">
         <v>139</v>
@@ -8227,10 +8242,10 @@
         <v>181</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C483" s="6">
-        <v>189.99</v>
+        <v>219</v>
       </c>
       <c r="D483" t="s">
         <v>139</v>
@@ -8241,10 +8256,10 @@
         <v>181</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C484" s="6">
-        <v>248</v>
+        <v>189.99</v>
       </c>
       <c r="D484" t="s">
         <v>139</v>
@@ -8255,10 +8270,10 @@
         <v>181</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C485" s="6">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="D485" t="s">
         <v>139</v>
@@ -8269,26 +8284,26 @@
         <v>181</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C486" s="6">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="D486" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
-        <v>224</v>
-      </c>
-      <c r="B496" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C496" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D496" t="s">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>181</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C487" s="6">
+        <v>322</v>
+      </c>
+      <c r="D487" t="s">
         <v>139</v>
       </c>
     </row>
@@ -8297,10 +8312,10 @@
         <v>224</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C497" s="6">
-        <v>79.47</v>
+        <v>42.75</v>
       </c>
       <c r="D497" t="s">
         <v>139</v>
@@ -8311,10 +8326,10 @@
         <v>224</v>
       </c>
       <c r="B498" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C498" s="6">
-        <v>92.85</v>
+        <v>79.47</v>
       </c>
       <c r="D498" t="s">
         <v>139</v>
@@ -8324,14 +8339,14 @@
       <c r="A499" t="s">
         <v>224</v>
       </c>
-      <c r="B499" s="3">
-        <v>4430</v>
+      <c r="B499" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="C499" s="6">
-        <v>15.25</v>
+        <v>92.85</v>
       </c>
       <c r="D499" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
@@ -8339,10 +8354,10 @@
         <v>224</v>
       </c>
       <c r="B500" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C500" s="6">
-        <v>18.899999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="D500" t="s">
         <v>148</v>
@@ -8353,10 +8368,10 @@
         <v>224</v>
       </c>
       <c r="B501" s="3">
-        <v>6642</v>
+        <v>4442</v>
       </c>
       <c r="C501" s="6">
-        <v>26.8</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D501" t="s">
         <v>148</v>
@@ -8367,27 +8382,27 @@
         <v>224</v>
       </c>
       <c r="B502" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C502" s="6">
-        <v>27.05</v>
+        <v>26.8</v>
       </c>
       <c r="D502" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>228</v>
-      </c>
-      <c r="B505" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C505" s="6">
-        <v>47.95</v>
-      </c>
-      <c r="D505" t="s">
-        <v>139</v>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>224</v>
+      </c>
+      <c r="B503" s="3">
+        <v>6660</v>
+      </c>
+      <c r="C503" s="6">
+        <v>27.05</v>
+      </c>
+      <c r="D503" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
@@ -8395,10 +8410,10 @@
         <v>228</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C506" s="6">
-        <v>59.07</v>
+        <v>47.95</v>
       </c>
       <c r="D506" t="s">
         <v>139</v>
@@ -8409,10 +8424,10 @@
         <v>228</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C507" s="6">
-        <v>83.8</v>
+        <v>59.07</v>
       </c>
       <c r="D507" t="s">
         <v>139</v>
@@ -8423,10 +8438,10 @@
         <v>228</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C508" s="6">
-        <v>115.4</v>
+        <v>83.8</v>
       </c>
       <c r="D508" t="s">
         <v>139</v>
@@ -8437,10 +8452,10 @@
         <v>228</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C509" s="6">
-        <v>107.15</v>
+        <v>115.4</v>
       </c>
       <c r="D509" t="s">
         <v>139</v>
@@ -8451,13 +8466,13 @@
         <v>228</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C510" s="6">
-        <v>13</v>
+        <v>107.15</v>
       </c>
       <c r="D510" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
@@ -8465,10 +8480,10 @@
         <v>228</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C511" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D511" t="s">
         <v>140</v>
@@ -8479,27 +8494,27 @@
         <v>228</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C512" s="6">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D512" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>228</v>
       </c>
-      <c r="B513" s="3">
-        <v>4430</v>
+      <c r="B513" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="C513" s="6">
-        <v>15.25</v>
+        <v>30</v>
       </c>
       <c r="D513" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
@@ -8507,10 +8522,10 @@
         <v>228</v>
       </c>
       <c r="B514" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C514" s="6">
-        <v>18.899999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="D514" t="s">
         <v>148</v>
@@ -8521,10 +8536,10 @@
         <v>228</v>
       </c>
       <c r="B515" s="3">
-        <v>6642</v>
+        <v>4442</v>
       </c>
       <c r="C515" s="6">
-        <v>26.8</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D515" t="s">
         <v>148</v>
@@ -8534,28 +8549,28 @@
       <c r="A516" t="s">
         <v>228</v>
       </c>
-      <c r="B516" s="3" t="s">
+      <c r="B516" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C516" s="6">
+        <v>26.8</v>
+      </c>
+      <c r="D516" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>228</v>
+      </c>
+      <c r="B517" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C516" s="6">
+      <c r="C517" s="6">
         <v>39.950000000000003</v>
       </c>
-      <c r="D516" t="s">
+      <c r="D517" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A519" t="s">
-        <v>229</v>
-      </c>
-      <c r="B519" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C519" s="6">
-        <v>9.92</v>
-      </c>
-      <c r="D519" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
@@ -8563,13 +8578,13 @@
         <v>229</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>9</v>
+        <v>230</v>
       </c>
       <c r="C520" s="6">
-        <v>47.95</v>
+        <v>9.92</v>
       </c>
       <c r="D520" t="s">
-        <v>139</v>
+        <v>231</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
@@ -8577,10 +8592,10 @@
         <v>229</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C521" s="6">
-        <v>55.73</v>
+        <v>47.95</v>
       </c>
       <c r="D521" t="s">
         <v>139</v>
@@ -8591,10 +8606,10 @@
         <v>229</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C522" s="6">
-        <v>79.06</v>
+        <v>55.73</v>
       </c>
       <c r="D522" t="s">
         <v>139</v>
@@ -8605,10 +8620,10 @@
         <v>229</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C523" s="6">
-        <v>108.86</v>
+        <v>79.06</v>
       </c>
       <c r="D523" t="s">
         <v>139</v>
@@ -8619,10 +8634,10 @@
         <v>229</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C524" s="6">
-        <v>101.09</v>
+        <v>108.86</v>
       </c>
       <c r="D524" t="s">
         <v>139</v>
@@ -8633,10 +8648,10 @@
         <v>229</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C525" s="6">
-        <v>160.69999999999999</v>
+        <v>101.09</v>
       </c>
       <c r="D525" t="s">
         <v>139</v>
@@ -8647,10 +8662,10 @@
         <v>229</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C526" s="6">
-        <v>121.82</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="D526" t="s">
         <v>139</v>
@@ -8661,10 +8676,10 @@
         <v>229</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C527" s="6">
-        <v>122.49</v>
+        <v>121.82</v>
       </c>
       <c r="D527" t="s">
         <v>139</v>
@@ -8675,7 +8690,10 @@
         <v>229</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="C528" s="6">
+        <v>122.49</v>
       </c>
       <c r="D528" t="s">
         <v>139</v>
@@ -8686,7 +8704,7 @@
         <v>229</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D529" t="s">
         <v>139</v>
@@ -8697,7 +8715,7 @@
         <v>229</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D530" t="s">
         <v>139</v>
@@ -8708,10 +8726,7 @@
         <v>229</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C531" s="6">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D531" t="s">
         <v>139</v>
@@ -8722,10 +8737,10 @@
         <v>229</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C532" s="6">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D532" t="s">
         <v>139</v>
@@ -8736,10 +8751,10 @@
         <v>229</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C533" s="6">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D533" t="s">
         <v>139</v>
@@ -8750,18 +8765,21 @@
         <v>229</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>92</v>
+        <v>227</v>
+      </c>
+      <c r="C534" s="6">
+        <v>79</v>
       </c>
       <c r="D534" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>229</v>
       </c>
-      <c r="B535" s="3">
-        <v>4430</v>
+      <c r="B535" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D535" t="s">
         <v>148</v>
@@ -8772,10 +8790,7 @@
         <v>229</v>
       </c>
       <c r="B536" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C536" s="6">
-        <v>15</v>
+        <v>4430</v>
       </c>
       <c r="D536" t="s">
         <v>148</v>
@@ -8785,11 +8800,11 @@
       <c r="A537" t="s">
         <v>229</v>
       </c>
-      <c r="B537" s="3" t="s">
-        <v>96</v>
+      <c r="B537" s="3">
+        <v>4442</v>
       </c>
       <c r="C537" s="6">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="D537" t="s">
         <v>148</v>
@@ -8800,7 +8815,10 @@
         <v>229</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="C538" s="6">
+        <v>171</v>
       </c>
       <c r="D538" t="s">
         <v>148</v>
@@ -8810,11 +8828,8 @@
       <c r="A539" t="s">
         <v>229</v>
       </c>
-      <c r="B539" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C539" s="6">
-        <v>16.5</v>
+      <c r="B539" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D539" t="s">
         <v>148</v>
@@ -8824,11 +8839,11 @@
       <c r="A540" t="s">
         <v>229</v>
       </c>
-      <c r="B540" s="3" t="s">
-        <v>98</v>
+      <c r="B540" s="3">
+        <v>4642</v>
       </c>
       <c r="C540" s="6">
-        <v>126</v>
+        <v>16.5</v>
       </c>
       <c r="D540" t="s">
         <v>148</v>
@@ -8838,11 +8853,11 @@
       <c r="A541" t="s">
         <v>229</v>
       </c>
-      <c r="B541" s="3">
-        <v>4660</v>
+      <c r="B541" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C541" s="6">
-        <v>20.25</v>
+        <v>126</v>
       </c>
       <c r="D541" t="s">
         <v>148</v>
@@ -8853,7 +8868,10 @@
         <v>229</v>
       </c>
       <c r="B542" s="3">
-        <v>6630</v>
+        <v>4660</v>
+      </c>
+      <c r="C542" s="6">
+        <v>20.25</v>
       </c>
       <c r="D542" t="s">
         <v>148</v>
@@ -8864,10 +8882,7 @@
         <v>229</v>
       </c>
       <c r="B543" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C543" s="6">
-        <v>18.5</v>
+        <v>6630</v>
       </c>
       <c r="D543" t="s">
         <v>148</v>
@@ -8877,11 +8892,11 @@
       <c r="A544" t="s">
         <v>229</v>
       </c>
-      <c r="B544" s="3" t="s">
-        <v>99</v>
+      <c r="B544" s="3">
+        <v>6642</v>
       </c>
       <c r="C544" s="6">
-        <v>103.5</v>
+        <v>18.5</v>
       </c>
       <c r="D544" t="s">
         <v>148</v>
@@ -8891,11 +8906,11 @@
       <c r="A545" t="s">
         <v>229</v>
       </c>
-      <c r="B545" s="3">
-        <v>6660</v>
+      <c r="B545" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C545" s="6">
-        <v>22.5</v>
+        <v>103.5</v>
       </c>
       <c r="D545" t="s">
         <v>148</v>
@@ -8905,11 +8920,11 @@
       <c r="A546" t="s">
         <v>229</v>
       </c>
-      <c r="B546" s="3" t="s">
-        <v>100</v>
+      <c r="B546" s="3">
+        <v>6660</v>
       </c>
       <c r="C546" s="6">
-        <v>126</v>
+        <v>22.5</v>
       </c>
       <c r="D546" t="s">
         <v>148</v>
@@ -8919,21 +8934,24 @@
       <c r="A547" t="s">
         <v>229</v>
       </c>
-      <c r="B547" s="3">
-        <v>8860</v>
+      <c r="B547" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C547" s="6">
+        <v>126</v>
       </c>
       <c r="D547" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A550" t="s">
-        <v>232</v>
-      </c>
-      <c r="B550" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D550" t="s">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>229</v>
+      </c>
+      <c r="B548" s="3">
+        <v>8860</v>
+      </c>
+      <c r="D548" t="s">
         <v>148</v>
       </c>
     </row>
@@ -8941,11 +8959,8 @@
       <c r="A551" t="s">
         <v>232</v>
       </c>
-      <c r="B551" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C551" s="6">
-        <v>15.25</v>
+      <c r="B551" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="D551" t="s">
         <v>148</v>
@@ -8956,10 +8971,10 @@
         <v>232</v>
       </c>
       <c r="B552" s="3">
-        <v>4442</v>
+        <v>4430</v>
       </c>
       <c r="C552" s="6">
-        <v>15</v>
+        <v>15.25</v>
       </c>
       <c r="D552" t="s">
         <v>148</v>
@@ -8969,11 +8984,11 @@
       <c r="A553" t="s">
         <v>232</v>
       </c>
-      <c r="B553" s="3" t="s">
-        <v>96</v>
+      <c r="B553" s="3">
+        <v>4442</v>
       </c>
       <c r="C553" s="6">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="D553" t="s">
         <v>148</v>
@@ -8984,10 +8999,10 @@
         <v>232</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C554" s="6">
-        <v>972</v>
+        <v>171</v>
       </c>
       <c r="D554" t="s">
         <v>148</v>
@@ -8997,11 +9012,11 @@
       <c r="A555" t="s">
         <v>232</v>
       </c>
-      <c r="B555" s="3">
-        <v>4642</v>
+      <c r="B555" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C555" s="6">
-        <v>16.5</v>
+        <v>972</v>
       </c>
       <c r="D555" t="s">
         <v>148</v>
@@ -9011,11 +9026,11 @@
       <c r="A556" t="s">
         <v>232</v>
       </c>
-      <c r="B556" s="3" t="s">
-        <v>98</v>
+      <c r="B556" s="3">
+        <v>4642</v>
       </c>
       <c r="C556" s="6">
-        <v>126</v>
+        <v>16.5</v>
       </c>
       <c r="D556" t="s">
         <v>148</v>
@@ -9025,11 +9040,11 @@
       <c r="A557" t="s">
         <v>232</v>
       </c>
-      <c r="B557" s="3">
-        <v>4660</v>
+      <c r="B557" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C557" s="6">
-        <v>20.25</v>
+        <v>126</v>
       </c>
       <c r="D557" t="s">
         <v>148</v>
@@ -9040,10 +9055,10 @@
         <v>232</v>
       </c>
       <c r="B558" s="3">
-        <v>6630</v>
+        <v>4660</v>
       </c>
       <c r="C558" s="6">
-        <v>19</v>
+        <v>20.25</v>
       </c>
       <c r="D558" t="s">
         <v>148</v>
@@ -9054,10 +9069,10 @@
         <v>232</v>
       </c>
       <c r="B559" s="3">
-        <v>6642</v>
+        <v>6630</v>
       </c>
       <c r="C559" s="6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="D559" t="s">
         <v>148</v>
@@ -9067,11 +9082,11 @@
       <c r="A560" t="s">
         <v>232</v>
       </c>
-      <c r="B560" s="3" t="s">
-        <v>99</v>
+      <c r="B560" s="3">
+        <v>6642</v>
       </c>
       <c r="C560" s="6">
-        <v>103.5</v>
+        <v>18.5</v>
       </c>
       <c r="D560" t="s">
         <v>148</v>
@@ -9081,11 +9096,11 @@
       <c r="A561" t="s">
         <v>232</v>
       </c>
-      <c r="B561" s="3">
-        <v>6660</v>
+      <c r="B561" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C561" s="6">
-        <v>22.5</v>
+        <v>103.5</v>
       </c>
       <c r="D561" t="s">
         <v>148</v>
@@ -9095,11 +9110,11 @@
       <c r="A562" t="s">
         <v>232</v>
       </c>
-      <c r="B562" s="3" t="s">
-        <v>100</v>
+      <c r="B562" s="3">
+        <v>6660</v>
       </c>
       <c r="C562" s="6">
-        <v>126</v>
+        <v>22.5</v>
       </c>
       <c r="D562" t="s">
         <v>148</v>
@@ -9109,11 +9124,11 @@
       <c r="A563" t="s">
         <v>232</v>
       </c>
-      <c r="B563" s="3">
-        <v>8860</v>
+      <c r="B563" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C563" s="6">
-        <v>42.25</v>
+        <v>126</v>
       </c>
       <c r="D563" t="s">
         <v>148</v>
@@ -9123,14 +9138,14 @@
       <c r="A564" t="s">
         <v>232</v>
       </c>
-      <c r="B564" s="3" t="s">
-        <v>316</v>
+      <c r="B564" s="3">
+        <v>8860</v>
       </c>
       <c r="C564" s="6">
-        <v>5.75</v>
+        <v>42.25</v>
       </c>
       <c r="D564" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
@@ -9138,10 +9153,10 @@
         <v>232</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C565" s="6">
-        <v>20</v>
+        <v>5.75</v>
       </c>
       <c r="D565" t="s">
         <v>309</v>
@@ -9152,10 +9167,10 @@
         <v>232</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C566" s="6">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="D566" t="s">
         <v>309</v>
@@ -9166,10 +9181,10 @@
         <v>232</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C567" s="6">
-        <v>77.5</v>
+        <v>12.5</v>
       </c>
       <c r="D567" t="s">
         <v>309</v>
@@ -9180,27 +9195,27 @@
         <v>232</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C568" s="6">
-        <v>195</v>
+        <v>77.5</v>
       </c>
       <c r="D568" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A572" t="s">
-        <v>276</v>
-      </c>
-      <c r="B572" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C572" s="6">
-        <v>50.35</v>
-      </c>
-      <c r="D572" t="s">
-        <v>139</v>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>232</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C569" s="6">
+        <v>195</v>
+      </c>
+      <c r="D569" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
@@ -9208,10 +9223,10 @@
         <v>276</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C573" s="6">
-        <v>106.14</v>
+        <v>50.35</v>
       </c>
       <c r="D573" t="s">
         <v>139</v>
@@ -9222,13 +9237,13 @@
         <v>276</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C574" s="6">
-        <v>41.99</v>
+        <v>106.14</v>
       </c>
       <c r="D574" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
@@ -9236,13 +9251,13 @@
         <v>276</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C575" s="6">
-        <v>82</v>
+        <v>41.99</v>
       </c>
       <c r="D575" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
@@ -9250,10 +9265,10 @@
         <v>276</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="C576" s="6">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D576" t="s">
         <v>145</v>
@@ -9264,13 +9279,13 @@
         <v>276</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>112</v>
+        <v>256</v>
       </c>
       <c r="C577" s="6">
-        <v>28.05</v>
+        <v>28</v>
       </c>
       <c r="D577" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.25">
@@ -9278,7 +9293,7 @@
         <v>276</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C578" s="6">
         <v>28.05</v>
@@ -9292,7 +9307,7 @@
         <v>276</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C579" s="6">
         <v>28.05</v>
@@ -9306,27 +9321,27 @@
         <v>276</v>
       </c>
       <c r="B580" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C580" s="6">
-        <v>11.2</v>
+        <v>28.05</v>
       </c>
       <c r="D580" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A583" t="s">
-        <v>144</v>
-      </c>
-      <c r="B583" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C583" s="6">
-        <v>29.87</v>
-      </c>
-      <c r="D583" t="s">
-        <v>136</v>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>276</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C581" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="D581" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -9334,13 +9349,13 @@
         <v>144</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C584" s="6">
-        <v>199</v>
+        <v>29.87</v>
       </c>
       <c r="D584" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
@@ -9348,13 +9363,13 @@
         <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C585" s="6">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="D585" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
@@ -9362,10 +9377,10 @@
         <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C586" s="6">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D586" t="s">
         <v>142</v>
@@ -9376,10 +9391,10 @@
         <v>144</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C587" s="6">
-        <v>224.1</v>
+        <v>189</v>
       </c>
       <c r="D587" t="s">
         <v>142</v>
@@ -9390,10 +9405,10 @@
         <v>144</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C588" s="6">
-        <v>309</v>
+        <v>224.1</v>
       </c>
       <c r="D588" t="s">
         <v>142</v>
@@ -9404,10 +9419,10 @@
         <v>144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C589" s="6">
-        <v>85.5</v>
+        <v>309</v>
       </c>
       <c r="D589" t="s">
         <v>142</v>
@@ -9417,25 +9432,25 @@
       <c r="A590" t="s">
         <v>144</v>
       </c>
-      <c r="B590" s="3">
-        <v>6102</v>
+      <c r="B590" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C590" s="6">
-        <v>38.99</v>
+        <v>85.5</v>
       </c>
       <c r="D590" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>144</v>
       </c>
-      <c r="B591" s="3" t="s">
-        <v>212</v>
+      <c r="B591" s="3">
+        <v>6102</v>
       </c>
       <c r="C591" s="6">
-        <v>175</v>
+        <v>38.99</v>
       </c>
       <c r="D591" t="s">
         <v>144</v>
@@ -9446,10 +9461,10 @@
         <v>144</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C592" s="6">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D592" t="s">
         <v>144</v>
@@ -9460,13 +9475,13 @@
         <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="C593" s="6">
-        <v>59.99</v>
+        <v>134</v>
       </c>
       <c r="D593" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
@@ -9474,10 +9489,10 @@
         <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C594" s="6">
-        <v>32.99</v>
+        <v>59.99</v>
       </c>
       <c r="D594" t="s">
         <v>145</v>
@@ -9488,10 +9503,10 @@
         <v>144</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C595" s="6">
-        <v>129</v>
+        <v>32.99</v>
       </c>
       <c r="D595" t="s">
         <v>145</v>
@@ -9502,10 +9517,10 @@
         <v>144</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C596" s="6">
-        <v>149.99</v>
+        <v>129</v>
       </c>
       <c r="D596" t="s">
         <v>145</v>
@@ -9516,13 +9531,13 @@
         <v>144</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C597" s="6">
-        <v>47.99</v>
+        <v>149.99</v>
       </c>
       <c r="D597" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
@@ -9530,10 +9545,10 @@
         <v>144</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C598" s="6">
-        <v>39.99</v>
+        <v>47.99</v>
       </c>
       <c r="D598" t="s">
         <v>146</v>
@@ -9544,13 +9559,13 @@
         <v>144</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C599" s="6">
         <v>39.99</v>
       </c>
       <c r="D599" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
@@ -9558,7 +9573,10 @@
         <v>144</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="C600" s="6">
+        <v>39.99</v>
       </c>
       <c r="D600" t="s">
         <v>151</v>
@@ -9569,27 +9587,24 @@
         <v>144</v>
       </c>
       <c r="B601" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D601" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>144</v>
+      </c>
+      <c r="B602" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C601" s="6">
+      <c r="C602" s="6">
         <v>36.950000000000003</v>
       </c>
-      <c r="D601" t="s">
+      <c r="D602" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A604" t="s">
-        <v>288</v>
-      </c>
-      <c r="B604" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C604" s="6">
-        <v>18</v>
-      </c>
-      <c r="D604" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
@@ -9597,10 +9612,10 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C605" s="6">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -9611,10 +9626,10 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C606" s="6">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -9625,10 +9640,10 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C607" s="6">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D607" t="s">
         <v>139</v>
@@ -9639,10 +9654,10 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C608" s="6">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D608" t="s">
         <v>139</v>
@@ -9653,10 +9668,10 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C609" s="6">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="D609" t="s">
         <v>139</v>
@@ -9667,10 +9682,10 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C610" s="6">
-        <v>239</v>
+        <v>155</v>
       </c>
       <c r="D610" t="s">
         <v>139</v>
@@ -9681,10 +9696,10 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C611" s="6">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="D611" t="s">
         <v>139</v>
@@ -9695,10 +9710,10 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C612" s="6">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D612" t="s">
         <v>139</v>
@@ -9709,10 +9724,10 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C613" s="6">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D613" t="s">
         <v>139</v>
@@ -9723,10 +9738,10 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C614" s="6">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="D614" t="s">
         <v>139</v>
@@ -9737,10 +9752,10 @@
         <v>288</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C615" s="6">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D615" t="s">
         <v>139</v>
@@ -9751,13 +9766,13 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C616" s="6">
-        <v>19.989999999999998</v>
+        <v>250</v>
       </c>
       <c r="D616" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
@@ -9765,10 +9780,10 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C617" s="6">
-        <v>29.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D617" t="s">
         <v>140</v>
@@ -9779,13 +9794,13 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C618" s="6">
-        <v>155</v>
+        <v>29.99</v>
       </c>
       <c r="D618" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.25">
@@ -9793,10 +9808,10 @@
         <v>288</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C619" s="6">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D619" t="s">
         <v>142</v>
@@ -9807,10 +9822,10 @@
         <v>288</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C620" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D620" t="s">
         <v>142</v>
@@ -9821,10 +9836,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C621" s="6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D621" t="s">
         <v>142</v>
@@ -9835,10 +9850,10 @@
         <v>288</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C622" s="6">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D622" t="s">
         <v>142</v>
@@ -9849,10 +9864,10 @@
         <v>288</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C623" s="6">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="D623" t="s">
         <v>142</v>
@@ -9863,10 +9878,10 @@
         <v>288</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C624" s="6">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="D624" t="s">
         <v>142</v>
@@ -9877,10 +9892,10 @@
         <v>288</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C625" s="6">
-        <v>399.99</v>
+        <v>389</v>
       </c>
       <c r="D625" t="s">
         <v>142</v>
@@ -9891,10 +9906,10 @@
         <v>288</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C626" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D626" t="s">
         <v>142</v>
@@ -9904,28 +9919,28 @@
       <c r="A627" t="s">
         <v>288</v>
       </c>
-      <c r="B627" s="3">
-        <v>6102</v>
+      <c r="B627" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C627" s="6">
-        <v>44</v>
+        <v>89.23</v>
       </c>
       <c r="D627" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>288</v>
       </c>
-      <c r="B628" s="3" t="s">
-        <v>281</v>
+      <c r="B628" s="3">
+        <v>6102</v>
       </c>
       <c r="C628" s="6">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D628" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
@@ -9933,10 +9948,10 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C629" s="6">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D629" t="s">
         <v>269</v>
@@ -9947,10 +9962,10 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C630" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D630" t="s">
         <v>269</v>
@@ -9961,10 +9976,10 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C631" s="6">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D631" t="s">
         <v>269</v>
@@ -9975,10 +9990,10 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C632" s="6">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D632" t="s">
         <v>269</v>
@@ -9989,10 +10004,10 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C633" s="6">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D633" t="s">
         <v>269</v>
@@ -10003,13 +10018,13 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="C634" s="6">
-        <v>27.99</v>
+        <v>114</v>
       </c>
       <c r="D634" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.25">
@@ -10017,10 +10032,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>255</v>
+        <v>55</v>
       </c>
       <c r="C635" s="6">
-        <v>28.99</v>
+        <v>27.99</v>
       </c>
       <c r="D635" t="s">
         <v>145</v>
@@ -10031,10 +10046,10 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="C636" s="6">
-        <v>39.99</v>
+        <v>28.99</v>
       </c>
       <c r="D636" t="s">
         <v>145</v>
@@ -10045,10 +10060,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C637" s="6">
-        <v>58</v>
+        <v>39.99</v>
       </c>
       <c r="D637" t="s">
         <v>145</v>
@@ -10059,10 +10074,10 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C638" s="6">
-        <v>42.99</v>
+        <v>58</v>
       </c>
       <c r="D638" t="s">
         <v>145</v>
@@ -10073,10 +10088,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C639" s="6">
-        <v>129</v>
+        <v>42.99</v>
       </c>
       <c r="D639" t="s">
         <v>145</v>
@@ -10087,10 +10102,10 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C640" s="6">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="D640" t="s">
         <v>145</v>
@@ -10101,13 +10116,13 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C641" s="6">
-        <v>54.5</v>
+        <v>180</v>
       </c>
       <c r="D641" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.25">
@@ -10115,10 +10130,10 @@
         <v>288</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C642" s="6">
-        <v>48.99</v>
+        <v>54.5</v>
       </c>
       <c r="D642" t="s">
         <v>146</v>
@@ -10129,10 +10144,10 @@
         <v>288</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C643" s="6">
-        <v>39.99</v>
+        <v>48.99</v>
       </c>
       <c r="D643" t="s">
         <v>146</v>
@@ -10143,10 +10158,10 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C644" s="6">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="D644" t="s">
         <v>146</v>
@@ -10157,10 +10172,10 @@
         <v>288</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C645" s="6">
-        <v>29.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D645" t="s">
         <v>146</v>
@@ -10171,10 +10186,10 @@
         <v>288</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C646" s="6">
-        <v>28.99</v>
+        <v>29.99</v>
       </c>
       <c r="D646" t="s">
         <v>146</v>
@@ -10185,7 +10200,10 @@
         <v>288</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>176</v>
+        <v>66</v>
+      </c>
+      <c r="C647" s="6">
+        <v>28.99</v>
       </c>
       <c r="D647" t="s">
         <v>146</v>
@@ -10196,10 +10214,7 @@
         <v>288</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C648" s="6">
-        <v>29.99</v>
+        <v>176</v>
       </c>
       <c r="D648" t="s">
         <v>146</v>
@@ -10210,10 +10225,10 @@
         <v>288</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C649" s="6">
-        <v>25.99</v>
+        <v>29.99</v>
       </c>
       <c r="D649" t="s">
         <v>146</v>
@@ -10223,28 +10238,28 @@
       <c r="A650" t="s">
         <v>288</v>
       </c>
-      <c r="B650" s="3">
-        <v>6642</v>
+      <c r="B650" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C650" s="6">
-        <v>50</v>
+        <v>25.99</v>
       </c>
       <c r="D650" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>288</v>
       </c>
-      <c r="B651" s="3" t="s">
-        <v>117</v>
+      <c r="B651" s="3">
+        <v>6642</v>
       </c>
       <c r="C651" s="6">
-        <v>19.2</v>
+        <v>50</v>
       </c>
       <c r="D651" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
@@ -10252,10 +10267,10 @@
         <v>288</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C652" s="6">
-        <v>40</v>
+        <v>19.2</v>
       </c>
       <c r="D652" t="s">
         <v>152</v>
@@ -10266,7 +10281,7 @@
         <v>288</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C653" s="6">
         <v>40</v>
@@ -10280,13 +10295,13 @@
         <v>288</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="C654" s="6">
-        <v>30.58</v>
+        <v>40</v>
       </c>
       <c r="D654" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
@@ -10294,10 +10309,10 @@
         <v>288</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C655" s="6">
-        <v>39.99</v>
+        <v>30.58</v>
       </c>
       <c r="D655" t="s">
         <v>154</v>
@@ -10308,27 +10323,27 @@
         <v>288</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="C656" s="6">
-        <v>90</v>
+        <v>39.99</v>
       </c>
       <c r="D656" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A659" t="s">
-        <v>290</v>
-      </c>
-      <c r="B659" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C659" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D659" t="s">
-        <v>139</v>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>288</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C657" s="6">
+        <v>90</v>
+      </c>
+      <c r="D657" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
@@ -10336,10 +10351,10 @@
         <v>290</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C660" s="6">
-        <v>68</v>
+        <v>42.75</v>
       </c>
       <c r="D660" t="s">
         <v>139</v>
@@ -10350,27 +10365,27 @@
         <v>290</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C661" s="6">
-        <v>82.2</v>
+        <v>68</v>
       </c>
       <c r="D661" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A663" t="s">
-        <v>304</v>
-      </c>
-      <c r="B663" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C663" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="D663" t="s">
-        <v>140</v>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A662" t="s">
+        <v>290</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C662" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D662" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
@@ -10378,10 +10393,10 @@
         <v>304</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C664" s="6">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="D664" t="s">
         <v>140</v>
@@ -10391,14 +10406,14 @@
       <c r="A665" t="s">
         <v>304</v>
       </c>
-      <c r="B665" s="3">
-        <v>4642</v>
+      <c r="B665" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C665" s="6">
-        <v>18.96</v>
+        <v>3.25</v>
       </c>
       <c r="D665" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.25">
@@ -10406,10 +10421,10 @@
         <v>304</v>
       </c>
       <c r="B666" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C666" s="6">
-        <v>22.37</v>
+        <v>18.96</v>
       </c>
       <c r="D666" t="s">
         <v>148</v>
@@ -10419,14 +10434,14 @@
       <c r="A667" t="s">
         <v>304</v>
       </c>
-      <c r="B667" s="3" t="s">
-        <v>116</v>
+      <c r="B667" s="3">
+        <v>6642</v>
       </c>
       <c r="C667" s="6">
-        <v>9.1</v>
+        <v>22.37</v>
       </c>
       <c r="D667" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
@@ -10434,7 +10449,7 @@
         <v>304</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C668" s="6">
         <v>9.1</v>
@@ -10443,18 +10458,18 @@
         <v>152</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A673" t="s">
-        <v>292</v>
-      </c>
-      <c r="B673" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C673" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="D673" t="s">
-        <v>140</v>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>304</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C669" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D669" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
@@ -10462,27 +10477,27 @@
         <v>292</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C674" s="6">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="D674" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A678" t="s">
-        <v>293</v>
-      </c>
-      <c r="B678" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C678" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D678" t="s">
-        <v>303</v>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>292</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C675" s="6">
+        <v>3.25</v>
+      </c>
+      <c r="D675" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
@@ -10490,10 +10505,10 @@
         <v>293</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C679" s="6">
-        <v>7.65</v>
+        <v>3.15</v>
       </c>
       <c r="D679" t="s">
         <v>303</v>
@@ -10504,10 +10519,10 @@
         <v>293</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C680" s="6">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="D680" t="s">
         <v>303</v>
@@ -10518,10 +10533,10 @@
         <v>293</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C681" s="6">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="D681" t="s">
         <v>303</v>
@@ -10532,10 +10547,10 @@
         <v>293</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C682" s="6">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="D682" t="s">
         <v>303</v>
@@ -10546,10 +10561,10 @@
         <v>293</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C683" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D683" t="s">
         <v>303</v>
@@ -10560,7 +10575,7 @@
         <v>293</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C684" s="6">
         <v>11.25</v>
@@ -10574,7 +10589,7 @@
         <v>293</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C685" s="6">
         <v>11.25</v>
@@ -10583,17 +10598,17 @@
         <v>303</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A688" t="s">
-        <v>294</v>
-      </c>
-      <c r="B688" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C688" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D688" t="s">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>293</v>
+      </c>
+      <c r="B686" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C686" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D686" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10602,10 +10617,10 @@
         <v>294</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C689" s="6">
-        <v>10.19</v>
+        <v>3.36</v>
       </c>
       <c r="D689" t="s">
         <v>303</v>
@@ -10616,10 +10631,10 @@
         <v>294</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C690" s="6">
-        <v>14.4</v>
+        <v>10.19</v>
       </c>
       <c r="D690" t="s">
         <v>303</v>
@@ -10630,10 +10645,10 @@
         <v>294</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C691" s="6">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="D691" t="s">
         <v>303</v>
@@ -10644,10 +10659,10 @@
         <v>294</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C692" s="6">
-        <v>11.52</v>
+        <v>14.39</v>
       </c>
       <c r="D692" t="s">
         <v>303</v>
@@ -10658,10 +10673,10 @@
         <v>294</v>
       </c>
       <c r="B693" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C693" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D693" t="s">
         <v>303</v>
@@ -10672,7 +10687,7 @@
         <v>294</v>
       </c>
       <c r="B694" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C694" s="6">
         <v>12</v>
@@ -10686,12 +10701,26 @@
         <v>294</v>
       </c>
       <c r="B695" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C695" s="6">
         <v>12</v>
       </c>
       <c r="D695" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>294</v>
+      </c>
+      <c r="B696" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C696" s="6">
+        <v>12</v>
+      </c>
+      <c r="D696" t="s">
         <v>303</v>
       </c>
     </row>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEF9AA7-AD8E-48F8-9572-C7AE19FF2BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A57A27-DA62-490D-A164-BB167D3FF904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47805" yWindow="-16320" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="11265" yWindow="3345" windowWidth="21600" windowHeight="11505" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="344">
   <si>
     <t>BGC10</t>
   </si>
@@ -1051,6 +1051,12 @@
   </si>
   <si>
     <t>NIBAN4LBSHAKER</t>
+  </si>
+  <si>
+    <t>Retailer Name Change</t>
+  </si>
+  <si>
+    <t>Depot DFC</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1462,7 @@
     <col min="3" max="3" width="21" style="6" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="7"/>
+    <col min="6" max="6" width="22.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1477,6 +1483,9 @@
       <c r="E1" s="3" t="s">
         <v>340</v>
       </c>
+      <c r="F1" s="7" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -8307,7 +8316,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>224</v>
       </c>
@@ -8320,8 +8329,11 @@
       <c r="D497" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F497" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>224</v>
       </c>
@@ -8334,8 +8346,11 @@
       <c r="D498" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F498" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>224</v>
       </c>
@@ -8348,8 +8363,11 @@
       <c r="D499" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F499" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>224</v>
       </c>
@@ -8362,8 +8380,11 @@
       <c r="D500" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F500" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>224</v>
       </c>
@@ -8376,8 +8397,11 @@
       <c r="D501" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F501" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>224</v>
       </c>
@@ -8390,8 +8414,11 @@
       <c r="D502" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F502" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>224</v>
       </c>
@@ -8404,8 +8431,11 @@
       <c r="D503" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F503" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>228</v>
       </c>
@@ -8419,7 +8449,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>228</v>
       </c>
@@ -8433,7 +8463,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>228</v>
       </c>
@@ -8447,7 +8477,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>228</v>
       </c>
@@ -8461,7 +8491,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>228</v>
       </c>
@@ -8475,7 +8505,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>228</v>
       </c>
@@ -8489,7 +8519,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>228</v>
       </c>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A57A27-DA62-490D-A164-BB167D3FF904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8776140C-0961-4879-9CB4-06F3A1E49198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11265" yWindow="3345" windowWidth="21600" windowHeight="11505" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="345">
   <si>
     <t>BGC10</t>
   </si>
@@ -1057,6 +1057,9 @@
   </si>
   <si>
     <t>Depot DFC</t>
+  </si>
+  <si>
+    <t>Depot Special Order</t>
   </si>
 </sst>
 </file>
@@ -8533,7 +8536,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>228</v>
       </c>
@@ -8547,7 +8550,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>228</v>
       </c>
@@ -8561,7 +8564,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>228</v>
       </c>
@@ -8575,7 +8578,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>228</v>
       </c>
@@ -8589,7 +8592,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>228</v>
       </c>
@@ -8603,7 +8606,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>229</v>
       </c>
@@ -8616,8 +8619,11 @@
       <c r="D520" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F520" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>229</v>
       </c>
@@ -8630,8 +8636,11 @@
       <c r="D521" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F521" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>229</v>
       </c>
@@ -8644,8 +8653,11 @@
       <c r="D522" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F522" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>229</v>
       </c>
@@ -8658,8 +8670,11 @@
       <c r="D523" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F523" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>229</v>
       </c>
@@ -8672,8 +8687,11 @@
       <c r="D524" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F524" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>229</v>
       </c>
@@ -8686,8 +8704,11 @@
       <c r="D525" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F525" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>229</v>
       </c>
@@ -8700,8 +8721,11 @@
       <c r="D526" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F526" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>229</v>
       </c>
@@ -8714,8 +8738,11 @@
       <c r="D527" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F527" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>229</v>
       </c>
@@ -8728,8 +8755,11 @@
       <c r="D528" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F528" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>229</v>
       </c>
@@ -8739,8 +8769,11 @@
       <c r="D529" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F529" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>229</v>
       </c>
@@ -8750,8 +8783,11 @@
       <c r="D530" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F530" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>229</v>
       </c>
@@ -8761,8 +8797,11 @@
       <c r="D531" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F531" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>229</v>
       </c>
@@ -8775,8 +8814,11 @@
       <c r="D532" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F532" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>229</v>
       </c>
@@ -8789,8 +8831,11 @@
       <c r="D533" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F533" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>229</v>
       </c>
@@ -8803,8 +8848,11 @@
       <c r="D534" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F534" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>229</v>
       </c>
@@ -8814,8 +8862,11 @@
       <c r="D535" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F535" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>229</v>
       </c>
@@ -8825,8 +8876,11 @@
       <c r="D536" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F536" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>229</v>
       </c>
@@ -8839,8 +8893,11 @@
       <c r="D537" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F537" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>229</v>
       </c>
@@ -8853,8 +8910,11 @@
       <c r="D538" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F538" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>229</v>
       </c>
@@ -8864,8 +8924,11 @@
       <c r="D539" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F539" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>229</v>
       </c>
@@ -8878,8 +8941,11 @@
       <c r="D540" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F540" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>229</v>
       </c>
@@ -8892,8 +8958,11 @@
       <c r="D541" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F541" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>229</v>
       </c>
@@ -8906,8 +8975,11 @@
       <c r="D542" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F542" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>229</v>
       </c>
@@ -8917,8 +8989,11 @@
       <c r="D543" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F543" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>229</v>
       </c>
@@ -8931,8 +9006,11 @@
       <c r="D544" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F544" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>229</v>
       </c>
@@ -8945,8 +9023,11 @@
       <c r="D545" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F545" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>229</v>
       </c>
@@ -8959,8 +9040,11 @@
       <c r="D546" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F546" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>229</v>
       </c>
@@ -8973,8 +9057,11 @@
       <c r="D547" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F547" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>229</v>
       </c>
@@ -8984,8 +9071,11 @@
       <c r="D548" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F548" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>232</v>
       </c>
@@ -8996,7 +9086,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>232</v>
       </c>
@@ -9010,7 +9100,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>232</v>
       </c>
@@ -9024,7 +9114,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>232</v>
       </c>
@@ -9038,7 +9128,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>232</v>
       </c>
@@ -9052,7 +9142,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>232</v>
       </c>
@@ -9066,7 +9156,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>232</v>
       </c>
@@ -9080,7 +9170,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>232</v>
       </c>
@@ -9094,7 +9184,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>232</v>
       </c>
@@ -9108,7 +9198,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>232</v>
       </c>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22299EC2-0CAE-42BE-94B4-67A72081938D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC9210-B924-4058-B314-49AA72AADBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1575" yWindow="1275" windowWidth="36405" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="352">
   <si>
     <t>Retailer</t>
   </si>
@@ -1067,6 +1067,15 @@
   </si>
   <si>
     <t>DIMONDI-27</t>
+  </si>
+  <si>
+    <t>Ace</t>
+  </si>
+  <si>
+    <t>TikTok</t>
+  </si>
+  <si>
+    <t>NIBORDPLUSIGR</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K699"/>
+  <dimension ref="A1:K705"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -8878,6 +8887,9 @@
       <c r="B535" s="3" t="s">
         <v>158</v>
       </c>
+      <c r="C535" s="6">
+        <v>69.900000000000006</v>
+      </c>
       <c r="D535" t="s">
         <v>156</v>
       </c>
@@ -8892,6 +8904,9 @@
       <c r="B536" s="3">
         <v>4430</v>
       </c>
+      <c r="C536" s="6">
+        <v>15.25</v>
+      </c>
       <c r="D536" t="s">
         <v>156</v>
       </c>
@@ -9005,6 +9020,9 @@
       <c r="B543" s="3">
         <v>6630</v>
       </c>
+      <c r="C543" s="6">
+        <v>20</v>
+      </c>
       <c r="D543" t="s">
         <v>156</v>
       </c>
@@ -9087,6 +9105,9 @@
       <c r="B548" s="3">
         <v>8860</v>
       </c>
+      <c r="C548" s="6">
+        <v>28</v>
+      </c>
       <c r="D548" t="s">
         <v>156</v>
       </c>
@@ -10361,6 +10382,9 @@
       <c r="B648" s="3" t="s">
         <v>254</v>
       </c>
+      <c r="C648" s="6">
+        <v>35</v>
+      </c>
       <c r="D648" t="s">
         <v>118</v>
       </c>
@@ -10617,7 +10641,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>333</v>
       </c>
@@ -10630,8 +10654,11 @@
       <c r="D674" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F674" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>333</v>
       </c>
@@ -10644,8 +10671,11 @@
       <c r="D675" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F675" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>334</v>
       </c>
@@ -10659,7 +10689,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>334</v>
       </c>
@@ -10673,7 +10703,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>334</v>
       </c>
@@ -10687,7 +10717,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>334</v>
       </c>
@@ -10701,7 +10731,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>334</v>
       </c>
@@ -10715,7 +10745,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>334</v>
       </c>
@@ -10729,7 +10759,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>334</v>
       </c>
@@ -10743,7 +10773,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>334</v>
       </c>
@@ -10879,6 +10909,9 @@
       <c r="C697">
         <v>23</v>
       </c>
+      <c r="D697" t="s">
+        <v>118</v>
+      </c>
       <c r="E697" t="s">
         <v>123</v>
       </c>
@@ -10893,6 +10926,9 @@
       <c r="C698">
         <v>12</v>
       </c>
+      <c r="D698" t="s">
+        <v>109</v>
+      </c>
       <c r="E698" t="s">
         <v>110</v>
       </c>
@@ -10907,8 +10943,70 @@
       <c r="C699">
         <v>126.38</v>
       </c>
+      <c r="D699" t="s">
+        <v>79</v>
+      </c>
       <c r="E699" t="s">
         <v>348</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>350</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C702" s="6">
+        <v>17.489999999999998</v>
+      </c>
+      <c r="D702" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>350</v>
+      </c>
+      <c r="B703" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C703" s="6">
+        <v>199.99</v>
+      </c>
+      <c r="D703" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>350</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C704" s="6">
+        <v>28.99</v>
+      </c>
+      <c r="D704" t="s">
+        <v>118</v>
+      </c>
+      <c r="E704" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>350</v>
+      </c>
+      <c r="B705" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C705" s="6">
+        <v>359.99</v>
+      </c>
+      <c r="D705" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC9210-B924-4058-B314-49AA72AADBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7595A752-7DB0-4BCA-BF74-852371309A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1575" yWindow="1275" windowWidth="36405" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43783" yWindow="-6214" windowWidth="33120" windowHeight="18274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="359">
   <si>
     <t>Retailer</t>
   </si>
@@ -1076,6 +1076,27 @@
   </si>
   <si>
     <t>NIBORDPLUSIGR</t>
+  </si>
+  <si>
+    <t>NFG1LB</t>
+  </si>
+  <si>
+    <t>DOMINANT</t>
+  </si>
+  <si>
+    <t>NIBORD5LB</t>
+  </si>
+  <si>
+    <t>ZO1G</t>
+  </si>
+  <si>
+    <t>Deco Mia-953</t>
+  </si>
+  <si>
+    <t>4660C</t>
+  </si>
+  <si>
+    <t>WO32OZ</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K705"/>
+  <dimension ref="A1:K713"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -2574,7 +2595,7 @@
         <v>6</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>87</v>
+        <v>356</v>
       </c>
       <c r="C73" s="6">
         <v>179</v>
@@ -5260,83 +5281,89 @@
         <v>227</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>153</v>
+        <v>351</v>
       </c>
       <c r="C259" s="6">
-        <v>60</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="D259" t="s">
-        <v>154</v>
+        <v>118</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>227</v>
       </c>
-      <c r="B260" s="3">
-        <v>4430</v>
+      <c r="B260" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="C260" s="6">
-        <v>12.6</v>
+        <v>28</v>
       </c>
       <c r="D260" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>227</v>
       </c>
-      <c r="B261" s="3">
-        <v>4442</v>
+      <c r="B261" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="C261" s="6">
-        <v>14.53</v>
+        <v>16</v>
       </c>
       <c r="D261" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>227</v>
       </c>
-      <c r="B262" s="3">
-        <v>4642</v>
+      <c r="B262" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="C262" s="6">
-        <v>20.8</v>
+        <v>42</v>
       </c>
       <c r="D262" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>227</v>
       </c>
-      <c r="B263" s="3">
-        <v>4660</v>
+      <c r="B263" s="3" t="s">
+        <v>355</v>
       </c>
       <c r="C263" s="6">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="D263" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>227</v>
       </c>
-      <c r="B264" s="3">
-        <v>6642</v>
+      <c r="B264" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="C264" s="6">
-        <v>18.52</v>
+        <v>11.5</v>
       </c>
       <c r="D264" t="s">
-        <v>156</v>
+        <v>118</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -5344,35 +5371,38 @@
         <v>227</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>164</v>
+        <v>352</v>
+      </c>
+      <c r="C265" s="6">
+        <v>15.35</v>
       </c>
       <c r="D265" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>227</v>
       </c>
-      <c r="B266" s="3">
-        <v>6660</v>
+      <c r="B266" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="C266" s="6">
-        <v>27.05</v>
+        <v>60</v>
       </c>
       <c r="D266" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>227</v>
       </c>
-      <c r="B267" s="3" t="s">
-        <v>165</v>
+      <c r="B267" s="3">
+        <v>4430</v>
       </c>
       <c r="C267" s="6">
-        <v>160</v>
+        <v>12.6</v>
       </c>
       <c r="D267" t="s">
         <v>156</v>
@@ -5383,10 +5413,10 @@
         <v>227</v>
       </c>
       <c r="B268" s="3">
-        <v>8860</v>
+        <v>4442</v>
       </c>
       <c r="C268" s="6">
-        <v>63.9</v>
+        <v>14.53</v>
       </c>
       <c r="D268" t="s">
         <v>156</v>
@@ -5396,42 +5426,42 @@
       <c r="A269" t="s">
         <v>227</v>
       </c>
-      <c r="B269" s="3" t="s">
-        <v>166</v>
+      <c r="B269" s="3">
+        <v>4642</v>
       </c>
       <c r="C269" s="6">
-        <v>92</v>
+        <v>20.8</v>
       </c>
       <c r="D269" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>227</v>
       </c>
-      <c r="B270" s="3" t="s">
-        <v>168</v>
+      <c r="B270" s="3">
+        <v>4660</v>
       </c>
       <c r="C270" s="6">
-        <v>22.75</v>
+        <v>27</v>
       </c>
       <c r="D270" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>227</v>
       </c>
-      <c r="B271" s="3" t="s">
-        <v>169</v>
+      <c r="B271" s="3">
+        <v>6642</v>
       </c>
       <c r="C271" s="6">
-        <v>18.25</v>
+        <v>18.52</v>
       </c>
       <c r="D271" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -5439,27 +5469,24 @@
         <v>227</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C272" s="6">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="D272" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>227</v>
       </c>
-      <c r="B273" s="3" t="s">
-        <v>172</v>
+      <c r="B273" s="3">
+        <v>6660</v>
       </c>
       <c r="C273" s="6">
-        <v>227</v>
+        <v>27.05</v>
       </c>
       <c r="D273" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -5467,27 +5494,27 @@
         <v>227</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="C274" s="6">
-        <v>41.5</v>
+        <v>160</v>
       </c>
       <c r="D274" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>227</v>
       </c>
-      <c r="B275" s="3" t="s">
-        <v>237</v>
+      <c r="B275" s="3">
+        <v>8860</v>
       </c>
       <c r="C275" s="6">
-        <v>11</v>
+        <v>63.9</v>
       </c>
       <c r="D275" t="s">
-        <v>238</v>
+        <v>156</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -5495,13 +5522,13 @@
         <v>227</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="C276" s="6">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="D276" t="s">
-        <v>238</v>
+        <v>167</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -5509,13 +5536,13 @@
         <v>227</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="C277" s="6">
-        <v>78</v>
+        <v>22.75</v>
       </c>
       <c r="D277" t="s">
-        <v>238</v>
+        <v>167</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -5523,13 +5550,13 @@
         <v>227</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="C278" s="6">
-        <v>23.15</v>
+        <v>18.25</v>
       </c>
       <c r="D278" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -5537,13 +5564,13 @@
         <v>227</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="C279" s="6">
-        <v>42.65</v>
+        <v>115</v>
       </c>
       <c r="D279" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -5551,13 +5578,13 @@
         <v>227</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="C280" s="6">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="D280" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -5565,13 +5592,13 @@
         <v>227</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C281" s="6">
-        <v>33.5</v>
+        <v>41.5</v>
       </c>
       <c r="D281" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -5579,13 +5606,13 @@
         <v>227</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C282" s="6">
-        <v>60.9</v>
+        <v>11</v>
       </c>
       <c r="D282" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -5593,13 +5620,13 @@
         <v>227</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C283" s="6">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="D283" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -5607,13 +5634,13 @@
         <v>227</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C284" s="6">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="D284" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -5621,10 +5648,10 @@
         <v>227</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C285" s="6">
-        <v>16</v>
+        <v>23.15</v>
       </c>
       <c r="D285" t="s">
         <v>211</v>
@@ -5635,10 +5662,10 @@
         <v>227</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C286" s="6">
-        <v>21.32</v>
+        <v>42.65</v>
       </c>
       <c r="D286" t="s">
         <v>211</v>
@@ -5649,13 +5676,13 @@
         <v>227</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="C287" s="6">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="D287" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -5663,13 +5690,13 @@
         <v>227</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="C288" s="6">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="D288" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -5677,13 +5704,13 @@
         <v>227</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="C289" s="6">
-        <v>27</v>
+        <v>60.9</v>
       </c>
       <c r="D289" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -5691,13 +5718,13 @@
         <v>227</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="C290" s="6">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="D290" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -5705,13 +5732,13 @@
         <v>227</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="C291" s="6">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="D291" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -5719,13 +5746,13 @@
         <v>227</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="C292" s="6">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="D292" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -5733,111 +5760,111 @@
         <v>227</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="C293" s="6">
-        <v>126</v>
+        <v>21.32</v>
       </c>
       <c r="D293" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>227</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C294" s="6">
+        <v>30</v>
+      </c>
+      <c r="D294" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>227</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C295" s="6">
+        <v>33</v>
+      </c>
+      <c r="D295" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>227</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C296" s="6">
+        <v>27</v>
+      </c>
+      <c r="D296" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>227</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C297" s="6">
+        <v>45</v>
+      </c>
+      <c r="D297" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>7</v>
+        <v>246</v>
       </c>
       <c r="C298" s="6">
-        <v>9.6</v>
+        <v>81</v>
       </c>
       <c r="D298" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>9</v>
+        <v>247</v>
       </c>
       <c r="C299" s="6">
-        <v>9.5399999999999991</v>
+        <v>114</v>
       </c>
       <c r="D299" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>10</v>
+        <v>248</v>
       </c>
       <c r="C300" s="6">
-        <v>9.6</v>
+        <v>126</v>
       </c>
       <c r="D300" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>249</v>
-      </c>
-      <c r="B301" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C301" s="6">
-        <v>11.5</v>
-      </c>
-      <c r="D301" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>249</v>
-      </c>
-      <c r="B302" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C302" s="6">
-        <v>14.99</v>
-      </c>
-      <c r="D302" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>249</v>
-      </c>
-      <c r="B303" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C303" s="6">
-        <v>16.5</v>
-      </c>
-      <c r="D303" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>249</v>
-      </c>
-      <c r="B304" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C304" s="6">
-        <v>17.97</v>
-      </c>
-      <c r="D304" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -5845,10 +5872,10 @@
         <v>249</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>229</v>
+        <v>7</v>
       </c>
       <c r="C305" s="6">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="D305" t="s">
         <v>8</v>
@@ -5859,10 +5886,10 @@
         <v>249</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>230</v>
+        <v>9</v>
       </c>
       <c r="C306" s="6">
-        <v>28.5</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="D306" t="s">
         <v>8</v>
@@ -5873,10 +5900,10 @@
         <v>249</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>231</v>
+        <v>10</v>
       </c>
       <c r="C307" s="6">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="D307" t="s">
         <v>8</v>
@@ -5887,10 +5914,10 @@
         <v>249</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C308" s="6">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="D308" t="s">
         <v>8</v>
@@ -5901,10 +5928,10 @@
         <v>249</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>233</v>
+        <v>11</v>
       </c>
       <c r="C309" s="6">
-        <v>36.5</v>
+        <v>14.99</v>
       </c>
       <c r="D309" t="s">
         <v>8</v>
@@ -5915,7 +5942,7 @@
         <v>249</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="C310" s="6">
         <v>16.5</v>
@@ -5928,28 +5955,28 @@
       <c r="A311" t="s">
         <v>249</v>
       </c>
-      <c r="B311" t="s">
-        <v>48</v>
+      <c r="B311" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C311" s="6">
-        <v>42.9</v>
+        <v>17.97</v>
       </c>
       <c r="D311" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>249</v>
       </c>
-      <c r="B312" t="s">
-        <v>52</v>
+      <c r="B312" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="C312" s="6">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="D312" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -5957,13 +5984,13 @@
         <v>249</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
       <c r="C313" s="6">
-        <v>98.5</v>
+        <v>28.5</v>
       </c>
       <c r="D313" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -5971,13 +5998,13 @@
         <v>249</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>56</v>
+        <v>231</v>
       </c>
       <c r="C314" s="6">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="D314" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -5985,13 +6012,13 @@
         <v>249</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>57</v>
+        <v>232</v>
       </c>
       <c r="C315" s="6">
-        <v>98.5</v>
+        <v>30</v>
       </c>
       <c r="D315" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -5999,13 +6026,13 @@
         <v>249</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>58</v>
+        <v>233</v>
       </c>
       <c r="C316" s="6">
-        <v>105</v>
+        <v>36.5</v>
       </c>
       <c r="D316" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -6013,41 +6040,41 @@
         <v>249</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
       <c r="C317" s="6">
-        <v>142</v>
+        <v>16.5</v>
       </c>
       <c r="D317" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>249</v>
       </c>
-      <c r="B318" s="3" t="s">
-        <v>60</v>
+      <c r="B318" t="s">
+        <v>48</v>
       </c>
       <c r="C318" s="6">
-        <v>170</v>
+        <v>42.9</v>
       </c>
       <c r="D318" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>249</v>
       </c>
-      <c r="B319" s="3" t="s">
-        <v>61</v>
+      <c r="B319" t="s">
+        <v>52</v>
       </c>
       <c r="C319" s="6">
-        <v>234</v>
+        <v>42.9</v>
       </c>
       <c r="D319" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -6055,10 +6082,10 @@
         <v>249</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C320" s="6">
-        <v>255</v>
+        <v>98.5</v>
       </c>
       <c r="D320" t="s">
         <v>55</v>
@@ -6069,10 +6096,10 @@
         <v>249</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C321" s="6">
-        <v>265</v>
+        <v>105</v>
       </c>
       <c r="D321" t="s">
         <v>55</v>
@@ -6083,10 +6110,10 @@
         <v>249</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C322" s="6">
-        <v>140</v>
+        <v>98.5</v>
       </c>
       <c r="D322" t="s">
         <v>55</v>
@@ -6097,10 +6124,10 @@
         <v>249</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>251</v>
+        <v>58</v>
       </c>
       <c r="C323" s="6">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D323" t="s">
         <v>55</v>
@@ -6111,10 +6138,10 @@
         <v>249</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C324" s="6">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="D324" t="s">
         <v>55</v>
@@ -6125,13 +6152,13 @@
         <v>249</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C325" s="6">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="D325" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6139,13 +6166,13 @@
         <v>249</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C326" s="6">
-        <v>475</v>
+        <v>234</v>
       </c>
       <c r="D326" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -6153,10 +6180,13 @@
         <v>249</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>252</v>
+        <v>62</v>
+      </c>
+      <c r="C327" s="6">
+        <v>255</v>
       </c>
       <c r="D327" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -6164,13 +6194,13 @@
         <v>249</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="C328" s="6">
-        <v>15.58</v>
+        <v>265</v>
       </c>
       <c r="D328" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -6178,13 +6208,13 @@
         <v>249</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="C329" s="6">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="D329" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -6192,13 +6222,13 @@
         <v>249</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>111</v>
+        <v>251</v>
       </c>
       <c r="C330" s="6">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D330" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -6206,13 +6236,13 @@
         <v>249</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="C331" s="6">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D331" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -6220,55 +6250,52 @@
         <v>249</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="C332" s="6">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="D332" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>249</v>
       </c>
-      <c r="B333" t="s">
-        <v>114</v>
+      <c r="B333" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="C333" s="6">
-        <v>16</v>
+        <v>475</v>
       </c>
       <c r="D333" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>249</v>
       </c>
-      <c r="B334" t="s">
-        <v>115</v>
-      </c>
-      <c r="C334" s="6">
-        <v>28</v>
+      <c r="B334" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="D334" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>249</v>
       </c>
-      <c r="B335" t="s">
-        <v>116</v>
+      <c r="B335" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="C335" s="6">
-        <v>102</v>
+        <v>15.58</v>
       </c>
       <c r="D335" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -6276,13 +6303,13 @@
         <v>249</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C336" s="6">
-        <v>33.5</v>
+        <v>12</v>
       </c>
       <c r="D336" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -6290,27 +6317,27 @@
         <v>249</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C337" s="6">
-        <v>15.1</v>
+        <v>21</v>
       </c>
       <c r="D337" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>249</v>
       </c>
-      <c r="B338" t="s">
-        <v>120</v>
+      <c r="B338" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C338" s="6">
-        <v>38.28</v>
+        <v>40</v>
       </c>
       <c r="D338" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -6318,58 +6345,55 @@
         <v>249</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C339" s="6">
-        <v>22.36</v>
+        <v>80</v>
       </c>
       <c r="D339" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>249</v>
       </c>
-      <c r="B340" s="3" t="s">
-        <v>254</v>
+      <c r="B340" t="s">
+        <v>114</v>
       </c>
       <c r="C340" s="6">
-        <v>23.68</v>
+        <v>16</v>
       </c>
       <c r="D340" t="s">
-        <v>118</v>
-      </c>
-      <c r="E340" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>249</v>
       </c>
-      <c r="B341" s="3" t="s">
-        <v>124</v>
+      <c r="B341" t="s">
+        <v>115</v>
       </c>
       <c r="C341" s="6">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D341" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>249</v>
       </c>
-      <c r="B342" s="3" t="s">
-        <v>255</v>
+      <c r="B342" t="s">
+        <v>116</v>
       </c>
       <c r="C342" s="6">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D342" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
@@ -6377,13 +6401,13 @@
         <v>249</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>256</v>
+        <v>117</v>
       </c>
       <c r="C343" s="6">
-        <v>225</v>
+        <v>33.5</v>
       </c>
       <c r="D343" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
@@ -6391,24 +6415,27 @@
         <v>249</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="C344" s="6">
-        <v>421.08</v>
+        <v>15.1</v>
       </c>
       <c r="D344" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>249</v>
       </c>
-      <c r="B345" s="3" t="s">
-        <v>158</v>
+      <c r="B345" t="s">
+        <v>120</v>
+      </c>
+      <c r="C345" s="6">
+        <v>38.28</v>
       </c>
       <c r="D345" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -6416,13 +6443,13 @@
         <v>249</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C346" s="6">
-        <v>60</v>
+        <v>22.36</v>
       </c>
       <c r="D346" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -6430,16 +6457,16 @@
         <v>249</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C347">
-        <v>6.25</v>
+        <v>254</v>
+      </c>
+      <c r="C347" s="6">
+        <v>23.68</v>
       </c>
       <c r="D347" t="s">
-        <v>156</v>
-      </c>
-      <c r="E347" t="s">
-        <v>159</v>
+        <v>118</v>
+      </c>
+      <c r="E347" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -6447,44 +6474,41 @@
         <v>249</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C348">
-        <v>6.75</v>
+        <v>124</v>
+      </c>
+      <c r="C348" s="6">
+        <v>10</v>
       </c>
       <c r="D348" t="s">
-        <v>156</v>
-      </c>
-      <c r="E348" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>249</v>
       </c>
-      <c r="B349" s="3">
-        <v>4430</v>
+      <c r="B349" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="C349" s="6">
-        <v>15.25</v>
+        <v>87</v>
       </c>
       <c r="D349" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>249</v>
       </c>
-      <c r="B350" s="3">
-        <v>4442</v>
+      <c r="B350" s="3" t="s">
+        <v>256</v>
       </c>
       <c r="C350" s="6">
-        <v>18.899999999999999</v>
+        <v>225</v>
       </c>
       <c r="D350" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -6492,13 +6516,13 @@
         <v>249</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>161</v>
+        <v>257</v>
       </c>
       <c r="C351" s="6">
-        <v>193</v>
+        <v>421.08</v>
       </c>
       <c r="D351" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
@@ -6506,228 +6530,231 @@
         <v>249</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D352" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>249</v>
       </c>
-      <c r="B353" s="3">
-        <v>4642</v>
+      <c r="B353" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="C353" s="6">
-        <v>20.8</v>
+        <v>60</v>
       </c>
       <c r="D353" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>249</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
+      </c>
+      <c r="C354">
+        <v>6.25</v>
       </c>
       <c r="D354" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E354" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>249</v>
       </c>
-      <c r="B355" s="3">
-        <v>4660</v>
-      </c>
-      <c r="C355" s="6">
-        <v>24.7</v>
+      <c r="B355" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C355">
+        <v>6.75</v>
       </c>
       <c r="D355" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E355" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>249</v>
       </c>
       <c r="B356" s="3">
-        <v>6642</v>
+        <v>4430</v>
       </c>
       <c r="C356" s="6">
-        <v>26.8</v>
+        <v>15.25</v>
       </c>
       <c r="D356" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>249</v>
       </c>
-      <c r="B357" s="3" t="s">
-        <v>164</v>
+      <c r="B357" s="3">
+        <v>4442</v>
       </c>
       <c r="C357" s="6">
-        <v>115</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D357" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>249</v>
       </c>
-      <c r="B358" s="3">
-        <v>6660</v>
+      <c r="B358" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="C358" s="6">
-        <v>27.05</v>
+        <v>193</v>
       </c>
       <c r="D358" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>249</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C359" s="6">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D359" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>249</v>
       </c>
-      <c r="B360" s="3" t="s">
-        <v>258</v>
+      <c r="B360" s="3">
+        <v>4642</v>
       </c>
       <c r="C360" s="6">
-        <v>30.5</v>
+        <v>20.8</v>
       </c>
       <c r="D360" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>249</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C361" s="6">
-        <v>12.75</v>
+        <v>163</v>
       </c>
       <c r="D361" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>249</v>
       </c>
-      <c r="B362" s="3" t="s">
-        <v>180</v>
+      <c r="B362" s="3">
+        <v>4660</v>
       </c>
       <c r="C362" s="6">
-        <v>12.75</v>
+        <v>24.7</v>
       </c>
       <c r="D362" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>249</v>
       </c>
-      <c r="B363" s="3" t="s">
-        <v>182</v>
+      <c r="B363" s="3">
+        <v>6642</v>
       </c>
       <c r="C363" s="6">
-        <v>13.25</v>
+        <v>26.8</v>
       </c>
       <c r="D363" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>249</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C364" s="6">
-        <v>10.3</v>
+        <v>115</v>
       </c>
       <c r="D364" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>249</v>
       </c>
-      <c r="B365" s="3" t="s">
-        <v>178</v>
+      <c r="B365" s="3">
+        <v>6660</v>
       </c>
       <c r="C365" s="6">
-        <v>11.85</v>
+        <v>27.05</v>
       </c>
       <c r="D365" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>249</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="C366" s="6">
-        <v>12.75</v>
+        <v>160</v>
       </c>
       <c r="D366" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>249</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>183</v>
+        <v>258</v>
       </c>
       <c r="C367" s="6">
-        <v>10.3</v>
+        <v>30.5</v>
       </c>
       <c r="D367" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>249</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>184</v>
+        <v>259</v>
       </c>
       <c r="C368" s="6">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="D368" t="s">
         <v>179</v>
@@ -6738,7 +6765,7 @@
         <v>249</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="C369" s="6">
         <v>12.75</v>
@@ -6752,13 +6779,13 @@
         <v>249</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="C370" s="6">
-        <v>21.5</v>
+        <v>13.25</v>
       </c>
       <c r="D370" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -6766,13 +6793,13 @@
         <v>249</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C371" s="6">
-        <v>22.5</v>
+        <v>10.3</v>
       </c>
       <c r="D371" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -6780,13 +6807,13 @@
         <v>249</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="C372" s="6">
-        <v>10.5</v>
+        <v>11.85</v>
       </c>
       <c r="D372" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -6794,13 +6821,13 @@
         <v>249</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C373" s="6">
-        <v>10.5</v>
+        <v>12.75</v>
       </c>
       <c r="D373" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -6808,13 +6835,13 @@
         <v>249</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="C374" s="6">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="D374" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -6822,10 +6849,13 @@
         <v>249</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>237</v>
+        <v>184</v>
+      </c>
+      <c r="C375" s="6">
+        <v>13.25</v>
       </c>
       <c r="D375" t="s">
-        <v>238</v>
+        <v>179</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -6833,13 +6863,13 @@
         <v>249</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="C376" s="6">
-        <v>23</v>
+        <v>12.75</v>
       </c>
       <c r="D376" t="s">
-        <v>238</v>
+        <v>179</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -6847,10 +6877,13 @@
         <v>249</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>240</v>
+        <v>198</v>
+      </c>
+      <c r="C377" s="6">
+        <v>21.5</v>
       </c>
       <c r="D377" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -6858,13 +6891,13 @@
         <v>249</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C378" s="6">
-        <v>23.15</v>
+        <v>22.5</v>
       </c>
       <c r="D378" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -6872,13 +6905,13 @@
         <v>249</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C379" s="6">
-        <v>42.65</v>
+        <v>10.5</v>
       </c>
       <c r="D379" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -6886,13 +6919,13 @@
         <v>249</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C380" s="6">
-        <v>82</v>
+        <v>10.5</v>
       </c>
       <c r="D380" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -6900,13 +6933,13 @@
         <v>249</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C381" s="6">
-        <v>33.5</v>
+        <v>10.5</v>
       </c>
       <c r="D381" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -6914,13 +6947,10 @@
         <v>249</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C382" s="6">
-        <v>60.9</v>
+        <v>237</v>
       </c>
       <c r="D382" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -6928,13 +6958,13 @@
         <v>249</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C383" s="6">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="D383" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -6942,13 +6972,10 @@
         <v>249</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C384" s="6">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="D384" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
@@ -6956,10 +6983,10 @@
         <v>249</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C385" s="6">
-        <v>16</v>
+        <v>23.15</v>
       </c>
       <c r="D385" t="s">
         <v>211</v>
@@ -6970,10 +6997,10 @@
         <v>249</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C386" s="6">
-        <v>21.32</v>
+        <v>42.65</v>
       </c>
       <c r="D386" t="s">
         <v>211</v>
@@ -6984,13 +7011,13 @@
         <v>249</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C387" s="6">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="D387" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
@@ -6998,16 +7025,13 @@
         <v>249</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C388">
-        <v>7.5</v>
+        <v>214</v>
+      </c>
+      <c r="C388" s="6">
+        <v>33.5</v>
       </c>
       <c r="D388" t="s">
-        <v>221</v>
-      </c>
-      <c r="E388" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -7015,13 +7039,13 @@
         <v>249</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C389" s="6">
-        <v>13.42</v>
+        <v>60.9</v>
       </c>
       <c r="D389" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
@@ -7029,10 +7053,13 @@
         <v>249</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>224</v>
+        <v>216</v>
+      </c>
+      <c r="C390" s="6">
+        <v>118</v>
       </c>
       <c r="D390" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
@@ -7040,10 +7067,13 @@
         <v>249</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
+      </c>
+      <c r="C391" s="6">
+        <v>16</v>
       </c>
       <c r="D391" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
@@ -7051,111 +7081,108 @@
         <v>249</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C392" s="6">
-        <v>9.5399999999999991</v>
+        <v>16</v>
       </c>
       <c r="D392" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>249</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C393" s="6">
+        <v>21.32</v>
+      </c>
+      <c r="D393" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>249</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C394" s="6">
+        <v>26</v>
+      </c>
+      <c r="D394" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C395" s="6">
-        <v>14.5</v>
+        <v>222</v>
+      </c>
+      <c r="C395">
+        <v>7.5</v>
       </c>
       <c r="D395" t="s">
-        <v>262</v>
+        <v>221</v>
+      </c>
+      <c r="E395" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>24</v>
+        <v>223</v>
       </c>
       <c r="C396" s="6">
-        <v>24.99</v>
+        <v>13.42</v>
       </c>
       <c r="D396" t="s">
-        <v>25</v>
+        <v>221</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C397" s="6">
-        <v>34.99</v>
+        <v>224</v>
       </c>
       <c r="D397" t="s">
-        <v>25</v>
+        <v>221</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C398" s="6">
-        <v>19.989999999999998</v>
+        <v>225</v>
       </c>
       <c r="D398" t="s">
-        <v>43</v>
+        <v>221</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="C399" s="6">
-        <v>29.99</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="D399" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A400" t="s">
-        <v>261</v>
-      </c>
-      <c r="B400" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C400" s="6">
-        <v>189.99</v>
-      </c>
-      <c r="D400" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A401" t="s">
-        <v>261</v>
-      </c>
-      <c r="B401" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C401" s="6">
-        <v>229.99</v>
-      </c>
-      <c r="D401" t="s">
-        <v>55</v>
+        <v>221</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -7163,13 +7190,13 @@
         <v>261</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C402" s="6">
-        <v>299.99</v>
+        <v>14.5</v>
       </c>
       <c r="D402" t="s">
-        <v>55</v>
+        <v>262</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -7177,13 +7204,13 @@
         <v>261</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C403" s="6">
-        <v>189.99</v>
+        <v>24.99</v>
       </c>
       <c r="D403" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -7191,13 +7218,13 @@
         <v>261</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C404" s="6">
-        <v>229</v>
+        <v>34.99</v>
       </c>
       <c r="D404" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -7205,13 +7232,13 @@
         <v>261</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>264</v>
+        <v>42</v>
       </c>
       <c r="C405" s="6">
-        <v>299.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D405" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -7219,13 +7246,13 @@
         <v>261</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C406" s="6">
-        <v>309</v>
+        <v>29.99</v>
       </c>
       <c r="D406" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -7233,10 +7260,10 @@
         <v>261</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C407" s="6">
-        <v>345</v>
+        <v>189.99</v>
       </c>
       <c r="D407" t="s">
         <v>55</v>
@@ -7247,10 +7274,10 @@
         <v>261</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C408" s="6">
-        <v>409</v>
+        <v>229.99</v>
       </c>
       <c r="D408" t="s">
         <v>55</v>
@@ -7261,10 +7288,10 @@
         <v>261</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>62</v>
+        <v>263</v>
       </c>
       <c r="C409" s="6">
-        <v>389</v>
+        <v>299.99</v>
       </c>
       <c r="D409" t="s">
         <v>55</v>
@@ -7275,10 +7302,10 @@
         <v>261</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="C410" s="6">
-        <v>389.99</v>
+        <v>189.99</v>
       </c>
       <c r="D410" t="s">
         <v>55</v>
@@ -7289,10 +7316,10 @@
         <v>261</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C411" s="6">
-        <v>399.99</v>
+        <v>229</v>
       </c>
       <c r="D411" t="s">
         <v>55</v>
@@ -7303,10 +7330,10 @@
         <v>261</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C412" s="6">
-        <v>399.99</v>
+        <v>299.99</v>
       </c>
       <c r="D412" t="s">
         <v>55</v>
@@ -7317,10 +7344,10 @@
         <v>261</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C413" s="6">
-        <v>89.23</v>
+        <v>309</v>
       </c>
       <c r="D413" t="s">
         <v>55</v>
@@ -7331,7 +7358,10 @@
         <v>261</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
+      </c>
+      <c r="C414" s="6">
+        <v>345</v>
       </c>
       <c r="D414" t="s">
         <v>55</v>
@@ -7342,10 +7372,10 @@
         <v>261</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C415" s="6">
-        <v>219.99</v>
+        <v>409</v>
       </c>
       <c r="D415" t="s">
         <v>55</v>
@@ -7356,10 +7386,10 @@
         <v>261</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>267</v>
+        <v>62</v>
       </c>
       <c r="C416" s="6">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="D416" t="s">
         <v>55</v>
@@ -7370,10 +7400,10 @@
         <v>261</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C417" s="6">
-        <v>439</v>
+        <v>389.99</v>
       </c>
       <c r="D417" t="s">
         <v>55</v>
@@ -7384,10 +7414,10 @@
         <v>261</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>269</v>
+        <v>63</v>
       </c>
       <c r="C418" s="6">
-        <v>199</v>
+        <v>399.99</v>
       </c>
       <c r="D418" t="s">
         <v>55</v>
@@ -7398,10 +7428,10 @@
         <v>261</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C419" s="6">
-        <v>249</v>
+        <v>399.99</v>
       </c>
       <c r="D419" t="s">
         <v>55</v>
@@ -7412,10 +7442,10 @@
         <v>261</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>271</v>
+        <v>66</v>
       </c>
       <c r="C420" s="6">
-        <v>670</v>
+        <v>89.23</v>
       </c>
       <c r="D420" t="s">
         <v>55</v>
@@ -7426,10 +7456,7 @@
         <v>261</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C421" s="6">
-        <v>49.99</v>
+        <v>65</v>
       </c>
       <c r="D421" t="s">
         <v>55</v>
@@ -7440,10 +7467,10 @@
         <v>261</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>273</v>
+        <v>64</v>
       </c>
       <c r="C422" s="6">
-        <v>49.99</v>
+        <v>219.99</v>
       </c>
       <c r="D422" t="s">
         <v>55</v>
@@ -7454,13 +7481,13 @@
         <v>261</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C423" s="6">
-        <v>15.99</v>
+        <v>429</v>
       </c>
       <c r="D423" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -7468,13 +7495,13 @@
         <v>261</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C424" s="6">
-        <v>29.99</v>
+        <v>439</v>
       </c>
       <c r="D424" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -7482,13 +7509,13 @@
         <v>261</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C425" s="6">
-        <v>16.989999999999998</v>
+        <v>199</v>
       </c>
       <c r="D425" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
@@ -7496,13 +7523,13 @@
         <v>261</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C426" s="6">
-        <v>29.99</v>
+        <v>249</v>
       </c>
       <c r="D426" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -7510,13 +7537,13 @@
         <v>261</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C427" s="6">
-        <v>11.49</v>
+        <v>670</v>
       </c>
       <c r="D427" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
@@ -7524,13 +7551,13 @@
         <v>261</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C428" s="6">
-        <v>18.95</v>
+        <v>49.99</v>
       </c>
       <c r="D428" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
@@ -7538,24 +7565,24 @@
         <v>261</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C429" s="6">
-        <v>39.99</v>
+        <v>49.99</v>
       </c>
       <c r="D429" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>261</v>
       </c>
-      <c r="B430" s="3">
-        <v>6102</v>
+      <c r="B430" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="C430" s="6">
-        <v>44.5</v>
+        <v>15.99</v>
       </c>
       <c r="D430" t="s">
         <v>79</v>
@@ -7566,10 +7593,10 @@
         <v>261</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C431" s="6">
-        <v>112</v>
+        <v>29.99</v>
       </c>
       <c r="D431" t="s">
         <v>79</v>
@@ -7580,10 +7607,10 @@
         <v>261</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C432" s="6">
-        <v>139</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D432" t="s">
         <v>79</v>
@@ -7594,10 +7621,10 @@
         <v>261</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C433" s="6">
-        <v>139</v>
+        <v>29.99</v>
       </c>
       <c r="D433" t="s">
         <v>79</v>
@@ -7608,7 +7635,10 @@
         <v>261</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
+      </c>
+      <c r="C434" s="6">
+        <v>11.49</v>
       </c>
       <c r="D434" t="s">
         <v>79</v>
@@ -7619,7 +7649,10 @@
         <v>261</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
+      </c>
+      <c r="C435" s="6">
+        <v>18.95</v>
       </c>
       <c r="D435" t="s">
         <v>79</v>
@@ -7630,10 +7663,10 @@
         <v>261</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C436" s="6">
-        <v>209</v>
+        <v>39.99</v>
       </c>
       <c r="D436" t="s">
         <v>79</v>
@@ -7643,8 +7676,11 @@
       <c r="A437" t="s">
         <v>261</v>
       </c>
-      <c r="B437" s="3" t="s">
-        <v>287</v>
+      <c r="B437" s="3">
+        <v>6102</v>
+      </c>
+      <c r="C437" s="6">
+        <v>44.5</v>
       </c>
       <c r="D437" t="s">
         <v>79</v>
@@ -7655,7 +7691,10 @@
         <v>261</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
+      </c>
+      <c r="C438" s="6">
+        <v>112</v>
       </c>
       <c r="D438" t="s">
         <v>79</v>
@@ -7666,10 +7705,10 @@
         <v>261</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C439" s="6">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D439" t="s">
         <v>79</v>
@@ -7680,10 +7719,10 @@
         <v>261</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C440" s="6">
-        <v>299.99</v>
+        <v>139</v>
       </c>
       <c r="D440" t="s">
         <v>79</v>
@@ -7694,10 +7733,7 @@
         <v>261</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C441" s="6">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D441" t="s">
         <v>79</v>
@@ -7708,10 +7744,7 @@
         <v>261</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C442" s="6">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="D442" t="s">
         <v>79</v>
@@ -7722,10 +7755,10 @@
         <v>261</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>99</v>
+        <v>286</v>
       </c>
       <c r="C443" s="6">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="D443" t="s">
         <v>79</v>
@@ -7736,10 +7769,7 @@
         <v>261</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C444" s="6">
-        <v>399</v>
+        <v>287</v>
       </c>
       <c r="D444" t="s">
         <v>79</v>
@@ -7750,10 +7780,7 @@
         <v>261</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C445" s="6">
-        <v>209</v>
+        <v>288</v>
       </c>
       <c r="D445" t="s">
         <v>79</v>
@@ -7764,10 +7791,10 @@
         <v>261</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>97</v>
+        <v>289</v>
       </c>
       <c r="C446" s="6">
-        <v>345</v>
+        <v>179</v>
       </c>
       <c r="D446" t="s">
         <v>79</v>
@@ -7778,10 +7805,10 @@
         <v>261</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>88</v>
+        <v>290</v>
       </c>
       <c r="C447" s="6">
-        <v>209</v>
+        <v>299.99</v>
       </c>
       <c r="D447" t="s">
         <v>79</v>
@@ -7792,10 +7819,10 @@
         <v>261</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C448" s="6">
-        <v>369</v>
+        <v>220</v>
       </c>
       <c r="D448" t="s">
         <v>79</v>
@@ -7806,10 +7833,10 @@
         <v>261</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C449" s="6">
-        <v>315</v>
+        <v>245</v>
       </c>
       <c r="D449" t="s">
         <v>79</v>
@@ -7820,10 +7847,10 @@
         <v>261</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>291</v>
+        <v>99</v>
       </c>
       <c r="C450" s="6">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="D450" t="s">
         <v>79</v>
@@ -7834,10 +7861,10 @@
         <v>261</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C451" s="6">
-        <v>251</v>
+        <v>399</v>
       </c>
       <c r="D451" t="s">
         <v>79</v>
@@ -7848,10 +7875,10 @@
         <v>261</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C452" s="6">
-        <v>420</v>
+        <v>209</v>
       </c>
       <c r="D452" t="s">
         <v>79</v>
@@ -7862,10 +7889,10 @@
         <v>261</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C453" s="6">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="D453" t="s">
         <v>79</v>
@@ -7876,10 +7903,10 @@
         <v>261</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C454" s="6">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="D454" t="s">
         <v>79</v>
@@ -7890,10 +7917,10 @@
         <v>261</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C455" s="6">
-        <v>285</v>
+        <v>369</v>
       </c>
       <c r="D455" t="s">
         <v>79</v>
@@ -7904,13 +7931,13 @@
         <v>261</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C456" s="6">
-        <v>55.99</v>
+        <v>315</v>
       </c>
       <c r="D456" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
@@ -7918,13 +7945,13 @@
         <v>261</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="C457" s="6">
-        <v>39.99</v>
+        <v>265</v>
       </c>
       <c r="D457" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
@@ -7932,13 +7959,13 @@
         <v>261</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C458" s="6">
-        <v>68</v>
+        <v>251</v>
       </c>
       <c r="D458" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
@@ -7946,13 +7973,13 @@
         <v>261</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C459" s="6">
-        <v>129</v>
+        <v>420</v>
       </c>
       <c r="D459" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
@@ -7960,13 +7987,13 @@
         <v>261</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C460" s="6">
-        <v>30.99</v>
+        <v>315</v>
       </c>
       <c r="D460" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
@@ -7974,13 +8001,13 @@
         <v>261</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="C461" s="6">
-        <v>42.99</v>
+        <v>365</v>
       </c>
       <c r="D461" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
@@ -7988,13 +8015,13 @@
         <v>261</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C462" s="6">
-        <v>159</v>
+        <v>285</v>
       </c>
       <c r="D462" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -8002,10 +8029,10 @@
         <v>261</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>292</v>
+        <v>108</v>
       </c>
       <c r="C463" s="6">
-        <v>49.99</v>
+        <v>55.99</v>
       </c>
       <c r="D463" t="s">
         <v>109</v>
@@ -8016,10 +8043,10 @@
         <v>261</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>293</v>
+        <v>111</v>
       </c>
       <c r="C464" s="6">
-        <v>129</v>
+        <v>39.99</v>
       </c>
       <c r="D464" t="s">
         <v>109</v>
@@ -8030,13 +8057,13 @@
         <v>261</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C465" s="6">
-        <v>47.99</v>
+        <v>68</v>
       </c>
       <c r="D465" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -8044,13 +8071,13 @@
         <v>261</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="C466" s="6">
-        <v>34.99</v>
+        <v>129</v>
       </c>
       <c r="D466" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
@@ -8058,13 +8085,13 @@
         <v>261</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="C467" s="6">
-        <v>89.99</v>
+        <v>30.99</v>
       </c>
       <c r="D467" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -8072,13 +8099,13 @@
         <v>261</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>258</v>
+        <v>115</v>
       </c>
       <c r="C468" s="6">
-        <v>45</v>
+        <v>42.99</v>
       </c>
       <c r="D468" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
@@ -8086,13 +8113,13 @@
         <v>261</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>295</v>
+        <v>116</v>
       </c>
       <c r="C469" s="6">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="D469" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -8100,13 +8127,13 @@
         <v>261</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C470" s="6">
-        <v>125</v>
+        <v>49.99</v>
       </c>
       <c r="D470" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -8114,13 +8141,13 @@
         <v>261</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>195</v>
+        <v>293</v>
       </c>
       <c r="C471" s="6">
-        <v>79.989999999999995</v>
+        <v>129</v>
       </c>
       <c r="D471" t="s">
-        <v>196</v>
+        <v>109</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -8128,13 +8155,13 @@
         <v>261</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>297</v>
+        <v>117</v>
       </c>
       <c r="C472" s="6">
-        <v>7.95</v>
+        <v>47.99</v>
       </c>
       <c r="D472" t="s">
-        <v>238</v>
+        <v>118</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
@@ -8142,13 +8169,13 @@
         <v>261</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="C473" s="6">
-        <v>18.95</v>
+        <v>34.99</v>
       </c>
       <c r="D473" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -8156,13 +8183,13 @@
         <v>261</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>239</v>
+        <v>153</v>
       </c>
       <c r="C474" s="6">
-        <v>36.950000000000003</v>
+        <v>89.99</v>
       </c>
       <c r="D474" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -8170,13 +8197,13 @@
         <v>261</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="C475" s="6">
-        <v>39.99</v>
+        <v>45</v>
       </c>
       <c r="D475" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
@@ -8184,13 +8211,13 @@
         <v>261</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>27</v>
+        <v>295</v>
       </c>
       <c r="C476" s="6">
-        <v>19.5</v>
+        <v>88</v>
       </c>
       <c r="D476" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
@@ -8198,13 +8225,13 @@
         <v>261</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C477" s="6">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D477" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
@@ -8212,13 +8239,13 @@
         <v>261</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="C478" s="6">
-        <v>98.45</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D478" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
@@ -8226,13 +8253,13 @@
         <v>261</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C479" s="6">
-        <v>139</v>
+        <v>7.95</v>
       </c>
       <c r="D479" t="s">
-        <v>28</v>
+        <v>238</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
@@ -8240,13 +8267,13 @@
         <v>261</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="C480" s="6">
-        <v>199</v>
+        <v>18.95</v>
       </c>
       <c r="D480" t="s">
-        <v>28</v>
+        <v>238</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
@@ -8254,13 +8281,13 @@
         <v>261</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="C481" s="6">
-        <v>169.99</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D481" t="s">
-        <v>28</v>
+        <v>238</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
@@ -8268,13 +8295,13 @@
         <v>261</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>303</v>
+        <v>220</v>
       </c>
       <c r="C482" s="6">
-        <v>239.08</v>
+        <v>39.99</v>
       </c>
       <c r="D482" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
@@ -8282,10 +8309,10 @@
         <v>261</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>304</v>
+        <v>27</v>
       </c>
       <c r="C483" s="6">
-        <v>219</v>
+        <v>19.5</v>
       </c>
       <c r="D483" t="s">
         <v>28</v>
@@ -8296,10 +8323,10 @@
         <v>261</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C484" s="6">
-        <v>189.99</v>
+        <v>110</v>
       </c>
       <c r="D484" t="s">
         <v>28</v>
@@ -8310,10 +8337,10 @@
         <v>261</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C485" s="6">
-        <v>248</v>
+        <v>98.45</v>
       </c>
       <c r="D485" t="s">
         <v>28</v>
@@ -8324,10 +8351,10 @@
         <v>261</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C486" s="6">
-        <v>297</v>
+        <v>139</v>
       </c>
       <c r="D486" t="s">
         <v>28</v>
@@ -8338,230 +8365,230 @@
         <v>261</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C487" s="6">
-        <v>322</v>
+        <v>199</v>
       </c>
       <c r="D487" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>261</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C488" s="6">
+        <v>169.99</v>
+      </c>
+      <c r="D488" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>261</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C489" s="6">
+        <v>239.08</v>
+      </c>
+      <c r="D489" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>261</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C490" s="6">
+        <v>219</v>
+      </c>
+      <c r="D490" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>261</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C491" s="6">
+        <v>189.99</v>
+      </c>
+      <c r="D491" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>261</v>
+      </c>
+      <c r="B492" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C492" s="6">
+        <v>248</v>
+      </c>
+      <c r="D492" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>261</v>
+      </c>
+      <c r="B493" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C493" s="6">
+        <v>297</v>
+      </c>
+      <c r="D493" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>261</v>
+      </c>
+      <c r="B494" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C494" s="6">
+        <v>322</v>
+      </c>
+      <c r="D494" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
         <v>309</v>
       </c>
-      <c r="B497" s="3" t="s">
+      <c r="B504" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C497" s="6">
+      <c r="C504" s="6">
         <v>42.75</v>
       </c>
-      <c r="D497" t="s">
+      <c r="D504" t="s">
         <v>28</v>
       </c>
-      <c r="F497" s="7" t="s">
+      <c r="F504" s="7" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
         <v>309</v>
       </c>
-      <c r="B498" s="3" t="s">
+      <c r="B505" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C498" s="6">
+      <c r="C505" s="6">
         <v>79.47</v>
       </c>
-      <c r="D498" t="s">
+      <c r="D505" t="s">
         <v>28</v>
       </c>
-      <c r="F498" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
-        <v>309</v>
-      </c>
-      <c r="B499" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C499" s="6">
-        <v>92.85</v>
-      </c>
-      <c r="D499" t="s">
-        <v>28</v>
-      </c>
-      <c r="F499" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
-        <v>309</v>
-      </c>
-      <c r="B500" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C500" s="6">
-        <v>15.25</v>
-      </c>
-      <c r="D500" t="s">
-        <v>156</v>
-      </c>
-      <c r="F500" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
-        <v>309</v>
-      </c>
-      <c r="B501" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C501" s="6">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="D501" t="s">
-        <v>156</v>
-      </c>
-      <c r="F501" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>309</v>
-      </c>
-      <c r="B502" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C502" s="6">
-        <v>26.8</v>
-      </c>
-      <c r="D502" t="s">
-        <v>156</v>
-      </c>
-      <c r="F502" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>309</v>
-      </c>
-      <c r="B503" s="3">
-        <v>6660</v>
-      </c>
-      <c r="C503" s="6">
-        <v>27.05</v>
-      </c>
-      <c r="D503" t="s">
-        <v>156</v>
-      </c>
-      <c r="F503" s="7" t="s">
+      <c r="F505" s="7" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>29</v>
+        <v>313</v>
       </c>
       <c r="C506" s="6">
-        <v>47.95</v>
+        <v>92.85</v>
       </c>
       <c r="D506" t="s">
         <v>28</v>
       </c>
+      <c r="F506" s="7" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>314</v>
-      </c>
-      <c r="B507" s="3" t="s">
-        <v>30</v>
+        <v>309</v>
+      </c>
+      <c r="B507" s="3">
+        <v>4430</v>
       </c>
       <c r="C507" s="6">
-        <v>59.07</v>
+        <v>15.25</v>
       </c>
       <c r="D507" t="s">
-        <v>28</v>
+        <v>156</v>
+      </c>
+      <c r="F507" s="7" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>314</v>
-      </c>
-      <c r="B508" s="3" t="s">
-        <v>31</v>
+        <v>309</v>
+      </c>
+      <c r="B508" s="3">
+        <v>4442</v>
       </c>
       <c r="C508" s="6">
-        <v>83.8</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D508" t="s">
-        <v>28</v>
+        <v>156</v>
+      </c>
+      <c r="F508" s="7" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>314</v>
-      </c>
-      <c r="B509" s="3" t="s">
-        <v>32</v>
+        <v>309</v>
+      </c>
+      <c r="B509" s="3">
+        <v>6642</v>
       </c>
       <c r="C509" s="6">
-        <v>115.4</v>
+        <v>26.8</v>
       </c>
       <c r="D509" t="s">
-        <v>28</v>
+        <v>156</v>
+      </c>
+      <c r="F509" s="7" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>314</v>
-      </c>
-      <c r="B510" s="3" t="s">
-        <v>33</v>
+        <v>309</v>
+      </c>
+      <c r="B510" s="3">
+        <v>6660</v>
       </c>
       <c r="C510" s="6">
-        <v>107.15</v>
+        <v>27.05</v>
       </c>
       <c r="D510" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A511" t="s">
-        <v>314</v>
-      </c>
-      <c r="B511" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C511" s="6">
-        <v>13</v>
-      </c>
-      <c r="D511" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A512" t="s">
-        <v>314</v>
-      </c>
-      <c r="B512" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C512" s="6">
-        <v>17</v>
-      </c>
-      <c r="D512" t="s">
-        <v>43</v>
+        <v>156</v>
+      </c>
+      <c r="F510" s="7" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
@@ -8569,55 +8596,55 @@
         <v>314</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="C513" s="6">
-        <v>30</v>
+        <v>47.95</v>
       </c>
       <c r="D513" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>314</v>
       </c>
-      <c r="B514" s="3">
-        <v>4430</v>
+      <c r="B514" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C514" s="6">
-        <v>15.25</v>
+        <v>59.07</v>
       </c>
       <c r="D514" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>314</v>
       </c>
-      <c r="B515" s="3">
-        <v>4442</v>
+      <c r="B515" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C515" s="6">
-        <v>18.899999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="D515" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>314</v>
       </c>
-      <c r="B516" s="3">
-        <v>6642</v>
+      <c r="B516" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C516" s="6">
-        <v>26.8</v>
+        <v>115.4</v>
       </c>
       <c r="D516" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
@@ -8625,132 +8652,111 @@
         <v>314</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>193</v>
+        <v>33</v>
       </c>
       <c r="C517" s="6">
-        <v>39.950000000000003</v>
+        <v>107.15</v>
       </c>
       <c r="D517" t="s">
-        <v>194</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>314</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C518" s="6">
+        <v>13</v>
+      </c>
+      <c r="D518" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>314</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C519" s="6">
+        <v>17</v>
+      </c>
+      <c r="D519" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>316</v>
+        <v>117</v>
       </c>
       <c r="C520" s="6">
-        <v>9.92</v>
+        <v>30</v>
       </c>
       <c r="D520" t="s">
-        <v>317</v>
-      </c>
-      <c r="F520" s="7" t="s">
-        <v>318</v>
+        <v>118</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>315</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>29</v>
+        <v>314</v>
+      </c>
+      <c r="B521" s="3">
+        <v>4430</v>
       </c>
       <c r="C521" s="6">
-        <v>47.95</v>
+        <v>15.25</v>
       </c>
       <c r="D521" t="s">
-        <v>28</v>
-      </c>
-      <c r="F521" s="7" t="s">
-        <v>318</v>
+        <v>156</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>315</v>
-      </c>
-      <c r="B522" s="3" t="s">
-        <v>30</v>
+        <v>314</v>
+      </c>
+      <c r="B522" s="3">
+        <v>4442</v>
       </c>
       <c r="C522" s="6">
-        <v>55.73</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D522" t="s">
-        <v>28</v>
-      </c>
-      <c r="F522" s="7" t="s">
-        <v>318</v>
+        <v>156</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>315</v>
-      </c>
-      <c r="B523" s="3" t="s">
-        <v>31</v>
+        <v>314</v>
+      </c>
+      <c r="B523" s="3">
+        <v>6642</v>
       </c>
       <c r="C523" s="6">
-        <v>79.06</v>
+        <v>26.8</v>
       </c>
       <c r="D523" t="s">
-        <v>28</v>
-      </c>
-      <c r="F523" s="7" t="s">
-        <v>318</v>
+        <v>156</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="C524" s="6">
-        <v>108.86</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="D524" t="s">
-        <v>28</v>
-      </c>
-      <c r="F524" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A525" t="s">
-        <v>315</v>
-      </c>
-      <c r="B525" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C525" s="6">
-        <v>101.09</v>
-      </c>
-      <c r="D525" t="s">
-        <v>28</v>
-      </c>
-      <c r="F525" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A526" t="s">
-        <v>315</v>
-      </c>
-      <c r="B526" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C526" s="6">
-        <v>160.69999999999999</v>
-      </c>
-      <c r="D526" t="s">
-        <v>28</v>
-      </c>
-      <c r="F526" s="7" t="s">
-        <v>318</v>
+        <v>194</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
@@ -8758,13 +8764,13 @@
         <v>315</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>35</v>
+        <v>316</v>
       </c>
       <c r="C527" s="6">
-        <v>121.82</v>
+        <v>9.92</v>
       </c>
       <c r="D527" t="s">
-        <v>28</v>
+        <v>317</v>
       </c>
       <c r="F527" s="7" t="s">
         <v>318</v>
@@ -8775,10 +8781,10 @@
         <v>315</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C528" s="6">
-        <v>122.49</v>
+        <v>47.95</v>
       </c>
       <c r="D528" t="s">
         <v>28</v>
@@ -8792,7 +8798,10 @@
         <v>315</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
+      </c>
+      <c r="C529" s="6">
+        <v>55.73</v>
       </c>
       <c r="D529" t="s">
         <v>28</v>
@@ -8806,7 +8815,10 @@
         <v>315</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="C530" s="6">
+        <v>79.06</v>
       </c>
       <c r="D530" t="s">
         <v>28</v>
@@ -8820,7 +8832,10 @@
         <v>315</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="C531" s="6">
+        <v>108.86</v>
       </c>
       <c r="D531" t="s">
         <v>28</v>
@@ -8834,10 +8849,10 @@
         <v>315</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>310</v>
+        <v>33</v>
       </c>
       <c r="C532" s="6">
-        <v>44</v>
+        <v>101.09</v>
       </c>
       <c r="D532" t="s">
         <v>28</v>
@@ -8851,10 +8866,10 @@
         <v>315</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>312</v>
+        <v>34</v>
       </c>
       <c r="C533" s="6">
-        <v>67</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="D533" t="s">
         <v>28</v>
@@ -8868,10 +8883,10 @@
         <v>315</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="C534" s="6">
-        <v>79</v>
+        <v>121.82</v>
       </c>
       <c r="D534" t="s">
         <v>28</v>
@@ -8885,13 +8900,13 @@
         <v>315</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>158</v>
+        <v>36</v>
       </c>
       <c r="C535" s="6">
-        <v>69.900000000000006</v>
+        <v>122.49</v>
       </c>
       <c r="D535" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F535" s="7" t="s">
         <v>318</v>
@@ -8901,14 +8916,11 @@
       <c r="A536" t="s">
         <v>315</v>
       </c>
-      <c r="B536" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C536" s="6">
-        <v>15.25</v>
+      <c r="B536" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="D536" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F536" s="7" t="s">
         <v>318</v>
@@ -8918,14 +8930,11 @@
       <c r="A537" t="s">
         <v>315</v>
       </c>
-      <c r="B537" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C537" s="6">
-        <v>15</v>
+      <c r="B537" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="D537" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F537" s="7" t="s">
         <v>318</v>
@@ -8936,13 +8945,10 @@
         <v>315</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C538" s="6">
-        <v>171</v>
+        <v>41</v>
       </c>
       <c r="D538" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F538" s="7" t="s">
         <v>318</v>
@@ -8953,10 +8959,13 @@
         <v>315</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>162</v>
+        <v>310</v>
+      </c>
+      <c r="C539" s="6">
+        <v>44</v>
       </c>
       <c r="D539" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F539" s="7" t="s">
         <v>318</v>
@@ -8966,14 +8975,14 @@
       <c r="A540" t="s">
         <v>315</v>
       </c>
-      <c r="B540" s="3">
-        <v>4642</v>
+      <c r="B540" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="C540" s="6">
-        <v>16.5</v>
+        <v>67</v>
       </c>
       <c r="D540" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F540" s="7" t="s">
         <v>318</v>
@@ -8984,13 +8993,13 @@
         <v>315</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="C541" s="6">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="D541" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F541" s="7" t="s">
         <v>318</v>
@@ -9000,11 +9009,11 @@
       <c r="A542" t="s">
         <v>315</v>
       </c>
-      <c r="B542" s="3">
-        <v>4660</v>
+      <c r="B542" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="C542" s="6">
-        <v>20.25</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="D542" t="s">
         <v>156</v>
@@ -9018,10 +9027,10 @@
         <v>315</v>
       </c>
       <c r="B543" s="3">
-        <v>6630</v>
+        <v>4430</v>
       </c>
       <c r="C543" s="6">
-        <v>20</v>
+        <v>15.25</v>
       </c>
       <c r="D543" t="s">
         <v>156</v>
@@ -9035,10 +9044,10 @@
         <v>315</v>
       </c>
       <c r="B544" s="3">
-        <v>6642</v>
+        <v>4442</v>
       </c>
       <c r="C544" s="6">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="D544" t="s">
         <v>156</v>
@@ -9052,10 +9061,10 @@
         <v>315</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C545" s="6">
-        <v>103.5</v>
+        <v>171</v>
       </c>
       <c r="D545" t="s">
         <v>156</v>
@@ -9068,11 +9077,8 @@
       <c r="A546" t="s">
         <v>315</v>
       </c>
-      <c r="B546" s="3">
-        <v>6660</v>
-      </c>
-      <c r="C546" s="6">
-        <v>22.5</v>
+      <c r="B546" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="D546" t="s">
         <v>156</v>
@@ -9085,11 +9091,11 @@
       <c r="A547" t="s">
         <v>315</v>
       </c>
-      <c r="B547" s="3" t="s">
-        <v>165</v>
+      <c r="B547" s="3">
+        <v>4642</v>
       </c>
       <c r="C547" s="6">
-        <v>126</v>
+        <v>16.5</v>
       </c>
       <c r="D547" t="s">
         <v>156</v>
@@ -9102,11 +9108,11 @@
       <c r="A548" t="s">
         <v>315</v>
       </c>
-      <c r="B548" s="3">
-        <v>8860</v>
+      <c r="B548" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C548" s="6">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="D548" t="s">
         <v>156</v>
@@ -9115,119 +9121,140 @@
         <v>318</v>
       </c>
     </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>315</v>
+      </c>
+      <c r="B549" s="3">
+        <v>4660</v>
+      </c>
+      <c r="C549" s="6">
+        <v>20.25</v>
+      </c>
+      <c r="D549" t="s">
+        <v>156</v>
+      </c>
+      <c r="F549" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>315</v>
+      </c>
+      <c r="B550" s="3">
+        <v>6630</v>
+      </c>
+      <c r="C550" s="6">
+        <v>20</v>
+      </c>
+      <c r="D550" t="s">
+        <v>156</v>
+      </c>
+      <c r="F550" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>319</v>
-      </c>
-      <c r="B551" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C551">
-        <v>69.900000000000006</v>
+        <v>315</v>
+      </c>
+      <c r="B551" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C551" s="6">
+        <v>18.5</v>
       </c>
       <c r="D551" t="s">
         <v>156</v>
       </c>
-      <c r="E551" t="s">
-        <v>158</v>
+      <c r="F551" s="7" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>319</v>
-      </c>
-      <c r="B552" s="3">
-        <v>4430</v>
+        <v>315</v>
+      </c>
+      <c r="B552" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="C552" s="6">
-        <v>15.25</v>
+        <v>103.5</v>
       </c>
       <c r="D552" t="s">
         <v>156</v>
       </c>
+      <c r="F552" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B553" s="3">
-        <v>4442</v>
+        <v>6660</v>
       </c>
       <c r="C553" s="6">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="D553" t="s">
         <v>156</v>
       </c>
+      <c r="F553" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C554" s="6">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="D554" t="s">
         <v>156</v>
       </c>
+      <c r="F554" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>319</v>
-      </c>
-      <c r="B555" s="3" t="s">
-        <v>162</v>
+        <v>315</v>
+      </c>
+      <c r="B555" s="3">
+        <v>8860</v>
       </c>
       <c r="C555" s="6">
-        <v>972</v>
+        <v>28</v>
       </c>
       <c r="D555" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A556" t="s">
-        <v>319</v>
-      </c>
-      <c r="B556" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C556" s="6">
-        <v>16.5</v>
-      </c>
-      <c r="D556" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A557" t="s">
-        <v>319</v>
-      </c>
-      <c r="B557" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C557" s="6">
-        <v>126</v>
-      </c>
-      <c r="D557" t="s">
-        <v>156</v>
+      <c r="F555" s="7" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>319</v>
       </c>
-      <c r="B558" s="3">
-        <v>4660</v>
-      </c>
-      <c r="C558" s="6">
-        <v>20.25</v>
+      <c r="B558" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C558">
+        <v>69.900000000000006</v>
       </c>
       <c r="D558" t="s">
         <v>156</v>
+      </c>
+      <c r="E558" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
@@ -9235,10 +9262,10 @@
         <v>319</v>
       </c>
       <c r="B559" s="3">
-        <v>6630</v>
+        <v>4430</v>
       </c>
       <c r="C559" s="6">
-        <v>19</v>
+        <v>15.25</v>
       </c>
       <c r="D559" t="s">
         <v>156</v>
@@ -9249,251 +9276,254 @@
         <v>319</v>
       </c>
       <c r="B560" s="3">
-        <v>6642</v>
+        <v>4442</v>
       </c>
       <c r="C560" s="6">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="D560" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>319</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C561" s="6">
-        <v>103.5</v>
+        <v>171</v>
       </c>
       <c r="D561" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>319</v>
       </c>
-      <c r="B562" s="3">
-        <v>6660</v>
+      <c r="B562" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C562" s="6">
-        <v>22.5</v>
+        <v>972</v>
       </c>
       <c r="D562" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>319</v>
       </c>
-      <c r="B563" s="3" t="s">
-        <v>165</v>
+      <c r="B563" s="3">
+        <v>4642</v>
       </c>
       <c r="C563" s="6">
-        <v>126</v>
+        <v>16.5</v>
       </c>
       <c r="D563" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>319</v>
       </c>
-      <c r="B564" s="3">
-        <v>8860</v>
+      <c r="B564" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C564" s="6">
-        <v>42.25</v>
+        <v>126</v>
       </c>
       <c r="D564" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>319</v>
       </c>
-      <c r="B565" s="3" t="s">
-        <v>321</v>
+      <c r="B565" s="3">
+        <v>4660</v>
       </c>
       <c r="C565" s="6">
-        <v>5.75</v>
+        <v>20.25</v>
       </c>
       <c r="D565" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>319</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>168</v>
+        <v>357</v>
       </c>
       <c r="C566" s="6">
-        <v>20</v>
+        <v>20.25</v>
       </c>
       <c r="D566" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="E566" s="3">
+        <v>4660</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>319</v>
       </c>
-      <c r="B567" s="3" t="s">
-        <v>169</v>
+      <c r="B567" s="3">
+        <v>6630</v>
       </c>
       <c r="C567" s="6">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="D567" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>319</v>
       </c>
-      <c r="B568" s="3" t="s">
-        <v>171</v>
+      <c r="B568" s="3">
+        <v>6642</v>
       </c>
       <c r="C568" s="6">
-        <v>77.5</v>
+        <v>18.5</v>
       </c>
       <c r="D568" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>319</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C569" s="6">
-        <v>195</v>
+        <v>103.5</v>
       </c>
       <c r="D569" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>319</v>
+      </c>
+      <c r="B570" s="3">
+        <v>6660</v>
+      </c>
+      <c r="C570" s="6">
+        <v>22.5</v>
+      </c>
+      <c r="D570" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>319</v>
+      </c>
+      <c r="B571" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C571" s="6">
+        <v>126</v>
+      </c>
+      <c r="D571" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>319</v>
+      </c>
+      <c r="B572" s="3">
+        <v>8860</v>
+      </c>
+      <c r="C572" s="6">
+        <v>42.25</v>
+      </c>
+      <c r="D572" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>319</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C573" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="D573" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A573" t="s">
-        <v>322</v>
-      </c>
-      <c r="B573" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C573" s="6">
-        <v>50.35</v>
-      </c>
-      <c r="D573" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="C574" s="6">
-        <v>106.14</v>
+        <v>20</v>
       </c>
       <c r="D574" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C575" s="6">
-        <v>41.99</v>
+        <v>12.5</v>
       </c>
       <c r="D575" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="C576" s="6">
-        <v>82</v>
+        <v>77.5</v>
       </c>
       <c r="D576" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="C577" s="6">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="D577" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A578" t="s">
-        <v>322</v>
-      </c>
-      <c r="B578" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C578" s="6">
-        <v>28.05</v>
-      </c>
-      <c r="D578" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A579" t="s">
-        <v>322</v>
-      </c>
-      <c r="B579" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C579" s="6">
-        <v>28.05</v>
-      </c>
-      <c r="D579" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A580" t="s">
-        <v>322</v>
-      </c>
-      <c r="B580" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C580" s="6">
-        <v>28.05</v>
-      </c>
-      <c r="D580" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
@@ -9501,125 +9531,125 @@
         <v>322</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="C581" s="6">
-        <v>11.2</v>
+        <v>50.35</v>
       </c>
       <c r="D581" t="s">
-        <v>199</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>322</v>
+      </c>
+      <c r="B582" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C582" s="6">
+        <v>106.14</v>
+      </c>
+      <c r="D582" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>322</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C583" s="6">
+        <v>41.99</v>
+      </c>
+      <c r="D583" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="C584" s="6">
-        <v>29.87</v>
+        <v>82</v>
       </c>
       <c r="D584" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="C585" s="6">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="D585" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>57</v>
+        <v>204</v>
       </c>
       <c r="C586" s="6">
-        <v>175</v>
+        <v>28.05</v>
       </c>
       <c r="D586" t="s">
-        <v>55</v>
+        <v>199</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>58</v>
+        <v>205</v>
       </c>
       <c r="C587" s="6">
-        <v>189</v>
+        <v>28.05</v>
       </c>
       <c r="D587" t="s">
-        <v>55</v>
+        <v>199</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>59</v>
+        <v>206</v>
       </c>
       <c r="C588" s="6">
-        <v>224.1</v>
+        <v>28.05</v>
       </c>
       <c r="D588" t="s">
-        <v>55</v>
+        <v>199</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="C589" s="6">
-        <v>309</v>
+        <v>11.2</v>
       </c>
       <c r="D589" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A590" t="s">
-        <v>79</v>
-      </c>
-      <c r="B590" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C590" s="6">
-        <v>85.5</v>
-      </c>
-      <c r="D590" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A591" t="s">
-        <v>79</v>
-      </c>
-      <c r="B591" s="3">
-        <v>6102</v>
-      </c>
-      <c r="C591" s="6">
-        <v>38.99</v>
-      </c>
-      <c r="D591" t="s">
-        <v>79</v>
+        <v>199</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.25">
@@ -9627,13 +9657,13 @@
         <v>79</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="C592" s="6">
-        <v>175</v>
+        <v>29.87</v>
       </c>
       <c r="D592" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
@@ -9641,13 +9671,13 @@
         <v>79</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>287</v>
+        <v>36</v>
       </c>
       <c r="C593" s="6">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="D593" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
@@ -9655,13 +9685,13 @@
         <v>79</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="C594" s="6">
-        <v>59.99</v>
+        <v>175</v>
       </c>
       <c r="D594" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
@@ -9669,13 +9699,13 @@
         <v>79</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="C595" s="6">
-        <v>32.99</v>
+        <v>189</v>
       </c>
       <c r="D595" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
@@ -9683,13 +9713,13 @@
         <v>79</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="C596" s="6">
-        <v>129</v>
+        <v>224.1</v>
       </c>
       <c r="D596" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
@@ -9697,13 +9727,13 @@
         <v>79</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="C597" s="6">
-        <v>149.99</v>
+        <v>309</v>
       </c>
       <c r="D597" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
@@ -9711,27 +9741,27 @@
         <v>79</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="C598" s="6">
-        <v>47.99</v>
+        <v>85.5</v>
       </c>
       <c r="D598" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>79</v>
       </c>
-      <c r="B599" s="3" t="s">
-        <v>123</v>
+      <c r="B599" s="3">
+        <v>6102</v>
       </c>
       <c r="C599" s="6">
-        <v>39.99</v>
+        <v>38.99</v>
       </c>
       <c r="D599" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
@@ -9739,13 +9769,13 @@
         <v>79</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>195</v>
+        <v>88</v>
       </c>
       <c r="C600" s="6">
-        <v>39.99</v>
+        <v>175</v>
       </c>
       <c r="D600" t="s">
-        <v>196</v>
+        <v>79</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
@@ -9753,10 +9783,13 @@
         <v>79</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>197</v>
+        <v>287</v>
+      </c>
+      <c r="C601" s="6">
+        <v>134</v>
       </c>
       <c r="D601" t="s">
-        <v>196</v>
+        <v>79</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
@@ -9764,125 +9797,122 @@
         <v>79</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>239</v>
+        <v>112</v>
       </c>
       <c r="C602" s="6">
-        <v>36.950000000000003</v>
+        <v>59.99</v>
       </c>
       <c r="D602" t="s">
-        <v>238</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>79</v>
+      </c>
+      <c r="B603" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C603" s="6">
+        <v>32.99</v>
+      </c>
+      <c r="D603" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>79</v>
+      </c>
+      <c r="B604" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C604" s="6">
+        <v>129</v>
+      </c>
+      <c r="D604" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="C605" s="6">
-        <v>18</v>
+        <v>149.99</v>
       </c>
       <c r="D605" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="C606" s="6">
-        <v>100</v>
+        <v>47.99</v>
       </c>
       <c r="D606" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="C607" s="6">
-        <v>99</v>
+        <v>39.99</v>
       </c>
       <c r="D607" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="C608" s="6">
-        <v>134</v>
+        <v>39.99</v>
       </c>
       <c r="D608" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C609" s="6">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="D609" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="C610" s="6">
-        <v>155</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D610" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A611" t="s">
-        <v>323</v>
-      </c>
-      <c r="B611" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C611" s="6">
-        <v>239</v>
-      </c>
-      <c r="D611" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A612" t="s">
-        <v>323</v>
-      </c>
-      <c r="B612" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C612" s="6">
-        <v>215</v>
-      </c>
-      <c r="D612" t="s">
-        <v>28</v>
+        <v>238</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
@@ -9890,10 +9920,10 @@
         <v>323</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C613" s="6">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="D613" t="s">
         <v>28</v>
@@ -9904,10 +9934,10 @@
         <v>323</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C614" s="6">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="D614" t="s">
         <v>28</v>
@@ -9918,10 +9948,10 @@
         <v>323</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C615" s="6">
-        <v>285</v>
+        <v>99</v>
       </c>
       <c r="D615" t="s">
         <v>28</v>
@@ -9932,10 +9962,10 @@
         <v>323</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C616" s="6">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c r="D616" t="s">
         <v>28</v>
@@ -9946,13 +9976,13 @@
         <v>323</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C617" s="6">
-        <v>19.989999999999998</v>
+        <v>185</v>
       </c>
       <c r="D617" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.25">
@@ -9960,13 +9990,13 @@
         <v>323</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C618" s="6">
-        <v>29.99</v>
+        <v>155</v>
       </c>
       <c r="D618" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.25">
@@ -9974,13 +10004,13 @@
         <v>323</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C619" s="6">
-        <v>155</v>
+        <v>239</v>
       </c>
       <c r="D619" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
@@ -9988,13 +10018,13 @@
         <v>323</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C620" s="6">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="D620" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.25">
@@ -10002,13 +10032,13 @@
         <v>323</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C621" s="6">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D621" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
@@ -10016,13 +10046,13 @@
         <v>323</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C622" s="6">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="D622" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
@@ -10030,13 +10060,13 @@
         <v>323</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C623" s="6">
-        <v>199</v>
+        <v>285</v>
       </c>
       <c r="D623" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
@@ -10044,13 +10074,13 @@
         <v>323</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C624" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D624" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
@@ -10058,13 +10088,13 @@
         <v>323</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C625" s="6">
-        <v>389</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D625" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
@@ -10072,13 +10102,13 @@
         <v>323</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C626" s="6">
-        <v>399.99</v>
+        <v>29.99</v>
       </c>
       <c r="D626" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
@@ -10086,10 +10116,10 @@
         <v>323</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C627" s="6">
-        <v>89.23</v>
+        <v>155</v>
       </c>
       <c r="D627" t="s">
         <v>55</v>
@@ -10099,14 +10129,14 @@
       <c r="A628" t="s">
         <v>323</v>
       </c>
-      <c r="B628" s="3">
-        <v>6102</v>
+      <c r="B628" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C628" s="6">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="D628" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
@@ -10114,13 +10144,13 @@
         <v>323</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>324</v>
+        <v>57</v>
       </c>
       <c r="C629" s="6">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="D629" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
@@ -10128,13 +10158,13 @@
         <v>323</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="C630" s="6">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="D630" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
@@ -10142,13 +10172,13 @@
         <v>323</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>326</v>
+        <v>59</v>
       </c>
       <c r="C631" s="6">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="D631" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
@@ -10156,13 +10186,13 @@
         <v>323</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>327</v>
+        <v>60</v>
       </c>
       <c r="C632" s="6">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="D632" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.25">
@@ -10170,13 +10200,13 @@
         <v>323</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>328</v>
+        <v>62</v>
       </c>
       <c r="C633" s="6">
-        <v>90</v>
+        <v>389</v>
       </c>
       <c r="D633" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.25">
@@ -10184,13 +10214,13 @@
         <v>323</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>329</v>
+        <v>63</v>
       </c>
       <c r="C634" s="6">
-        <v>114</v>
+        <v>399.99</v>
       </c>
       <c r="D634" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.25">
@@ -10198,27 +10228,27 @@
         <v>323</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="C635" s="6">
-        <v>27.99</v>
+        <v>89.23</v>
       </c>
       <c r="D635" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>323</v>
       </c>
-      <c r="B636" s="3" t="s">
-        <v>114</v>
+      <c r="B636" s="3">
+        <v>6102</v>
       </c>
       <c r="C636" s="6">
-        <v>28.99</v>
+        <v>44</v>
       </c>
       <c r="D636" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
@@ -10226,13 +10256,13 @@
         <v>323</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>111</v>
+        <v>324</v>
       </c>
       <c r="C637" s="6">
-        <v>39.99</v>
+        <v>64</v>
       </c>
       <c r="D637" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
@@ -10240,13 +10270,13 @@
         <v>323</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>112</v>
+        <v>325</v>
       </c>
       <c r="C638" s="6">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D638" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
@@ -10254,13 +10284,13 @@
         <v>323</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>115</v>
+        <v>326</v>
       </c>
       <c r="C639" s="6">
-        <v>42.99</v>
+        <v>72</v>
       </c>
       <c r="D639" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
@@ -10268,237 +10298,240 @@
         <v>323</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>113</v>
+        <v>327</v>
       </c>
       <c r="C640" s="6">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="D640" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>323</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>116</v>
+        <v>328</v>
       </c>
       <c r="C641" s="6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="D641" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>323</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>117</v>
+        <v>329</v>
       </c>
       <c r="C642" s="6">
-        <v>54.5</v>
+        <v>114</v>
       </c>
       <c r="D642" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>323</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C643" s="6">
-        <v>48.99</v>
+        <v>27.99</v>
       </c>
       <c r="D643" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>323</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C644" s="6">
-        <v>39.99</v>
+        <v>28.99</v>
       </c>
       <c r="D644" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>323</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C645" s="6">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="D645" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>323</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C646" s="6">
-        <v>29.99</v>
+        <v>58</v>
       </c>
       <c r="D646" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>323</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C647" s="6">
-        <v>28.99</v>
+        <v>42.99</v>
       </c>
       <c r="D647" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>323</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="C648" s="6">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="D648" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>323</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C649" s="6">
-        <v>29.99</v>
+        <v>180</v>
       </c>
       <c r="D649" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>323</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C650" s="6">
-        <v>25.99</v>
+        <v>54.5</v>
       </c>
       <c r="D650" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>323</v>
       </c>
-      <c r="B651" s="3">
-        <v>6642</v>
+      <c r="B651" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="C651" s="6">
-        <v>50</v>
+        <v>48.99</v>
       </c>
       <c r="D651" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>323</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="C652" s="6">
-        <v>19.2</v>
+        <v>39.99</v>
       </c>
       <c r="D652" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>323</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="C653" s="6">
-        <v>40</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D653" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>323</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>203</v>
+        <v>358</v>
       </c>
       <c r="C654" s="6">
-        <v>40</v>
+        <v>29.99</v>
       </c>
       <c r="D654" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="E654" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>323</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>224</v>
+        <v>126</v>
       </c>
       <c r="C655" s="6">
-        <v>30.58</v>
+        <v>28.99</v>
       </c>
       <c r="D655" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>323</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="C656" s="6">
-        <v>39.99</v>
+        <v>35</v>
       </c>
       <c r="D656" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
@@ -10506,506 +10539,618 @@
         <v>323</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>330</v>
+        <v>121</v>
       </c>
       <c r="C657" s="6">
-        <v>90</v>
+        <v>29.99</v>
       </c>
       <c r="D657" t="s">
-        <v>221</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>323</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C658" s="6">
+        <v>25.99</v>
+      </c>
+      <c r="D658" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>323</v>
+      </c>
+      <c r="B659" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C659" s="6">
+        <v>50</v>
+      </c>
+      <c r="D659" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>310</v>
+        <v>209</v>
       </c>
       <c r="C660" s="6">
-        <v>42.75</v>
+        <v>19.2</v>
       </c>
       <c r="D660" t="s">
-        <v>28</v>
+        <v>199</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>312</v>
+        <v>201</v>
       </c>
       <c r="C661" s="6">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D661" t="s">
-        <v>28</v>
+        <v>199</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B662" s="3" t="s">
-        <v>313</v>
+        <v>203</v>
       </c>
       <c r="C662" s="6">
-        <v>82.2</v>
+        <v>40</v>
       </c>
       <c r="D662" t="s">
-        <v>28</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
+        <v>323</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C663" s="6">
+        <v>30.58</v>
+      </c>
+      <c r="D663" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="C664" s="6">
-        <v>2.75</v>
+        <v>39.99</v>
       </c>
       <c r="D664" t="s">
-        <v>43</v>
+        <v>221</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>44</v>
+        <v>330</v>
       </c>
       <c r="C665" s="6">
-        <v>3.25</v>
+        <v>90</v>
       </c>
       <c r="D665" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A666" t="s">
-        <v>332</v>
-      </c>
-      <c r="B666" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C666" s="6">
-        <v>18.96</v>
-      </c>
-      <c r="D666" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A667" t="s">
-        <v>332</v>
-      </c>
-      <c r="B667" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C667" s="6">
-        <v>22.37</v>
-      </c>
-      <c r="D667" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>208</v>
+        <v>310</v>
       </c>
       <c r="C668" s="6">
-        <v>9.1</v>
+        <v>42.75</v>
       </c>
       <c r="D668" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
+        <v>331</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C669" s="6">
+        <v>68</v>
+      </c>
+      <c r="D669" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>331</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C670" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D670" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
         <v>332</v>
       </c>
-      <c r="B669" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C669" s="6">
-        <v>9.1</v>
-      </c>
-      <c r="D669" t="s">
-        <v>199</v>
+      <c r="B672" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C672" s="6">
+        <v>2.75</v>
+      </c>
+      <c r="D672" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>332</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C673" s="6">
+        <v>3.25</v>
+      </c>
+      <c r="D673" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>333</v>
-      </c>
-      <c r="B674" s="3" t="s">
-        <v>42</v>
+        <v>332</v>
+      </c>
+      <c r="B674" s="3">
+        <v>4642</v>
       </c>
       <c r="C674" s="6">
-        <v>2.75</v>
+        <v>18.96</v>
       </c>
       <c r="D674" t="s">
-        <v>43</v>
-      </c>
-      <c r="F674" s="7" t="s">
-        <v>349</v>
+        <v>156</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>333</v>
-      </c>
-      <c r="B675" s="3" t="s">
-        <v>44</v>
+        <v>332</v>
+      </c>
+      <c r="B675" s="3">
+        <v>6642</v>
       </c>
       <c r="C675" s="6">
-        <v>3.25</v>
+        <v>22.37</v>
       </c>
       <c r="D675" t="s">
-        <v>43</v>
-      </c>
-      <c r="F675" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A679" t="s">
-        <v>334</v>
-      </c>
-      <c r="B679" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C679" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D679" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A680" t="s">
-        <v>334</v>
-      </c>
-      <c r="B680" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C680" s="6">
-        <v>7.65</v>
-      </c>
-      <c r="D680" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A681" t="s">
-        <v>334</v>
-      </c>
-      <c r="B681" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C681" s="6">
-        <v>8.1</v>
-      </c>
-      <c r="D681" t="s">
-        <v>336</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>332</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C676" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D676" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>332</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C677" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D677" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>339</v>
+        <v>42</v>
       </c>
       <c r="C682" s="6">
-        <v>10.8</v>
+        <v>2.75</v>
       </c>
       <c r="D682" t="s">
-        <v>336</v>
+        <v>43</v>
+      </c>
+      <c r="F682" s="7" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
+        <v>333</v>
+      </c>
+      <c r="B683" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C683" s="6">
+        <v>3.25</v>
+      </c>
+      <c r="D683" t="s">
+        <v>43</v>
+      </c>
+      <c r="F683" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
         <v>334</v>
       </c>
-      <c r="B683" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C683" s="6">
-        <v>12.2</v>
-      </c>
-      <c r="D683" t="s">
+      <c r="B687" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C687" s="6">
+        <v>3.15</v>
+      </c>
+      <c r="D687" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A684" t="s">
+    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
         <v>334</v>
       </c>
-      <c r="B684" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C684" s="6">
-        <v>11.25</v>
-      </c>
-      <c r="D684" t="s">
+      <c r="B688" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C688" s="6">
+        <v>7.65</v>
+      </c>
+      <c r="D688" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A685" t="s">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
         <v>334</v>
       </c>
-      <c r="B685" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C685" s="6">
-        <v>11.25</v>
-      </c>
-      <c r="D685" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A686" t="s">
-        <v>334</v>
-      </c>
-      <c r="B686" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C686" s="6">
-        <v>11.25</v>
-      </c>
-      <c r="D686" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A689" t="s">
-        <v>344</v>
-      </c>
       <c r="B689" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C689" s="6">
-        <v>3.36</v>
+        <v>8.1</v>
       </c>
       <c r="D689" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C690" s="6">
-        <v>10.19</v>
+        <v>10.8</v>
       </c>
       <c r="D690" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C691" s="6">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="D691" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C692" s="6">
-        <v>14.39</v>
+        <v>11.25</v>
       </c>
       <c r="D692" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B693" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C693" s="6">
-        <v>11.52</v>
+        <v>11.25</v>
       </c>
       <c r="D693" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B694" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C694" s="6">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="D694" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A695" t="s">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
         <v>344</v>
       </c>
-      <c r="B695" s="3" t="s">
+      <c r="B697" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C697" s="6">
+        <v>3.36</v>
+      </c>
+      <c r="D697" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>344</v>
+      </c>
+      <c r="B698" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C698" s="6">
+        <v>10.19</v>
+      </c>
+      <c r="D698" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>344</v>
+      </c>
+      <c r="B699" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C699" s="6">
+        <v>14.4</v>
+      </c>
+      <c r="D699" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>344</v>
+      </c>
+      <c r="B700" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C700" s="6">
+        <v>14.39</v>
+      </c>
+      <c r="D700" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>344</v>
+      </c>
+      <c r="B701" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C701" s="6">
+        <v>11.52</v>
+      </c>
+      <c r="D701" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>344</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C702" s="6">
+        <v>12</v>
+      </c>
+      <c r="D702" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>344</v>
+      </c>
+      <c r="B703" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C695" s="6">
+      <c r="C703" s="6">
         <v>12</v>
       </c>
-      <c r="D695" t="s">
+      <c r="D703" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A696" t="s">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
         <v>344</v>
       </c>
-      <c r="B696" s="3" t="s">
+      <c r="B704" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C696" s="6">
+      <c r="C704" s="6">
         <v>12</v>
       </c>
-      <c r="D696" t="s">
+      <c r="D704" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A697" t="s">
-        <v>6</v>
-      </c>
-      <c r="B697" t="s">
+    <row r="705" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>6</v>
+      </c>
+      <c r="B705" t="s">
         <v>345</v>
       </c>
-      <c r="C697">
+      <c r="C705">
         <v>23</v>
       </c>
-      <c r="D697" t="s">
+      <c r="D705" t="s">
         <v>118</v>
       </c>
-      <c r="E697" t="s">
+      <c r="E705" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A698" t="s">
+    <row r="706" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
         <v>249</v>
       </c>
-      <c r="B698" t="s">
+      <c r="B706" t="s">
         <v>346</v>
       </c>
-      <c r="C698">
+      <c r="C706">
         <v>12</v>
       </c>
-      <c r="D698" t="s">
+      <c r="D706" t="s">
         <v>109</v>
       </c>
-      <c r="E698" t="s">
+      <c r="E706" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A699" t="s">
+    <row r="707" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
         <v>79</v>
       </c>
-      <c r="B699" t="s">
+      <c r="B707" t="s">
         <v>347</v>
       </c>
-      <c r="C699">
+      <c r="C707">
         <v>126.38</v>
       </c>
-      <c r="D699" t="s">
+      <c r="D707" t="s">
         <v>79</v>
       </c>
-      <c r="E699" t="s">
+      <c r="E707" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A702" t="s">
+    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
         <v>350</v>
       </c>
-      <c r="B702" s="3" t="s">
+      <c r="B710" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C702" s="6">
+      <c r="C710" s="6">
         <v>17.489999999999998</v>
       </c>
-      <c r="D702" t="s">
+      <c r="D710" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A703" t="s">
+    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
         <v>350</v>
       </c>
-      <c r="B703" s="3" t="s">
+      <c r="B711" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C703" s="6">
+      <c r="C711" s="6">
         <v>199.99</v>
       </c>
-      <c r="D703" t="s">
+      <c r="D711" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A704" t="s">
+    <row r="712" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
         <v>350</v>
       </c>
-      <c r="B704" s="3" t="s">
+      <c r="B712" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C704" s="6">
+      <c r="C712" s="6">
         <v>28.99</v>
       </c>
-      <c r="D704" t="s">
+      <c r="D712" t="s">
         <v>118</v>
       </c>
-      <c r="E704" s="3" t="s">
+      <c r="E712" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A705" t="s">
+    <row r="713" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
         <v>350</v>
       </c>
-      <c r="B705" s="3" t="s">
+      <c r="B713" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C705" s="6">
+      <c r="C713" s="6">
         <v>359.99</v>
       </c>
-      <c r="D705" t="s">
+      <c r="D713" t="s">
         <v>55</v>
       </c>
     </row>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7595A752-7DB0-4BCA-BF74-852371309A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC59DEB0-71A3-4357-9898-98B36BA937BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43783" yWindow="-6214" windowWidth="33120" windowHeight="18274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47805" yWindow="-16380" windowWidth="29160" windowHeight="16110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="361">
   <si>
     <t>Retailer</t>
   </si>
@@ -1097,6 +1097,12 @@
   </si>
   <si>
     <t>WO32OZ</t>
+  </si>
+  <si>
+    <t>DECOMIA-53</t>
+  </si>
+  <si>
+    <t>DECOMIA-953</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K713"/>
+  <dimension ref="A1:K715"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -2603,6 +2609,9 @@
       <c r="D73" t="s">
         <v>79</v>
       </c>
+      <c r="E73" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="K73" s="3"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2610,14 +2619,17 @@
         <v>6</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>88</v>
+        <v>359</v>
       </c>
       <c r="C74" s="6">
-        <v>126.38</v>
+        <v>179</v>
       </c>
       <c r="D74" t="s">
         <v>79</v>
       </c>
+      <c r="E74" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="K74" s="3"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2625,14 +2637,17 @@
         <v>6</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>89</v>
+        <v>360</v>
       </c>
       <c r="C75" s="6">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="D75" t="s">
         <v>79</v>
       </c>
+      <c r="E75" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="K75" s="3"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2640,10 +2655,10 @@
         <v>6</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C76" s="6">
-        <v>147.15</v>
+        <v>126.38</v>
       </c>
       <c r="D76" t="s">
         <v>79</v>
@@ -2655,10 +2670,10 @@
         <v>6</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C77" s="6">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="D77" t="s">
         <v>79</v>
@@ -2670,10 +2685,10 @@
         <v>6</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C78" s="6">
-        <v>138</v>
+        <v>147.15</v>
       </c>
       <c r="D78" t="s">
         <v>79</v>
@@ -2685,10 +2700,10 @@
         <v>6</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C79" s="6">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="D79" t="s">
         <v>79</v>
@@ -2700,10 +2715,10 @@
         <v>6</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C80" s="6">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="D80" t="s">
         <v>79</v>
@@ -2715,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C81" s="6">
-        <v>164</v>
+        <v>225</v>
       </c>
       <c r="D81" t="s">
         <v>79</v>
@@ -2730,10 +2745,10 @@
         <v>6</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C82" s="6">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D82" t="s">
         <v>79</v>
@@ -2745,10 +2760,10 @@
         <v>6</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C83" s="6">
-        <v>225</v>
+        <v>164</v>
       </c>
       <c r="D83" t="s">
         <v>79</v>
@@ -2760,10 +2775,10 @@
         <v>6</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C84" s="6">
-        <v>285.45</v>
+        <v>136</v>
       </c>
       <c r="D84" t="s">
         <v>79</v>
@@ -2775,10 +2790,10 @@
         <v>6</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C85" s="6">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="D85" t="s">
         <v>79</v>
@@ -2790,10 +2805,10 @@
         <v>6</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C86" s="6">
-        <v>241</v>
+        <v>285.45</v>
       </c>
       <c r="D86" t="s">
         <v>79</v>
@@ -2804,39 +2819,41 @@
       <c r="A87" t="s">
         <v>6</v>
       </c>
-      <c r="B87" t="s">
-        <v>101</v>
+      <c r="B87" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C87" s="6">
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="D87" t="s">
-        <v>102</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="K87" s="3"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>6</v>
       </c>
-      <c r="B88" t="s">
-        <v>103</v>
+      <c r="B88" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C88" s="6">
-        <v>46</v>
+        <v>241</v>
       </c>
       <c r="D88" t="s">
-        <v>102</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="K88" s="3"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C89" s="6">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D89" t="s">
         <v>102</v>
@@ -2847,10 +2864,10 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C90" s="6">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D90" t="s">
         <v>102</v>
@@ -2861,10 +2878,10 @@
         <v>6</v>
       </c>
       <c r="B91" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C91" s="6">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D91" t="s">
         <v>102</v>
@@ -2875,10 +2892,10 @@
         <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C92" s="6">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D92" t="s">
         <v>102</v>
@@ -2888,41 +2905,39 @@
       <c r="A93" t="s">
         <v>6</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>108</v>
+      <c r="B93" t="s">
+        <v>106</v>
       </c>
       <c r="C93" s="6">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="D93" t="s">
-        <v>109</v>
-      </c>
-      <c r="K93" s="3"/>
+        <v>102</v>
+      </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>6</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>110</v>
+      <c r="B94" t="s">
+        <v>107</v>
       </c>
       <c r="C94" s="6">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="D94" t="s">
-        <v>109</v>
-      </c>
-      <c r="K94" s="3"/>
+        <v>102</v>
+      </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C95" s="6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D95" t="s">
         <v>109</v>
@@ -2934,10 +2949,10 @@
         <v>6</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C96" s="6">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D96" t="s">
         <v>109</v>
@@ -2949,10 +2964,10 @@
         <v>6</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C97" s="6">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
         <v>109</v>
@@ -2963,39 +2978,41 @@
       <c r="A98" t="s">
         <v>6</v>
       </c>
-      <c r="B98" t="s">
-        <v>114</v>
-      </c>
-      <c r="C98" s="7">
-        <v>14</v>
+      <c r="B98" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C98" s="6">
+        <v>40</v>
       </c>
       <c r="D98" t="s">
         <v>109</v>
       </c>
+      <c r="K98" s="3"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>6</v>
       </c>
-      <c r="B99" t="s">
-        <v>115</v>
+      <c r="B99" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="C99" s="6">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D99" t="s">
         <v>109</v>
       </c>
+      <c r="K99" s="3"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>116</v>
-      </c>
-      <c r="C100" s="6">
-        <v>102</v>
+        <v>114</v>
+      </c>
+      <c r="C100" s="7">
+        <v>14</v>
       </c>
       <c r="D100" t="s">
         <v>109</v>
@@ -3005,41 +3022,39 @@
       <c r="A101" t="s">
         <v>6</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>117</v>
+      <c r="B101" t="s">
+        <v>115</v>
       </c>
       <c r="C101" s="6">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D101" t="s">
-        <v>118</v>
-      </c>
-      <c r="K101" s="3"/>
+        <v>109</v>
+      </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>6</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>119</v>
+      <c r="B102" t="s">
+        <v>116</v>
       </c>
       <c r="C102" s="6">
-        <v>15.1</v>
+        <v>102</v>
       </c>
       <c r="D102" t="s">
-        <v>118</v>
-      </c>
-      <c r="K102" s="3"/>
+        <v>109</v>
+      </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>6</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="6">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D103" t="s">
         <v>118</v>
@@ -3051,10 +3066,10 @@
         <v>6</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C104" s="6">
-        <v>20.84</v>
+        <v>15.1</v>
       </c>
       <c r="D104" t="s">
         <v>118</v>
@@ -3066,10 +3081,10 @@
         <v>6</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C105" s="6">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D105" t="s">
         <v>118</v>
@@ -3081,10 +3096,10 @@
         <v>6</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C106" s="6">
-        <v>23</v>
+        <v>20.84</v>
       </c>
       <c r="D106" t="s">
         <v>118</v>
@@ -3096,10 +3111,10 @@
         <v>6</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C107" s="6">
-        <v>10.1</v>
+        <v>24</v>
       </c>
       <c r="D107" t="s">
         <v>118</v>
@@ -3111,10 +3126,10 @@
         <v>6</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C108" s="6">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="D108" t="s">
         <v>118</v>
@@ -3125,27 +3140,26 @@
       <c r="A109" t="s">
         <v>6</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C109" s="2">
-        <v>16.5</v>
+      <c r="B109" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C109" s="6">
+        <v>10.1</v>
       </c>
       <c r="D109" t="s">
         <v>118</v>
       </c>
-      <c r="E109" s="1"/>
-      <c r="K109" s="1"/>
+      <c r="K109" s="3"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>6</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C110" s="6">
-        <v>22</v>
+        <v>5.5</v>
       </c>
       <c r="D110" t="s">
         <v>118</v>
@@ -3156,26 +3170,27 @@
       <c r="A111" t="s">
         <v>6</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C111" s="6">
-        <v>26.25</v>
+      <c r="B111" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C111" s="2">
+        <v>16.5</v>
       </c>
       <c r="D111" t="s">
         <v>118</v>
       </c>
-      <c r="K111" s="3"/>
+      <c r="E111" s="1"/>
+      <c r="K111" s="1"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>6</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C112" s="6">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D112" t="s">
         <v>118</v>
@@ -3187,10 +3202,10 @@
         <v>6</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C113" s="6">
-        <v>26</v>
+        <v>26.25</v>
       </c>
       <c r="D113" t="s">
         <v>118</v>
@@ -3201,46 +3216,44 @@
       <c r="A114" t="s">
         <v>6</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C114" s="2">
-        <v>25</v>
+      <c r="B114" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C114" s="6">
+        <v>28</v>
       </c>
       <c r="D114" t="s">
         <v>118</v>
       </c>
-      <c r="E114" s="1"/>
-      <c r="K114" s="1"/>
+      <c r="K114" s="3"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C115" s="2">
-        <v>12</v>
+      <c r="B115" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C115" s="6">
+        <v>26</v>
       </c>
       <c r="D115" t="s">
         <v>118</v>
       </c>
-      <c r="E115" s="1"/>
-      <c r="K115" s="1"/>
+      <c r="K115" s="3"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>6</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C116" s="2">
-        <v>1149.73</v>
+        <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E116" s="1"/>
       <c r="K116" s="1"/>
@@ -3250,13 +3263,13 @@
         <v>6</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C117" s="2">
-        <v>919.63</v>
+        <v>12</v>
       </c>
       <c r="D117" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E117" s="1"/>
       <c r="K117" s="1"/>
@@ -3266,10 +3279,10 @@
         <v>6</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C118" s="2">
-        <v>1188.08</v>
+        <v>1149.73</v>
       </c>
       <c r="D118" t="s">
         <v>134</v>
@@ -3282,10 +3295,10 @@
         <v>6</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C119" s="2">
-        <v>1149.73</v>
+        <v>919.63</v>
       </c>
       <c r="D119" t="s">
         <v>134</v>
@@ -3298,10 +3311,10 @@
         <v>6</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C120" s="2">
-        <v>957.98</v>
+        <v>1188.08</v>
       </c>
       <c r="D120" t="s">
         <v>134</v>
@@ -3314,10 +3327,10 @@
         <v>6</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C121" s="2">
-        <v>919.63</v>
+        <v>1149.73</v>
       </c>
       <c r="D121" t="s">
         <v>134</v>
@@ -3330,10 +3343,10 @@
         <v>6</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C122" s="2">
-        <v>1571.58</v>
+        <v>957.98</v>
       </c>
       <c r="D122" t="s">
         <v>134</v>
@@ -3345,38 +3358,40 @@
       <c r="A123" t="s">
         <v>6</v>
       </c>
-      <c r="B123" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C123" s="6">
-        <v>1533.23</v>
+      <c r="B123" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" s="2">
+        <v>919.63</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
       </c>
-      <c r="K123" s="3"/>
+      <c r="E123" s="1"/>
+      <c r="K123" s="1"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>6</v>
       </c>
-      <c r="B124" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C124" s="6">
+      <c r="B124" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C124" s="2">
         <v>1571.58</v>
       </c>
       <c r="D124" t="s">
         <v>134</v>
       </c>
-      <c r="K124" s="3"/>
+      <c r="E124" s="1"/>
+      <c r="K124" s="1"/>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>6</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C125" s="6">
         <v>1533.23</v>
@@ -3391,10 +3406,10 @@
         <v>6</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C126" s="6">
-        <v>758.56</v>
+        <v>1571.58</v>
       </c>
       <c r="D126" t="s">
         <v>134</v>
@@ -3406,10 +3421,10 @@
         <v>6</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C127" s="6">
-        <v>689</v>
+        <v>1533.23</v>
       </c>
       <c r="D127" t="s">
         <v>134</v>
@@ -3421,10 +3436,10 @@
         <v>6</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C128" s="6">
-        <v>421.08</v>
+        <v>758.56</v>
       </c>
       <c r="D128" t="s">
         <v>134</v>
@@ -3436,10 +3451,10 @@
         <v>6</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C129" s="6">
-        <v>382.73</v>
+        <v>689</v>
       </c>
       <c r="D129" t="s">
         <v>134</v>
@@ -3451,10 +3466,10 @@
         <v>6</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C130" s="6">
-        <v>574.48</v>
+        <v>421.08</v>
       </c>
       <c r="D130" t="s">
         <v>134</v>
@@ -3466,10 +3481,10 @@
         <v>6</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C131" s="6">
-        <v>536.13</v>
+        <v>382.73</v>
       </c>
       <c r="D131" t="s">
         <v>134</v>
@@ -3481,10 +3496,10 @@
         <v>6</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C132" s="6">
-        <v>87</v>
+        <v>574.48</v>
       </c>
       <c r="D132" t="s">
         <v>134</v>
@@ -3496,10 +3511,10 @@
         <v>6</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C133" s="6">
-        <v>225</v>
+        <v>536.13</v>
       </c>
       <c r="D133" t="s">
         <v>134</v>
@@ -3511,10 +3526,10 @@
         <v>6</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C134" s="6">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="D134" t="s">
         <v>134</v>
@@ -3526,13 +3541,13 @@
         <v>6</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C135" s="6">
-        <v>60</v>
+        <v>225</v>
       </c>
       <c r="D135" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="K135" s="3"/>
     </row>
@@ -3541,13 +3556,13 @@
         <v>6</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C136" s="6">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="D136" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="K136" s="3"/>
     </row>
@@ -3556,13 +3571,13 @@
         <v>6</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C137" s="6">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D137" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K137" s="3"/>
     </row>
@@ -3571,10 +3586,10 @@
         <v>6</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C138" s="6">
-        <v>69.900000000000006</v>
+        <v>16</v>
       </c>
       <c r="D138" t="s">
         <v>156</v>
@@ -3586,10 +3601,10 @@
         <v>6</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C139" s="6">
-        <v>6.25</v>
+        <v>33</v>
       </c>
       <c r="D139" t="s">
         <v>156</v>
@@ -3601,10 +3616,10 @@
         <v>6</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C140" s="6">
-        <v>6.75</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="D140" t="s">
         <v>156</v>
@@ -3615,11 +3630,11 @@
       <c r="A141" t="s">
         <v>6</v>
       </c>
-      <c r="B141" s="3">
-        <v>4430</v>
+      <c r="B141" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="C141" s="6">
-        <v>15.25</v>
+        <v>6.25</v>
       </c>
       <c r="D141" t="s">
         <v>156</v>
@@ -3630,11 +3645,11 @@
       <c r="A142" t="s">
         <v>6</v>
       </c>
-      <c r="B142" s="3">
-        <v>4442</v>
+      <c r="B142" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="C142" s="6">
-        <v>18.899999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="D142" t="s">
         <v>156</v>
@@ -3645,11 +3660,11 @@
       <c r="A143" t="s">
         <v>6</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>161</v>
+      <c r="B143" s="3">
+        <v>4430</v>
       </c>
       <c r="C143" s="6">
-        <v>224</v>
+        <v>15.25</v>
       </c>
       <c r="D143" t="s">
         <v>156</v>
@@ -3660,11 +3675,11 @@
       <c r="A144" t="s">
         <v>6</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>162</v>
+      <c r="B144" s="3">
+        <v>4442</v>
       </c>
       <c r="C144" s="6">
-        <v>972</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D144" t="s">
         <v>156</v>
@@ -3675,11 +3690,11 @@
       <c r="A145" t="s">
         <v>6</v>
       </c>
-      <c r="B145" s="3">
-        <v>4642</v>
+      <c r="B145" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="C145" s="6">
-        <v>20.8</v>
+        <v>224</v>
       </c>
       <c r="D145" t="s">
         <v>156</v>
@@ -3691,10 +3706,10 @@
         <v>6</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C146" s="6">
-        <v>126</v>
+        <v>972</v>
       </c>
       <c r="D146" t="s">
         <v>156</v>
@@ -3706,10 +3721,10 @@
         <v>6</v>
       </c>
       <c r="B147" s="3">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C147" s="6">
-        <v>24.7</v>
+        <v>20.8</v>
       </c>
       <c r="D147" t="s">
         <v>156</v>
@@ -3720,11 +3735,11 @@
       <c r="A148" t="s">
         <v>6</v>
       </c>
-      <c r="B148" s="3">
-        <v>6630</v>
+      <c r="B148" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C148" s="6">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="D148" t="s">
         <v>156</v>
@@ -3736,10 +3751,10 @@
         <v>6</v>
       </c>
       <c r="B149" s="3">
-        <v>6642</v>
+        <v>4660</v>
       </c>
       <c r="C149" s="6">
-        <v>26.8</v>
+        <v>24.7</v>
       </c>
       <c r="D149" t="s">
         <v>156</v>
@@ -3750,11 +3765,11 @@
       <c r="A150" t="s">
         <v>6</v>
       </c>
-      <c r="B150" s="3" t="s">
-        <v>164</v>
+      <c r="B150" s="3">
+        <v>6630</v>
       </c>
       <c r="C150" s="6">
-        <v>151.19999999999999</v>
+        <v>19</v>
       </c>
       <c r="D150" t="s">
         <v>156</v>
@@ -3766,10 +3781,10 @@
         <v>6</v>
       </c>
       <c r="B151" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C151" s="6">
-        <v>27.05</v>
+        <v>26.8</v>
       </c>
       <c r="D151" t="s">
         <v>156</v>
@@ -3781,10 +3796,10 @@
         <v>6</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C152" s="6">
-        <v>160</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="D152" t="s">
         <v>156</v>
@@ -3796,10 +3811,10 @@
         <v>6</v>
       </c>
       <c r="B153" s="3">
-        <v>8860</v>
+        <v>6660</v>
       </c>
       <c r="C153" s="6">
-        <v>42.25</v>
+        <v>27.05</v>
       </c>
       <c r="D153" t="s">
         <v>156</v>
@@ -3811,13 +3826,13 @@
         <v>6</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C154" s="6">
-        <v>22.85</v>
+        <v>160</v>
       </c>
       <c r="D154" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="K154" s="3"/>
     </row>
@@ -3825,14 +3840,14 @@
       <c r="A155" t="s">
         <v>6</v>
       </c>
-      <c r="B155" s="3" t="s">
-        <v>168</v>
+      <c r="B155" s="3">
+        <v>8860</v>
       </c>
       <c r="C155" s="6">
-        <v>15.75</v>
+        <v>42.25</v>
       </c>
       <c r="D155" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="K155" s="3"/>
     </row>
@@ -3841,10 +3856,10 @@
         <v>6</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C156" s="6">
-        <v>10.5</v>
+        <v>22.85</v>
       </c>
       <c r="D156" t="s">
         <v>167</v>
@@ -3856,10 +3871,10 @@
         <v>6</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C157" s="6">
-        <v>45</v>
+        <v>15.75</v>
       </c>
       <c r="D157" t="s">
         <v>167</v>
@@ -3871,10 +3886,10 @@
         <v>6</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C158" s="6">
-        <v>77.5</v>
+        <v>10.5</v>
       </c>
       <c r="D158" t="s">
         <v>167</v>
@@ -3886,10 +3901,10 @@
         <v>6</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C159" s="6">
-        <v>152.30000000000001</v>
+        <v>45</v>
       </c>
       <c r="D159" t="s">
         <v>167</v>
@@ -3901,10 +3916,10 @@
         <v>6</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C160" s="6">
-        <v>273</v>
+        <v>77.5</v>
       </c>
       <c r="D160" t="s">
         <v>167</v>
@@ -3916,13 +3931,13 @@
         <v>6</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C161" s="6">
-        <v>30.5</v>
+        <v>152.30000000000001</v>
       </c>
       <c r="D161" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="K161" s="3"/>
     </row>
@@ -3931,13 +3946,13 @@
         <v>6</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C162" s="6">
-        <v>62</v>
+        <v>273</v>
       </c>
       <c r="D162" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="K162" s="3"/>
     </row>
@@ -3946,10 +3961,10 @@
         <v>6</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C163" s="6">
-        <v>79</v>
+        <v>30.5</v>
       </c>
       <c r="D163" t="s">
         <v>175</v>
@@ -3960,39 +3975,41 @@
       <c r="A164" t="s">
         <v>6</v>
       </c>
-      <c r="B164" t="s">
-        <v>178</v>
+      <c r="B164" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="C164" s="6">
-        <v>10.85</v>
+        <v>62</v>
       </c>
       <c r="D164" t="s">
-        <v>179</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="K164" s="3"/>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>6</v>
       </c>
-      <c r="B165" t="s">
-        <v>180</v>
+      <c r="B165" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C165" s="6">
-        <v>10.85</v>
+        <v>79</v>
       </c>
       <c r="D165" t="s">
-        <v>179</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="K165" s="3"/>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>6</v>
       </c>
       <c r="B166" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C166" s="6">
-        <v>9.15</v>
+        <v>10.85</v>
       </c>
       <c r="D166" t="s">
         <v>179</v>
@@ -4003,10 +4020,10 @@
         <v>6</v>
       </c>
       <c r="B167" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C167" s="6">
-        <v>11.5</v>
+        <v>10.85</v>
       </c>
       <c r="D167" t="s">
         <v>179</v>
@@ -4017,7 +4034,7 @@
         <v>6</v>
       </c>
       <c r="B168" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C168" s="6">
         <v>9.15</v>
@@ -4031,7 +4048,7 @@
         <v>6</v>
       </c>
       <c r="B169" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C169" s="6">
         <v>11.5</v>
@@ -4045,10 +4062,10 @@
         <v>6</v>
       </c>
       <c r="B170" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C170" s="6">
-        <v>11.5</v>
+        <v>9.15</v>
       </c>
       <c r="D170" t="s">
         <v>179</v>
@@ -4059,7 +4076,7 @@
         <v>6</v>
       </c>
       <c r="B171" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C171" s="6">
         <v>11.5</v>
@@ -4073,10 +4090,10 @@
         <v>6</v>
       </c>
       <c r="B172" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C172" s="6">
-        <v>11.15</v>
+        <v>11.5</v>
       </c>
       <c r="D172" t="s">
         <v>179</v>
@@ -4087,10 +4104,10 @@
         <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C173" s="6">
-        <v>23.1</v>
+        <v>11.5</v>
       </c>
       <c r="D173" t="s">
         <v>179</v>
@@ -4101,13 +4118,13 @@
         <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C174" s="6">
-        <v>9.25</v>
+        <v>11.15</v>
       </c>
       <c r="D174" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -4115,13 +4132,13 @@
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C175" s="6">
-        <v>11.4</v>
+        <v>23.1</v>
       </c>
       <c r="D175" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -4129,10 +4146,10 @@
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C176" s="6">
-        <v>11.4</v>
+        <v>9.25</v>
       </c>
       <c r="D176" t="s">
         <v>190</v>
@@ -4142,44 +4159,42 @@
       <c r="A177" t="s">
         <v>6</v>
       </c>
-      <c r="B177" s="5" t="s">
-        <v>193</v>
+      <c r="B177" t="s">
+        <v>191</v>
       </c>
       <c r="C177" s="6">
-        <v>42</v>
+        <v>11.4</v>
       </c>
       <c r="D177" t="s">
-        <v>194</v>
-      </c>
-      <c r="K177" s="3"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>6</v>
       </c>
-      <c r="B178" s="3" t="s">
-        <v>195</v>
+      <c r="B178" t="s">
+        <v>192</v>
       </c>
       <c r="C178" s="6">
-        <v>68.25</v>
+        <v>11.4</v>
       </c>
       <c r="D178" t="s">
-        <v>196</v>
-      </c>
-      <c r="K178" s="3"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>6</v>
       </c>
-      <c r="B179" s="3" t="s">
-        <v>197</v>
+      <c r="B179" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="C179" s="6">
-        <v>23.5</v>
+        <v>42</v>
       </c>
       <c r="D179" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K179" s="3"/>
     </row>
@@ -4188,13 +4203,13 @@
         <v>6</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C180" s="6">
-        <v>21.5</v>
+        <v>68.25</v>
       </c>
       <c r="D180" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K180" s="3"/>
     </row>
@@ -4203,13 +4218,13 @@
         <v>6</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C181" s="6">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="D181" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K181" s="3"/>
     </row>
@@ -4218,10 +4233,10 @@
         <v>6</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C182" s="6">
-        <v>25.9</v>
+        <v>21.5</v>
       </c>
       <c r="D182" t="s">
         <v>199</v>
@@ -4233,10 +4248,10 @@
         <v>6</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C183" s="6">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="D183" t="s">
         <v>199</v>
@@ -4248,7 +4263,7 @@
         <v>6</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C184" s="6">
         <v>25.9</v>
@@ -4263,7 +4278,7 @@
         <v>6</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C185" s="6">
         <v>25.9</v>
@@ -4278,7 +4293,7 @@
         <v>6</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C186" s="6">
         <v>25.9</v>
@@ -4293,7 +4308,7 @@
         <v>6</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C187" s="6">
         <v>25.9</v>
@@ -4308,10 +4323,10 @@
         <v>6</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C188" s="6">
-        <v>9.5</v>
+        <v>25.9</v>
       </c>
       <c r="D188" t="s">
         <v>199</v>
@@ -4323,10 +4338,10 @@
         <v>6</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C189" s="6">
-        <v>9.5</v>
+        <v>25.9</v>
       </c>
       <c r="D189" t="s">
         <v>199</v>
@@ -4338,7 +4353,7 @@
         <v>6</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C190" s="6">
         <v>9.5</v>
@@ -4353,13 +4368,13 @@
         <v>6</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C191" s="6">
-        <v>23.15</v>
+        <v>9.5</v>
       </c>
       <c r="D191" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="K191" s="3"/>
     </row>
@@ -4368,13 +4383,13 @@
         <v>6</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C192" s="6">
-        <v>42.65</v>
+        <v>9.5</v>
       </c>
       <c r="D192" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="K192" s="3"/>
     </row>
@@ -4383,10 +4398,10 @@
         <v>6</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C193" s="6">
-        <v>82</v>
+        <v>23.15</v>
       </c>
       <c r="D193" t="s">
         <v>211</v>
@@ -4398,10 +4413,10 @@
         <v>6</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C194" s="6">
-        <v>33.5</v>
+        <v>42.65</v>
       </c>
       <c r="D194" t="s">
         <v>211</v>
@@ -4413,10 +4428,10 @@
         <v>6</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C195" s="6">
-        <v>60.9</v>
+        <v>82</v>
       </c>
       <c r="D195" t="s">
         <v>211</v>
@@ -4428,10 +4443,10 @@
         <v>6</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C196" s="6">
-        <v>118</v>
+        <v>33.5</v>
       </c>
       <c r="D196" t="s">
         <v>211</v>
@@ -4443,10 +4458,10 @@
         <v>6</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C197" s="6">
-        <v>16</v>
+        <v>60.9</v>
       </c>
       <c r="D197" t="s">
         <v>211</v>
@@ -4458,10 +4473,10 @@
         <v>6</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C198" s="6">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D198" t="s">
         <v>211</v>
@@ -4473,10 +4488,10 @@
         <v>6</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C199" s="6">
-        <v>21.32</v>
+        <v>16</v>
       </c>
       <c r="D199" t="s">
         <v>211</v>
@@ -4488,13 +4503,13 @@
         <v>6</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C200" s="6">
-        <v>27.5</v>
+        <v>16</v>
       </c>
       <c r="D200" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="K200" s="3"/>
     </row>
@@ -4503,13 +4518,13 @@
         <v>6</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C201" s="6">
-        <v>7.5</v>
+        <v>21.32</v>
       </c>
       <c r="D201" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="K201" s="3"/>
     </row>
@@ -4518,10 +4533,10 @@
         <v>6</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C202" s="6">
-        <v>11.9</v>
+        <v>27.5</v>
       </c>
       <c r="D202" t="s">
         <v>221</v>
@@ -4533,10 +4548,10 @@
         <v>6</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C203" s="6">
-        <v>18.05</v>
+        <v>7.5</v>
       </c>
       <c r="D203" t="s">
         <v>221</v>
@@ -4548,10 +4563,10 @@
         <v>6</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C204" s="6">
-        <v>4.8499999999999996</v>
+        <v>11.9</v>
       </c>
       <c r="D204" t="s">
         <v>221</v>
@@ -4563,50 +4578,52 @@
         <v>6</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C205" s="6">
-        <v>8</v>
+        <v>18.05</v>
       </c>
       <c r="D205" t="s">
         <v>221</v>
       </c>
       <c r="K205" s="3"/>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>227</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C209" s="6">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="D209" t="s">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>6</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C206" s="6">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="D206" t="s">
+        <v>221</v>
+      </c>
+      <c r="K206" s="3"/>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>6</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C207" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>227</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C210" s="6">
-        <v>9.8800000000000008</v>
-      </c>
-      <c r="D210" t="s">
-        <v>8</v>
-      </c>
+      <c r="D207" t="s">
+        <v>221</v>
+      </c>
+      <c r="K207" s="3"/>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>227</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C211" s="6">
         <v>9.8800000000000008</v>
@@ -4620,10 +4637,10 @@
         <v>227</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>228</v>
+        <v>9</v>
       </c>
       <c r="C212" s="6">
-        <v>11.85</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="D212" t="s">
         <v>8</v>
@@ -4634,10 +4651,10 @@
         <v>227</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C213" s="6">
-        <v>15.44</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="D213" t="s">
         <v>8</v>
@@ -4648,10 +4665,10 @@
         <v>227</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="C214" s="6">
-        <v>18.510000000000002</v>
+        <v>11.85</v>
       </c>
       <c r="D214" t="s">
         <v>8</v>
@@ -4662,10 +4679,10 @@
         <v>227</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C215" s="6">
-        <v>17</v>
+        <v>15.44</v>
       </c>
       <c r="D215" t="s">
         <v>8</v>
@@ -4676,10 +4693,10 @@
         <v>227</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>229</v>
+        <v>12</v>
       </c>
       <c r="C216" s="6">
-        <v>20.6</v>
+        <v>18.510000000000002</v>
       </c>
       <c r="D216" t="s">
         <v>8</v>
@@ -4690,10 +4707,10 @@
         <v>227</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="C217" s="6">
-        <v>29.36</v>
+        <v>17</v>
       </c>
       <c r="D217" t="s">
         <v>8</v>
@@ -4704,10 +4721,10 @@
         <v>227</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C218" s="6">
-        <v>30.9</v>
+        <v>20.6</v>
       </c>
       <c r="D218" t="s">
         <v>8</v>
@@ -4718,10 +4735,10 @@
         <v>227</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C219" s="6">
-        <v>30.9</v>
+        <v>29.36</v>
       </c>
       <c r="D219" t="s">
         <v>8</v>
@@ -4732,10 +4749,10 @@
         <v>227</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C220" s="6">
-        <v>37.6</v>
+        <v>30.9</v>
       </c>
       <c r="D220" t="s">
         <v>8</v>
@@ -4746,13 +4763,13 @@
         <v>227</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>54</v>
+        <v>232</v>
       </c>
       <c r="C221" s="6">
-        <v>133</v>
+        <v>30.9</v>
       </c>
       <c r="D221" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -4760,13 +4777,13 @@
         <v>227</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="C222" s="6">
-        <v>145</v>
+        <v>37.6</v>
       </c>
       <c r="D222" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -4774,7 +4791,7 @@
         <v>227</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C223" s="6">
         <v>133</v>
@@ -4788,7 +4805,7 @@
         <v>227</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C224" s="6">
         <v>145</v>
@@ -4802,10 +4819,10 @@
         <v>227</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C225" s="6">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="D225" t="s">
         <v>55</v>
@@ -4816,10 +4833,10 @@
         <v>227</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C226" s="6">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="D226" t="s">
         <v>55</v>
@@ -4830,10 +4847,10 @@
         <v>227</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C227" s="6">
-        <v>292</v>
+        <v>192</v>
       </c>
       <c r="D227" t="s">
         <v>55</v>
@@ -4844,10 +4861,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C228" s="6">
-        <v>262.64999999999998</v>
+        <v>230</v>
       </c>
       <c r="D228" t="s">
         <v>55</v>
@@ -4858,10 +4875,10 @@
         <v>227</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C229" s="6">
-        <v>272.95</v>
+        <v>292</v>
       </c>
       <c r="D229" t="s">
         <v>55</v>
@@ -4872,10 +4889,10 @@
         <v>227</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C230" s="6">
-        <v>136</v>
+        <v>262.64999999999998</v>
       </c>
       <c r="D230" t="s">
         <v>55</v>
@@ -4886,10 +4903,10 @@
         <v>227</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C231" s="6">
-        <v>125</v>
+        <v>272.95</v>
       </c>
       <c r="D231" t="s">
         <v>55</v>
@@ -4900,10 +4917,10 @@
         <v>227</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C232" s="6">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="D232" t="s">
         <v>55</v>
@@ -4914,13 +4931,13 @@
         <v>227</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C233" s="6">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="D233" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -4928,13 +4945,13 @@
         <v>227</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C234" s="6">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="D234" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -4942,52 +4959,52 @@
         <v>227</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="C235" s="6">
-        <v>450</v>
+        <v>13</v>
       </c>
       <c r="D235" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>227</v>
       </c>
-      <c r="B236" s="4">
-        <v>6102</v>
-      </c>
-      <c r="C236" s="8">
-        <v>23.86</v>
+      <c r="B236" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C236" s="6">
+        <v>17</v>
       </c>
       <c r="D236" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>227</v>
       </c>
-      <c r="B237" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C237" s="8">
-        <v>35.5</v>
+      <c r="B237" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C237" s="6">
+        <v>450</v>
       </c>
       <c r="D237" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>227</v>
       </c>
-      <c r="B238" s="4" t="s">
-        <v>81</v>
+      <c r="B238" s="4">
+        <v>6102</v>
       </c>
       <c r="C238" s="8">
-        <v>32</v>
+        <v>23.86</v>
       </c>
       <c r="D238" t="s">
         <v>79</v>
@@ -4998,10 +5015,10 @@
         <v>227</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C239" s="8">
-        <v>47</v>
+        <v>35.5</v>
       </c>
       <c r="D239" t="s">
         <v>79</v>
@@ -5012,10 +5029,10 @@
         <v>227</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C240" s="8">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D240" t="s">
         <v>79</v>
@@ -5026,10 +5043,10 @@
         <v>227</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C241" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D241" t="s">
         <v>79</v>
@@ -5040,10 +5057,10 @@
         <v>227</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C242" s="8">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D242" t="s">
         <v>79</v>
@@ -5054,13 +5071,13 @@
         <v>227</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C243" s="8">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D243" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -5068,13 +5085,13 @@
         <v>227</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C244" s="8">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="D244" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -5082,10 +5099,10 @@
         <v>227</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C245" s="8">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D245" t="s">
         <v>102</v>
@@ -5096,10 +5113,10 @@
         <v>227</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C246" s="8">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D246" t="s">
         <v>102</v>
@@ -5110,10 +5127,10 @@
         <v>227</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C247" s="8">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D247" t="s">
         <v>102</v>
@@ -5124,10 +5141,10 @@
         <v>227</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C248" s="8">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D248" t="s">
         <v>102</v>
@@ -5138,38 +5155,38 @@
         <v>227</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="C249" s="8">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D249" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>227</v>
       </c>
-      <c r="B250" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C250" s="6">
-        <v>24</v>
+      <c r="B250" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C250" s="8">
+        <v>75</v>
       </c>
       <c r="D250" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>227</v>
       </c>
-      <c r="B251" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C251" s="6">
-        <v>48</v>
+      <c r="B251" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C251" s="8">
+        <v>38</v>
       </c>
       <c r="D251" t="s">
         <v>109</v>
@@ -5180,10 +5197,10 @@
         <v>227</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C252" s="6">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="D252" t="s">
         <v>109</v>
@@ -5194,10 +5211,10 @@
         <v>227</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C253" s="6">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D253" t="s">
         <v>109</v>
@@ -5208,10 +5225,10 @@
         <v>227</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C254" s="6">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="D254" t="s">
         <v>109</v>
@@ -5222,10 +5239,10 @@
         <v>227</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C255" s="6">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="D255" t="s">
         <v>109</v>
@@ -5236,10 +5253,10 @@
         <v>227</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>235</v>
+        <v>115</v>
       </c>
       <c r="C256" s="6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D256" t="s">
         <v>109</v>
@@ -5250,13 +5267,13 @@
         <v>227</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C257" s="6">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="D257" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -5264,16 +5281,13 @@
         <v>227</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C258" s="6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>118</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -5281,16 +5295,13 @@
         <v>227</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>351</v>
+        <v>117</v>
       </c>
       <c r="C259" s="6">
-        <v>20.100000000000001</v>
+        <v>37</v>
       </c>
       <c r="D259" t="s">
         <v>118</v>
-      </c>
-      <c r="E259" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -5298,13 +5309,16 @@
         <v>227</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>354</v>
+        <v>236</v>
       </c>
       <c r="C260" s="6">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D260" t="s">
         <v>118</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -5312,13 +5326,16 @@
         <v>227</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>119</v>
+        <v>351</v>
       </c>
       <c r="C261" s="6">
-        <v>16</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="D261" t="s">
         <v>118</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
@@ -5326,10 +5343,10 @@
         <v>227</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>120</v>
+        <v>354</v>
       </c>
       <c r="C262" s="6">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D262" t="s">
         <v>118</v>
@@ -5340,10 +5357,10 @@
         <v>227</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>355</v>
+        <v>119</v>
       </c>
       <c r="C263" s="6">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="D263" t="s">
         <v>118</v>
@@ -5354,16 +5371,13 @@
         <v>227</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>353</v>
+        <v>120</v>
       </c>
       <c r="C264" s="6">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="D264" t="s">
         <v>118</v>
-      </c>
-      <c r="E264" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
@@ -5371,10 +5385,10 @@
         <v>227</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C265" s="6">
-        <v>15.35</v>
+        <v>110</v>
       </c>
       <c r="D265" t="s">
         <v>118</v>
@@ -5385,41 +5399,44 @@
         <v>227</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>153</v>
+        <v>353</v>
       </c>
       <c r="C266" s="6">
-        <v>60</v>
+        <v>11.5</v>
       </c>
       <c r="D266" t="s">
-        <v>154</v>
+        <v>118</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>227</v>
       </c>
-      <c r="B267" s="3">
-        <v>4430</v>
+      <c r="B267" s="3" t="s">
+        <v>352</v>
       </c>
       <c r="C267" s="6">
-        <v>12.6</v>
+        <v>15.35</v>
       </c>
       <c r="D267" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>227</v>
       </c>
-      <c r="B268" s="3">
-        <v>4442</v>
+      <c r="B268" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="C268" s="6">
-        <v>14.53</v>
+        <v>60</v>
       </c>
       <c r="D268" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
@@ -5427,10 +5444,10 @@
         <v>227</v>
       </c>
       <c r="B269" s="3">
-        <v>4642</v>
+        <v>4430</v>
       </c>
       <c r="C269" s="6">
-        <v>20.8</v>
+        <v>12.6</v>
       </c>
       <c r="D269" t="s">
         <v>156</v>
@@ -5441,10 +5458,10 @@
         <v>227</v>
       </c>
       <c r="B270" s="3">
-        <v>4660</v>
+        <v>4442</v>
       </c>
       <c r="C270" s="6">
-        <v>27</v>
+        <v>14.53</v>
       </c>
       <c r="D270" t="s">
         <v>156</v>
@@ -5455,10 +5472,10 @@
         <v>227</v>
       </c>
       <c r="B271" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C271" s="6">
-        <v>18.52</v>
+        <v>20.8</v>
       </c>
       <c r="D271" t="s">
         <v>156</v>
@@ -5468,8 +5485,11 @@
       <c r="A272" t="s">
         <v>227</v>
       </c>
-      <c r="B272" s="3" t="s">
-        <v>164</v>
+      <c r="B272" s="3">
+        <v>4660</v>
+      </c>
+      <c r="C272" s="6">
+        <v>27</v>
       </c>
       <c r="D272" t="s">
         <v>156</v>
@@ -5480,10 +5500,10 @@
         <v>227</v>
       </c>
       <c r="B273" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C273" s="6">
-        <v>27.05</v>
+        <v>18.52</v>
       </c>
       <c r="D273" t="s">
         <v>156</v>
@@ -5494,10 +5514,7 @@
         <v>227</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C274" s="6">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D274" t="s">
         <v>156</v>
@@ -5508,10 +5525,10 @@
         <v>227</v>
       </c>
       <c r="B275" s="3">
-        <v>8860</v>
+        <v>6660</v>
       </c>
       <c r="C275" s="6">
-        <v>63.9</v>
+        <v>27.05</v>
       </c>
       <c r="D275" t="s">
         <v>156</v>
@@ -5522,27 +5539,27 @@
         <v>227</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C276" s="6">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="D276" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>227</v>
       </c>
-      <c r="B277" s="3" t="s">
-        <v>168</v>
+      <c r="B277" s="3">
+        <v>8860</v>
       </c>
       <c r="C277" s="6">
-        <v>22.75</v>
+        <v>63.9</v>
       </c>
       <c r="D277" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -5550,10 +5567,10 @@
         <v>227</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C278" s="6">
-        <v>18.25</v>
+        <v>92</v>
       </c>
       <c r="D278" t="s">
         <v>167</v>
@@ -5564,10 +5581,10 @@
         <v>227</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C279" s="6">
-        <v>115</v>
+        <v>22.75</v>
       </c>
       <c r="D279" t="s">
         <v>167</v>
@@ -5578,10 +5595,10 @@
         <v>227</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C280" s="6">
-        <v>227</v>
+        <v>18.25</v>
       </c>
       <c r="D280" t="s">
         <v>167</v>
@@ -5592,13 +5609,13 @@
         <v>227</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="C281" s="6">
-        <v>41.5</v>
+        <v>115</v>
       </c>
       <c r="D281" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -5606,13 +5623,13 @@
         <v>227</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="C282" s="6">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="D282" t="s">
-        <v>238</v>
+        <v>167</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -5620,13 +5637,13 @@
         <v>227</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>239</v>
+        <v>193</v>
       </c>
       <c r="C283" s="6">
-        <v>23</v>
+        <v>41.5</v>
       </c>
       <c r="D283" t="s">
-        <v>238</v>
+        <v>194</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -5634,10 +5651,10 @@
         <v>227</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C284" s="6">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="D284" t="s">
         <v>238</v>
@@ -5648,13 +5665,13 @@
         <v>227</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="C285" s="6">
-        <v>23.15</v>
+        <v>23</v>
       </c>
       <c r="D285" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -5662,13 +5679,13 @@
         <v>227</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="C286" s="6">
-        <v>42.65</v>
+        <v>78</v>
       </c>
       <c r="D286" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -5676,10 +5693,10 @@
         <v>227</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C287" s="6">
-        <v>82</v>
+        <v>23.15</v>
       </c>
       <c r="D287" t="s">
         <v>211</v>
@@ -5690,10 +5707,10 @@
         <v>227</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C288" s="6">
-        <v>33.5</v>
+        <v>42.65</v>
       </c>
       <c r="D288" t="s">
         <v>211</v>
@@ -5704,10 +5721,10 @@
         <v>227</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C289" s="6">
-        <v>60.9</v>
+        <v>82</v>
       </c>
       <c r="D289" t="s">
         <v>211</v>
@@ -5718,10 +5735,10 @@
         <v>227</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C290" s="6">
-        <v>118</v>
+        <v>33.5</v>
       </c>
       <c r="D290" t="s">
         <v>211</v>
@@ -5732,10 +5749,10 @@
         <v>227</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C291" s="6">
-        <v>16</v>
+        <v>60.9</v>
       </c>
       <c r="D291" t="s">
         <v>211</v>
@@ -5746,10 +5763,10 @@
         <v>227</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C292" s="6">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D292" t="s">
         <v>211</v>
@@ -5760,10 +5777,10 @@
         <v>227</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C293" s="6">
-        <v>21.32</v>
+        <v>16</v>
       </c>
       <c r="D293" t="s">
         <v>211</v>
@@ -5774,13 +5791,13 @@
         <v>227</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="C294" s="6">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D294" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -5788,13 +5805,13 @@
         <v>227</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="C295" s="6">
-        <v>33</v>
+        <v>21.32</v>
       </c>
       <c r="D295" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -5802,10 +5819,10 @@
         <v>227</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C296" s="6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D296" t="s">
         <v>242</v>
@@ -5816,10 +5833,10 @@
         <v>227</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C297" s="6">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D297" t="s">
         <v>242</v>
@@ -5830,10 +5847,10 @@
         <v>227</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C298" s="6">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="D298" t="s">
         <v>242</v>
@@ -5844,10 +5861,10 @@
         <v>227</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C299" s="6">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="D299" t="s">
         <v>242</v>
@@ -5858,41 +5875,41 @@
         <v>227</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C300" s="6">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="D300" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>249</v>
-      </c>
-      <c r="B305" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C305" s="6">
-        <v>9.6</v>
-      </c>
-      <c r="D305" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>249</v>
-      </c>
-      <c r="B306" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C306" s="6">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="D306" t="s">
-        <v>8</v>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>227</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C301" s="6">
+        <v>114</v>
+      </c>
+      <c r="D301" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>227</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C302" s="6">
+        <v>126</v>
+      </c>
+      <c r="D302" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -5900,7 +5917,7 @@
         <v>249</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C307" s="6">
         <v>9.6</v>
@@ -5914,10 +5931,10 @@
         <v>249</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>228</v>
+        <v>9</v>
       </c>
       <c r="C308" s="6">
-        <v>11.5</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="D308" t="s">
         <v>8</v>
@@ -5928,10 +5945,10 @@
         <v>249</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C309" s="6">
-        <v>14.99</v>
+        <v>9.6</v>
       </c>
       <c r="D309" t="s">
         <v>8</v>
@@ -5942,10 +5959,10 @@
         <v>249</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="C310" s="6">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="D310" t="s">
         <v>8</v>
@@ -5956,10 +5973,10 @@
         <v>249</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C311" s="6">
-        <v>17.97</v>
+        <v>14.99</v>
       </c>
       <c r="D311" t="s">
         <v>8</v>
@@ -5970,10 +5987,10 @@
         <v>249</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>229</v>
+        <v>12</v>
       </c>
       <c r="C312" s="6">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="D312" t="s">
         <v>8</v>
@@ -5984,10 +6001,10 @@
         <v>249</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="C313" s="6">
-        <v>28.5</v>
+        <v>17.97</v>
       </c>
       <c r="D313" t="s">
         <v>8</v>
@@ -5998,10 +6015,10 @@
         <v>249</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C314" s="6">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D314" t="s">
         <v>8</v>
@@ -6012,10 +6029,10 @@
         <v>249</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C315" s="6">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="D315" t="s">
         <v>8</v>
@@ -6026,10 +6043,10 @@
         <v>249</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C316" s="6">
-        <v>36.5</v>
+        <v>30</v>
       </c>
       <c r="D316" t="s">
         <v>8</v>
@@ -6040,10 +6057,10 @@
         <v>249</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C317" s="6">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="D317" t="s">
         <v>8</v>
@@ -6053,56 +6070,56 @@
       <c r="A318" t="s">
         <v>249</v>
       </c>
-      <c r="B318" t="s">
-        <v>48</v>
+      <c r="B318" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="C318" s="6">
-        <v>42.9</v>
+        <v>36.5</v>
       </c>
       <c r="D318" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>249</v>
       </c>
-      <c r="B319" t="s">
-        <v>52</v>
+      <c r="B319" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="C319" s="6">
-        <v>42.9</v>
+        <v>16.5</v>
       </c>
       <c r="D319" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>249</v>
       </c>
-      <c r="B320" s="3" t="s">
-        <v>54</v>
+      <c r="B320" t="s">
+        <v>48</v>
       </c>
       <c r="C320" s="6">
-        <v>98.5</v>
+        <v>42.9</v>
       </c>
       <c r="D320" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>249</v>
       </c>
-      <c r="B321" s="3" t="s">
-        <v>56</v>
+      <c r="B321" t="s">
+        <v>52</v>
       </c>
       <c r="C321" s="6">
-        <v>105</v>
+        <v>42.9</v>
       </c>
       <c r="D321" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -6110,7 +6127,7 @@
         <v>249</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C322" s="6">
         <v>98.5</v>
@@ -6124,7 +6141,7 @@
         <v>249</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C323" s="6">
         <v>105</v>
@@ -6138,10 +6155,10 @@
         <v>249</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C324" s="6">
-        <v>142</v>
+        <v>98.5</v>
       </c>
       <c r="D324" t="s">
         <v>55</v>
@@ -6152,10 +6169,10 @@
         <v>249</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C325" s="6">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="D325" t="s">
         <v>55</v>
@@ -6166,10 +6183,10 @@
         <v>249</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C326" s="6">
-        <v>234</v>
+        <v>142</v>
       </c>
       <c r="D326" t="s">
         <v>55</v>
@@ -6180,10 +6197,10 @@
         <v>249</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C327" s="6">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="D327" t="s">
         <v>55</v>
@@ -6194,10 +6211,10 @@
         <v>249</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C328" s="6">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D328" t="s">
         <v>55</v>
@@ -6208,10 +6225,10 @@
         <v>249</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C329" s="6">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="D329" t="s">
         <v>55</v>
@@ -6222,10 +6239,10 @@
         <v>249</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>251</v>
+        <v>63</v>
       </c>
       <c r="C330" s="6">
-        <v>130</v>
+        <v>265</v>
       </c>
       <c r="D330" t="s">
         <v>55</v>
@@ -6236,10 +6253,10 @@
         <v>249</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C331" s="6">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="D331" t="s">
         <v>55</v>
@@ -6250,13 +6267,13 @@
         <v>249</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>44</v>
+        <v>251</v>
       </c>
       <c r="C332" s="6">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="D332" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -6264,13 +6281,13 @@
         <v>249</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C333" s="6">
-        <v>475</v>
+        <v>58</v>
       </c>
       <c r="D333" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -6278,10 +6295,13 @@
         <v>249</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>252</v>
+        <v>44</v>
+      </c>
+      <c r="C334" s="6">
+        <v>18</v>
       </c>
       <c r="D334" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -6289,13 +6309,13 @@
         <v>249</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="C335" s="6">
-        <v>15.58</v>
+        <v>475</v>
       </c>
       <c r="D335" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -6303,13 +6323,10 @@
         <v>249</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C336" s="6">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="D336" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -6317,13 +6334,13 @@
         <v>249</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>111</v>
+        <v>253</v>
       </c>
       <c r="C337" s="6">
-        <v>21</v>
+        <v>15.58</v>
       </c>
       <c r="D337" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -6331,10 +6348,10 @@
         <v>249</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C338" s="6">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D338" t="s">
         <v>109</v>
@@ -6345,10 +6362,10 @@
         <v>249</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C339" s="6">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="D339" t="s">
         <v>109</v>
@@ -6358,11 +6375,11 @@
       <c r="A340" t="s">
         <v>249</v>
       </c>
-      <c r="B340" t="s">
-        <v>114</v>
+      <c r="B340" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C340" s="6">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D340" t="s">
         <v>109</v>
@@ -6372,11 +6389,11 @@
       <c r="A341" t="s">
         <v>249</v>
       </c>
-      <c r="B341" t="s">
-        <v>115</v>
+      <c r="B341" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="C341" s="6">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D341" t="s">
         <v>109</v>
@@ -6387,10 +6404,10 @@
         <v>249</v>
       </c>
       <c r="B342" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C342" s="6">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="D342" t="s">
         <v>109</v>
@@ -6400,39 +6417,39 @@
       <c r="A343" t="s">
         <v>249</v>
       </c>
-      <c r="B343" s="3" t="s">
-        <v>117</v>
+      <c r="B343" t="s">
+        <v>115</v>
       </c>
       <c r="C343" s="6">
-        <v>33.5</v>
+        <v>28</v>
       </c>
       <c r="D343" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>249</v>
       </c>
-      <c r="B344" s="3" t="s">
-        <v>119</v>
+      <c r="B344" t="s">
+        <v>116</v>
       </c>
       <c r="C344" s="6">
-        <v>15.1</v>
+        <v>102</v>
       </c>
       <c r="D344" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>249</v>
       </c>
-      <c r="B345" t="s">
-        <v>120</v>
+      <c r="B345" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C345" s="6">
-        <v>38.28</v>
+        <v>33.5</v>
       </c>
       <c r="D345" t="s">
         <v>118</v>
@@ -6443,10 +6460,10 @@
         <v>249</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C346" s="6">
-        <v>22.36</v>
+        <v>15.1</v>
       </c>
       <c r="D346" t="s">
         <v>118</v>
@@ -6456,17 +6473,14 @@
       <c r="A347" t="s">
         <v>249</v>
       </c>
-      <c r="B347" s="3" t="s">
-        <v>254</v>
+      <c r="B347" t="s">
+        <v>120</v>
       </c>
       <c r="C347" s="6">
-        <v>23.68</v>
+        <v>38.28</v>
       </c>
       <c r="D347" t="s">
         <v>118</v>
-      </c>
-      <c r="E347" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -6474,10 +6488,10 @@
         <v>249</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C348" s="6">
-        <v>10</v>
+        <v>22.36</v>
       </c>
       <c r="D348" t="s">
         <v>118</v>
@@ -6488,13 +6502,16 @@
         <v>249</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C349" s="6">
-        <v>87</v>
+        <v>23.68</v>
       </c>
       <c r="D349" t="s">
-        <v>134</v>
+        <v>118</v>
+      </c>
+      <c r="E349" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
@@ -6502,13 +6519,13 @@
         <v>249</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>256</v>
+        <v>124</v>
       </c>
       <c r="C350" s="6">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="D350" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
@@ -6516,10 +6533,10 @@
         <v>249</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C351" s="6">
-        <v>421.08</v>
+        <v>87</v>
       </c>
       <c r="D351" t="s">
         <v>134</v>
@@ -6530,10 +6547,13 @@
         <v>249</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>158</v>
+        <v>256</v>
+      </c>
+      <c r="C352" s="6">
+        <v>225</v>
       </c>
       <c r="D352" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
@@ -6541,13 +6561,13 @@
         <v>249</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>153</v>
+        <v>257</v>
       </c>
       <c r="C353" s="6">
-        <v>60</v>
+        <v>421.08</v>
       </c>
       <c r="D353" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
@@ -6555,16 +6575,10 @@
         <v>249</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C354">
-        <v>6.25</v>
+        <v>158</v>
       </c>
       <c r="D354" t="s">
         <v>156</v>
-      </c>
-      <c r="E354" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -6572,55 +6586,58 @@
         <v>249</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C355">
-        <v>6.75</v>
+        <v>153</v>
+      </c>
+      <c r="C355" s="6">
+        <v>60</v>
       </c>
       <c r="D355" t="s">
-        <v>156</v>
-      </c>
-      <c r="E355" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>249</v>
       </c>
-      <c r="B356" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C356" s="6">
-        <v>15.25</v>
+      <c r="B356" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C356">
+        <v>6.25</v>
       </c>
       <c r="D356" t="s">
         <v>156</v>
+      </c>
+      <c r="E356" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>249</v>
       </c>
-      <c r="B357" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C357" s="6">
-        <v>18.899999999999999</v>
+      <c r="B357" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C357">
+        <v>6.75</v>
       </c>
       <c r="D357" t="s">
         <v>156</v>
+      </c>
+      <c r="E357" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>249</v>
       </c>
-      <c r="B358" s="3" t="s">
-        <v>161</v>
+      <c r="B358" s="3">
+        <v>4430</v>
       </c>
       <c r="C358" s="6">
-        <v>193</v>
+        <v>15.25</v>
       </c>
       <c r="D358" t="s">
         <v>156</v>
@@ -6630,8 +6647,11 @@
       <c r="A359" t="s">
         <v>249</v>
       </c>
-      <c r="B359" s="3" t="s">
-        <v>162</v>
+      <c r="B359" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C359" s="6">
+        <v>18.899999999999999</v>
       </c>
       <c r="D359" t="s">
         <v>156</v>
@@ -6641,11 +6661,11 @@
       <c r="A360" t="s">
         <v>249</v>
       </c>
-      <c r="B360" s="3">
-        <v>4642</v>
+      <c r="B360" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="C360" s="6">
-        <v>20.8</v>
+        <v>193</v>
       </c>
       <c r="D360" t="s">
         <v>156</v>
@@ -6656,7 +6676,7 @@
         <v>249</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D361" t="s">
         <v>156</v>
@@ -6667,10 +6687,10 @@
         <v>249</v>
       </c>
       <c r="B362" s="3">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C362" s="6">
-        <v>24.7</v>
+        <v>20.8</v>
       </c>
       <c r="D362" t="s">
         <v>156</v>
@@ -6680,11 +6700,8 @@
       <c r="A363" t="s">
         <v>249</v>
       </c>
-      <c r="B363" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C363" s="6">
-        <v>26.8</v>
+      <c r="B363" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="D363" t="s">
         <v>156</v>
@@ -6694,11 +6711,11 @@
       <c r="A364" t="s">
         <v>249</v>
       </c>
-      <c r="B364" s="3" t="s">
-        <v>164</v>
+      <c r="B364" s="3">
+        <v>4660</v>
       </c>
       <c r="C364" s="6">
-        <v>115</v>
+        <v>24.7</v>
       </c>
       <c r="D364" t="s">
         <v>156</v>
@@ -6709,10 +6726,10 @@
         <v>249</v>
       </c>
       <c r="B365" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C365" s="6">
-        <v>27.05</v>
+        <v>26.8</v>
       </c>
       <c r="D365" t="s">
         <v>156</v>
@@ -6723,10 +6740,10 @@
         <v>249</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C366" s="6">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="D366" t="s">
         <v>156</v>
@@ -6736,14 +6753,14 @@
       <c r="A367" t="s">
         <v>249</v>
       </c>
-      <c r="B367" s="3" t="s">
-        <v>258</v>
+      <c r="B367" s="3">
+        <v>6660</v>
       </c>
       <c r="C367" s="6">
-        <v>30.5</v>
+        <v>27.05</v>
       </c>
       <c r="D367" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
@@ -6751,13 +6768,13 @@
         <v>249</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
       <c r="C368" s="6">
-        <v>12.75</v>
+        <v>160</v>
       </c>
       <c r="D368" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -6765,13 +6782,13 @@
         <v>249</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="C369" s="6">
-        <v>12.75</v>
+        <v>30.5</v>
       </c>
       <c r="D369" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -6779,10 +6796,10 @@
         <v>249</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>182</v>
+        <v>259</v>
       </c>
       <c r="C370" s="6">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="D370" t="s">
         <v>179</v>
@@ -6793,10 +6810,10 @@
         <v>249</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C371" s="6">
-        <v>10.3</v>
+        <v>12.75</v>
       </c>
       <c r="D371" t="s">
         <v>179</v>
@@ -6807,10 +6824,10 @@
         <v>249</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C372" s="6">
-        <v>11.85</v>
+        <v>13.25</v>
       </c>
       <c r="D372" t="s">
         <v>179</v>
@@ -6821,10 +6838,10 @@
         <v>249</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C373" s="6">
-        <v>12.75</v>
+        <v>10.3</v>
       </c>
       <c r="D373" t="s">
         <v>179</v>
@@ -6835,10 +6852,10 @@
         <v>249</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C374" s="6">
-        <v>10.3</v>
+        <v>11.85</v>
       </c>
       <c r="D374" t="s">
         <v>179</v>
@@ -6849,10 +6866,10 @@
         <v>249</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C375" s="6">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="D375" t="s">
         <v>179</v>
@@ -6863,10 +6880,10 @@
         <v>249</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="C376" s="6">
-        <v>12.75</v>
+        <v>10.3</v>
       </c>
       <c r="D376" t="s">
         <v>179</v>
@@ -6877,13 +6894,13 @@
         <v>249</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="C377" s="6">
-        <v>21.5</v>
+        <v>13.25</v>
       </c>
       <c r="D377" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -6891,13 +6908,13 @@
         <v>249</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="C378" s="6">
-        <v>22.5</v>
+        <v>12.75</v>
       </c>
       <c r="D378" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -6905,10 +6922,10 @@
         <v>249</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C379" s="6">
-        <v>10.5</v>
+        <v>21.5</v>
       </c>
       <c r="D379" t="s">
         <v>199</v>
@@ -6919,10 +6936,10 @@
         <v>249</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C380" s="6">
-        <v>10.5</v>
+        <v>22.5</v>
       </c>
       <c r="D380" t="s">
         <v>199</v>
@@ -6933,7 +6950,7 @@
         <v>249</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C381" s="6">
         <v>10.5</v>
@@ -6947,10 +6964,13 @@
         <v>249</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>237</v>
+        <v>208</v>
+      </c>
+      <c r="C382" s="6">
+        <v>10.5</v>
       </c>
       <c r="D382" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -6958,13 +6978,13 @@
         <v>249</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="C383" s="6">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="D383" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -6972,7 +6992,7 @@
         <v>249</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D384" t="s">
         <v>238</v>
@@ -6983,13 +7003,13 @@
         <v>249</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="C385" s="6">
-        <v>23.15</v>
+        <v>23</v>
       </c>
       <c r="D385" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
@@ -6997,13 +7017,10 @@
         <v>249</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C386" s="6">
-        <v>42.65</v>
+        <v>240</v>
       </c>
       <c r="D386" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
@@ -7011,10 +7028,10 @@
         <v>249</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C387" s="6">
-        <v>82</v>
+        <v>23.15</v>
       </c>
       <c r="D387" t="s">
         <v>211</v>
@@ -7025,10 +7042,10 @@
         <v>249</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C388" s="6">
-        <v>33.5</v>
+        <v>42.65</v>
       </c>
       <c r="D388" t="s">
         <v>211</v>
@@ -7039,10 +7056,10 @@
         <v>249</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C389" s="6">
-        <v>60.9</v>
+        <v>82</v>
       </c>
       <c r="D389" t="s">
         <v>211</v>
@@ -7053,10 +7070,10 @@
         <v>249</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C390" s="6">
-        <v>118</v>
+        <v>33.5</v>
       </c>
       <c r="D390" t="s">
         <v>211</v>
@@ -7067,10 +7084,10 @@
         <v>249</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C391" s="6">
-        <v>16</v>
+        <v>60.9</v>
       </c>
       <c r="D391" t="s">
         <v>211</v>
@@ -7081,10 +7098,10 @@
         <v>249</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C392" s="6">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D392" t="s">
         <v>211</v>
@@ -7095,10 +7112,10 @@
         <v>249</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C393" s="6">
-        <v>21.32</v>
+        <v>16</v>
       </c>
       <c r="D393" t="s">
         <v>211</v>
@@ -7109,13 +7126,13 @@
         <v>249</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C394" s="6">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D394" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
@@ -7123,16 +7140,13 @@
         <v>249</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C395">
-        <v>7.5</v>
+        <v>219</v>
+      </c>
+      <c r="C395" s="6">
+        <v>21.32</v>
       </c>
       <c r="D395" t="s">
-        <v>221</v>
-      </c>
-      <c r="E395" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
@@ -7140,10 +7154,10 @@
         <v>249</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C396" s="6">
-        <v>13.42</v>
+        <v>26</v>
       </c>
       <c r="D396" t="s">
         <v>221</v>
@@ -7154,10 +7168,16 @@
         <v>249</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+      <c r="C397">
+        <v>7.5</v>
       </c>
       <c r="D397" t="s">
         <v>221</v>
+      </c>
+      <c r="E397" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -7165,7 +7185,10 @@
         <v>249</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
+      </c>
+      <c r="C398" s="6">
+        <v>13.42</v>
       </c>
       <c r="D398" t="s">
         <v>221</v>
@@ -7176,41 +7199,35 @@
         <v>249</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C399" s="6">
-        <v>9.5399999999999991</v>
+        <v>224</v>
       </c>
       <c r="D399" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A402" t="s">
-        <v>261</v>
-      </c>
-      <c r="B402" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C402" s="6">
-        <v>14.5</v>
-      </c>
-      <c r="D402" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A403" t="s">
-        <v>261</v>
-      </c>
-      <c r="B403" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C403" s="6">
-        <v>24.99</v>
-      </c>
-      <c r="D403" t="s">
-        <v>25</v>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>249</v>
+      </c>
+      <c r="B400" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D400" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>249</v>
+      </c>
+      <c r="B401" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C401" s="6">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="D401" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -7218,13 +7235,13 @@
         <v>261</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
       <c r="C404" s="6">
-        <v>34.99</v>
+        <v>14.5</v>
       </c>
       <c r="D404" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -7232,13 +7249,13 @@
         <v>261</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C405" s="6">
-        <v>19.989999999999998</v>
+        <v>24.99</v>
       </c>
       <c r="D405" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -7246,13 +7263,13 @@
         <v>261</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C406" s="6">
-        <v>29.99</v>
+        <v>34.99</v>
       </c>
       <c r="D406" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -7260,13 +7277,13 @@
         <v>261</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C407" s="6">
-        <v>189.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D407" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -7274,13 +7291,13 @@
         <v>261</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C408" s="6">
-        <v>229.99</v>
+        <v>29.99</v>
       </c>
       <c r="D408" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -7288,10 +7305,10 @@
         <v>261</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>263</v>
+        <v>57</v>
       </c>
       <c r="C409" s="6">
-        <v>299.99</v>
+        <v>189.99</v>
       </c>
       <c r="D409" t="s">
         <v>55</v>
@@ -7302,10 +7319,10 @@
         <v>261</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C410" s="6">
-        <v>189.99</v>
+        <v>229.99</v>
       </c>
       <c r="D410" t="s">
         <v>55</v>
@@ -7316,10 +7333,10 @@
         <v>261</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>56</v>
+        <v>263</v>
       </c>
       <c r="C411" s="6">
-        <v>229</v>
+        <v>299.99</v>
       </c>
       <c r="D411" t="s">
         <v>55</v>
@@ -7330,10 +7347,10 @@
         <v>261</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>264</v>
+        <v>54</v>
       </c>
       <c r="C412" s="6">
-        <v>299.99</v>
+        <v>189.99</v>
       </c>
       <c r="D412" t="s">
         <v>55</v>
@@ -7344,10 +7361,10 @@
         <v>261</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C413" s="6">
-        <v>309</v>
+        <v>229</v>
       </c>
       <c r="D413" t="s">
         <v>55</v>
@@ -7358,10 +7375,10 @@
         <v>261</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>60</v>
+        <v>264</v>
       </c>
       <c r="C414" s="6">
-        <v>345</v>
+        <v>299.99</v>
       </c>
       <c r="D414" t="s">
         <v>55</v>
@@ -7372,10 +7389,10 @@
         <v>261</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C415" s="6">
-        <v>409</v>
+        <v>309</v>
       </c>
       <c r="D415" t="s">
         <v>55</v>
@@ -7386,10 +7403,10 @@
         <v>261</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C416" s="6">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="D416" t="s">
         <v>55</v>
@@ -7400,10 +7417,10 @@
         <v>261</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>265</v>
+        <v>61</v>
       </c>
       <c r="C417" s="6">
-        <v>389.99</v>
+        <v>409</v>
       </c>
       <c r="D417" t="s">
         <v>55</v>
@@ -7414,10 +7431,10 @@
         <v>261</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C418" s="6">
-        <v>399.99</v>
+        <v>389</v>
       </c>
       <c r="D418" t="s">
         <v>55</v>
@@ -7428,10 +7445,10 @@
         <v>261</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C419" s="6">
-        <v>399.99</v>
+        <v>389.99</v>
       </c>
       <c r="D419" t="s">
         <v>55</v>
@@ -7442,10 +7459,10 @@
         <v>261</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C420" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D420" t="s">
         <v>55</v>
@@ -7456,7 +7473,10 @@
         <v>261</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>65</v>
+        <v>266</v>
+      </c>
+      <c r="C421" s="6">
+        <v>399.99</v>
       </c>
       <c r="D421" t="s">
         <v>55</v>
@@ -7467,10 +7487,10 @@
         <v>261</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C422" s="6">
-        <v>219.99</v>
+        <v>89.23</v>
       </c>
       <c r="D422" t="s">
         <v>55</v>
@@ -7481,10 +7501,7 @@
         <v>261</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C423" s="6">
-        <v>429</v>
+        <v>65</v>
       </c>
       <c r="D423" t="s">
         <v>55</v>
@@ -7495,10 +7512,10 @@
         <v>261</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>268</v>
+        <v>64</v>
       </c>
       <c r="C424" s="6">
-        <v>439</v>
+        <v>219.99</v>
       </c>
       <c r="D424" t="s">
         <v>55</v>
@@ -7509,10 +7526,10 @@
         <v>261</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C425" s="6">
-        <v>199</v>
+        <v>429</v>
       </c>
       <c r="D425" t="s">
         <v>55</v>
@@ -7523,10 +7540,10 @@
         <v>261</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C426" s="6">
-        <v>249</v>
+        <v>439</v>
       </c>
       <c r="D426" t="s">
         <v>55</v>
@@ -7537,10 +7554,10 @@
         <v>261</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C427" s="6">
-        <v>670</v>
+        <v>199</v>
       </c>
       <c r="D427" t="s">
         <v>55</v>
@@ -7551,10 +7568,10 @@
         <v>261</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C428" s="6">
-        <v>49.99</v>
+        <v>249</v>
       </c>
       <c r="D428" t="s">
         <v>55</v>
@@ -7565,10 +7582,10 @@
         <v>261</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C429" s="6">
-        <v>49.99</v>
+        <v>670</v>
       </c>
       <c r="D429" t="s">
         <v>55</v>
@@ -7579,13 +7596,13 @@
         <v>261</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C430" s="6">
-        <v>15.99</v>
+        <v>49.99</v>
       </c>
       <c r="D430" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
@@ -7593,13 +7610,13 @@
         <v>261</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C431" s="6">
-        <v>29.99</v>
+        <v>49.99</v>
       </c>
       <c r="D431" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
@@ -7607,10 +7624,10 @@
         <v>261</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C432" s="6">
-        <v>16.989999999999998</v>
+        <v>15.99</v>
       </c>
       <c r="D432" t="s">
         <v>79</v>
@@ -7621,7 +7638,7 @@
         <v>261</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C433" s="6">
         <v>29.99</v>
@@ -7635,10 +7652,10 @@
         <v>261</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C434" s="6">
-        <v>11.49</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D434" t="s">
         <v>79</v>
@@ -7649,10 +7666,10 @@
         <v>261</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C435" s="6">
-        <v>18.95</v>
+        <v>29.99</v>
       </c>
       <c r="D435" t="s">
         <v>79</v>
@@ -7663,10 +7680,10 @@
         <v>261</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C436" s="6">
-        <v>39.99</v>
+        <v>11.49</v>
       </c>
       <c r="D436" t="s">
         <v>79</v>
@@ -7676,11 +7693,11 @@
       <c r="A437" t="s">
         <v>261</v>
       </c>
-      <c r="B437" s="3">
-        <v>6102</v>
+      <c r="B437" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="C437" s="6">
-        <v>44.5</v>
+        <v>18.95</v>
       </c>
       <c r="D437" t="s">
         <v>79</v>
@@ -7691,10 +7708,10 @@
         <v>261</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C438" s="6">
-        <v>112</v>
+        <v>39.99</v>
       </c>
       <c r="D438" t="s">
         <v>79</v>
@@ -7704,11 +7721,11 @@
       <c r="A439" t="s">
         <v>261</v>
       </c>
-      <c r="B439" s="3" t="s">
-        <v>282</v>
+      <c r="B439" s="3">
+        <v>6102</v>
       </c>
       <c r="C439" s="6">
-        <v>139</v>
+        <v>44.5</v>
       </c>
       <c r="D439" t="s">
         <v>79</v>
@@ -7719,10 +7736,10 @@
         <v>261</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C440" s="6">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="D440" t="s">
         <v>79</v>
@@ -7733,7 +7750,10 @@
         <v>261</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
+      </c>
+      <c r="C441" s="6">
+        <v>139</v>
       </c>
       <c r="D441" t="s">
         <v>79</v>
@@ -7744,7 +7764,10 @@
         <v>261</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
+      </c>
+      <c r="C442" s="6">
+        <v>139</v>
       </c>
       <c r="D442" t="s">
         <v>79</v>
@@ -7755,10 +7778,7 @@
         <v>261</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C443" s="6">
-        <v>209</v>
+        <v>284</v>
       </c>
       <c r="D443" t="s">
         <v>79</v>
@@ -7769,7 +7789,7 @@
         <v>261</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D444" t="s">
         <v>79</v>
@@ -7780,7 +7800,10 @@
         <v>261</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
+      </c>
+      <c r="C445" s="6">
+        <v>209</v>
       </c>
       <c r="D445" t="s">
         <v>79</v>
@@ -7791,10 +7814,7 @@
         <v>261</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C446" s="6">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="D446" t="s">
         <v>79</v>
@@ -7805,10 +7825,7 @@
         <v>261</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C447" s="6">
-        <v>299.99</v>
+        <v>288</v>
       </c>
       <c r="D447" t="s">
         <v>79</v>
@@ -7819,10 +7836,10 @@
         <v>261</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>92</v>
+        <v>289</v>
       </c>
       <c r="C448" s="6">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="D448" t="s">
         <v>79</v>
@@ -7833,10 +7850,10 @@
         <v>261</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="C449" s="6">
-        <v>245</v>
+        <v>299.99</v>
       </c>
       <c r="D449" t="s">
         <v>79</v>
@@ -7847,10 +7864,10 @@
         <v>261</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C450" s="6">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="D450" t="s">
         <v>79</v>
@@ -7861,10 +7878,10 @@
         <v>261</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C451" s="6">
-        <v>399</v>
+        <v>245</v>
       </c>
       <c r="D451" t="s">
         <v>79</v>
@@ -7875,10 +7892,10 @@
         <v>261</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C452" s="6">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="D452" t="s">
         <v>79</v>
@@ -7889,10 +7906,10 @@
         <v>261</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C453" s="6">
-        <v>345</v>
+        <v>399</v>
       </c>
       <c r="D453" t="s">
         <v>79</v>
@@ -7903,7 +7920,7 @@
         <v>261</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C454" s="6">
         <v>209</v>
@@ -7917,10 +7934,10 @@
         <v>261</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C455" s="6">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="D455" t="s">
         <v>79</v>
@@ -7931,10 +7948,10 @@
         <v>261</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C456" s="6">
-        <v>315</v>
+        <v>209</v>
       </c>
       <c r="D456" t="s">
         <v>79</v>
@@ -7945,10 +7962,10 @@
         <v>261</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>291</v>
+        <v>89</v>
       </c>
       <c r="C457" s="6">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="D457" t="s">
         <v>79</v>
@@ -7959,10 +7976,10 @@
         <v>261</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C458" s="6">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="D458" t="s">
         <v>79</v>
@@ -7973,10 +7990,10 @@
         <v>261</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>98</v>
+        <v>291</v>
       </c>
       <c r="C459" s="6">
-        <v>420</v>
+        <v>265</v>
       </c>
       <c r="D459" t="s">
         <v>79</v>
@@ -7987,10 +8004,10 @@
         <v>261</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C460" s="6">
-        <v>315</v>
+        <v>251</v>
       </c>
       <c r="D460" t="s">
         <v>79</v>
@@ -8001,10 +8018,10 @@
         <v>261</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C461" s="6">
-        <v>365</v>
+        <v>420</v>
       </c>
       <c r="D461" t="s">
         <v>79</v>
@@ -8015,10 +8032,10 @@
         <v>261</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C462" s="6">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="D462" t="s">
         <v>79</v>
@@ -8029,13 +8046,13 @@
         <v>261</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C463" s="6">
-        <v>55.99</v>
+        <v>365</v>
       </c>
       <c r="D463" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -8043,13 +8060,13 @@
         <v>261</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C464" s="6">
-        <v>39.99</v>
+        <v>285</v>
       </c>
       <c r="D464" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -8057,10 +8074,10 @@
         <v>261</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C465" s="6">
-        <v>68</v>
+        <v>55.99</v>
       </c>
       <c r="D465" t="s">
         <v>109</v>
@@ -8071,10 +8088,10 @@
         <v>261</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C466" s="6">
-        <v>129</v>
+        <v>39.99</v>
       </c>
       <c r="D466" t="s">
         <v>109</v>
@@ -8085,10 +8102,10 @@
         <v>261</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C467" s="6">
-        <v>30.99</v>
+        <v>68</v>
       </c>
       <c r="D467" t="s">
         <v>109</v>
@@ -8099,10 +8116,10 @@
         <v>261</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C468" s="6">
-        <v>42.99</v>
+        <v>129</v>
       </c>
       <c r="D468" t="s">
         <v>109</v>
@@ -8113,10 +8130,10 @@
         <v>261</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C469" s="6">
-        <v>159</v>
+        <v>30.99</v>
       </c>
       <c r="D469" t="s">
         <v>109</v>
@@ -8127,10 +8144,10 @@
         <v>261</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>292</v>
+        <v>115</v>
       </c>
       <c r="C470" s="6">
-        <v>49.99</v>
+        <v>42.99</v>
       </c>
       <c r="D470" t="s">
         <v>109</v>
@@ -8141,10 +8158,10 @@
         <v>261</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="C471" s="6">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D471" t="s">
         <v>109</v>
@@ -8155,13 +8172,13 @@
         <v>261</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="C472" s="6">
-        <v>47.99</v>
+        <v>49.99</v>
       </c>
       <c r="D472" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
@@ -8169,13 +8186,13 @@
         <v>261</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C473" s="6">
-        <v>34.99</v>
+        <v>129</v>
       </c>
       <c r="D473" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -8183,13 +8200,13 @@
         <v>261</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="C474" s="6">
-        <v>89.99</v>
+        <v>47.99</v>
       </c>
       <c r="D474" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -8197,13 +8214,13 @@
         <v>261</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="C475" s="6">
-        <v>45</v>
+        <v>34.99</v>
       </c>
       <c r="D475" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
@@ -8211,13 +8228,13 @@
         <v>261</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>295</v>
+        <v>153</v>
       </c>
       <c r="C476" s="6">
-        <v>88</v>
+        <v>89.99</v>
       </c>
       <c r="D476" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
@@ -8225,10 +8242,10 @@
         <v>261</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="C477" s="6">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="D477" t="s">
         <v>175</v>
@@ -8239,13 +8256,13 @@
         <v>261</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="C478" s="6">
-        <v>79.989999999999995</v>
+        <v>88</v>
       </c>
       <c r="D478" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
@@ -8253,13 +8270,13 @@
         <v>261</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C479" s="6">
-        <v>7.95</v>
+        <v>125</v>
       </c>
       <c r="D479" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
@@ -8267,13 +8284,13 @@
         <v>261</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="C480" s="6">
-        <v>18.95</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D480" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
@@ -8281,10 +8298,10 @@
         <v>261</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>239</v>
+        <v>297</v>
       </c>
       <c r="C481" s="6">
-        <v>36.950000000000003</v>
+        <v>7.95</v>
       </c>
       <c r="D481" t="s">
         <v>238</v>
@@ -8295,13 +8312,13 @@
         <v>261</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C482" s="6">
-        <v>39.99</v>
+        <v>18.95</v>
       </c>
       <c r="D482" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
@@ -8309,13 +8326,13 @@
         <v>261</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>27</v>
+        <v>239</v>
       </c>
       <c r="C483" s="6">
-        <v>19.5</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D483" t="s">
-        <v>28</v>
+        <v>238</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
@@ -8323,13 +8340,13 @@
         <v>261</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>298</v>
+        <v>220</v>
       </c>
       <c r="C484" s="6">
-        <v>110</v>
+        <v>39.99</v>
       </c>
       <c r="D484" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
@@ -8337,10 +8354,10 @@
         <v>261</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>299</v>
+        <v>27</v>
       </c>
       <c r="C485" s="6">
-        <v>98.45</v>
+        <v>19.5</v>
       </c>
       <c r="D485" t="s">
         <v>28</v>
@@ -8351,10 +8368,10 @@
         <v>261</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C486" s="6">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D486" t="s">
         <v>28</v>
@@ -8365,10 +8382,10 @@
         <v>261</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C487" s="6">
-        <v>199</v>
+        <v>98.45</v>
       </c>
       <c r="D487" t="s">
         <v>28</v>
@@ -8379,10 +8396,10 @@
         <v>261</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C488" s="6">
-        <v>169.99</v>
+        <v>139</v>
       </c>
       <c r="D488" t="s">
         <v>28</v>
@@ -8393,10 +8410,10 @@
         <v>261</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C489" s="6">
-        <v>239.08</v>
+        <v>199</v>
       </c>
       <c r="D489" t="s">
         <v>28</v>
@@ -8407,10 +8424,10 @@
         <v>261</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C490" s="6">
-        <v>219</v>
+        <v>169.99</v>
       </c>
       <c r="D490" t="s">
         <v>28</v>
@@ -8421,10 +8438,10 @@
         <v>261</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C491" s="6">
-        <v>189.99</v>
+        <v>239.08</v>
       </c>
       <c r="D491" t="s">
         <v>28</v>
@@ -8435,10 +8452,10 @@
         <v>261</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C492" s="6">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="D492" t="s">
         <v>28</v>
@@ -8449,10 +8466,10 @@
         <v>261</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C493" s="6">
-        <v>297</v>
+        <v>189.99</v>
       </c>
       <c r="D493" t="s">
         <v>28</v>
@@ -8463,47 +8480,41 @@
         <v>261</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C494" s="6">
-        <v>322</v>
+        <v>248</v>
       </c>
       <c r="D494" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
-        <v>309</v>
-      </c>
-      <c r="B504" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C504" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D504" t="s">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>261</v>
+      </c>
+      <c r="B495" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C495" s="6">
+        <v>297</v>
+      </c>
+      <c r="D495" t="s">
         <v>28</v>
       </c>
-      <c r="F504" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>309</v>
-      </c>
-      <c r="B505" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C505" s="6">
-        <v>79.47</v>
-      </c>
-      <c r="D505" t="s">
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>261</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C496" s="6">
+        <v>322</v>
+      </c>
+      <c r="D496" t="s">
         <v>28</v>
-      </c>
-      <c r="F505" s="7" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -8511,10 +8522,10 @@
         <v>309</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C506" s="6">
-        <v>92.85</v>
+        <v>42.75</v>
       </c>
       <c r="D506" t="s">
         <v>28</v>
@@ -8527,14 +8538,14 @@
       <c r="A507" t="s">
         <v>309</v>
       </c>
-      <c r="B507" s="3">
-        <v>4430</v>
+      <c r="B507" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="C507" s="6">
-        <v>15.25</v>
+        <v>79.47</v>
       </c>
       <c r="D507" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F507" s="7" t="s">
         <v>311</v>
@@ -8544,14 +8555,14 @@
       <c r="A508" t="s">
         <v>309</v>
       </c>
-      <c r="B508" s="3">
-        <v>4442</v>
+      <c r="B508" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="C508" s="6">
-        <v>18.899999999999999</v>
+        <v>92.85</v>
       </c>
       <c r="D508" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F508" s="7" t="s">
         <v>311</v>
@@ -8562,10 +8573,10 @@
         <v>309</v>
       </c>
       <c r="B509" s="3">
-        <v>6642</v>
+        <v>4430</v>
       </c>
       <c r="C509" s="6">
-        <v>26.8</v>
+        <v>15.25</v>
       </c>
       <c r="D509" t="s">
         <v>156</v>
@@ -8579,10 +8590,10 @@
         <v>309</v>
       </c>
       <c r="B510" s="3">
-        <v>6660</v>
+        <v>4442</v>
       </c>
       <c r="C510" s="6">
-        <v>27.05</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D510" t="s">
         <v>156</v>
@@ -8591,206 +8602,206 @@
         <v>311</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A513" t="s">
-        <v>314</v>
-      </c>
-      <c r="B513" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C513" s="6">
-        <v>47.95</v>
-      </c>
-      <c r="D513" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A514" t="s">
-        <v>314</v>
-      </c>
-      <c r="B514" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C514" s="6">
-        <v>59.07</v>
-      </c>
-      <c r="D514" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>309</v>
+      </c>
+      <c r="B511" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C511" s="6">
+        <v>26.8</v>
+      </c>
+      <c r="D511" t="s">
+        <v>156</v>
+      </c>
+      <c r="F511" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>309</v>
+      </c>
+      <c r="B512" s="3">
+        <v>6660</v>
+      </c>
+      <c r="C512" s="6">
+        <v>27.05</v>
+      </c>
+      <c r="D512" t="s">
+        <v>156</v>
+      </c>
+      <c r="F512" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>314</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C515" s="6">
-        <v>83.8</v>
+        <v>47.95</v>
       </c>
       <c r="D515" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>314</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C516" s="6">
-        <v>115.4</v>
+        <v>59.07</v>
       </c>
       <c r="D516" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>314</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C517" s="6">
-        <v>107.15</v>
+        <v>83.8</v>
       </c>
       <c r="D517" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>314</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C518" s="6">
-        <v>13</v>
+        <v>115.4</v>
       </c>
       <c r="D518" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>314</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C519" s="6">
-        <v>17</v>
+        <v>107.15</v>
       </c>
       <c r="D519" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>314</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="C520" s="6">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D520" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>314</v>
       </c>
-      <c r="B521" s="3">
-        <v>4430</v>
+      <c r="B521" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C521" s="6">
-        <v>15.25</v>
+        <v>17</v>
       </c>
       <c r="D521" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>314</v>
       </c>
-      <c r="B522" s="3">
-        <v>4442</v>
+      <c r="B522" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C522" s="6">
-        <v>18.899999999999999</v>
+        <v>30</v>
       </c>
       <c r="D522" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>314</v>
       </c>
       <c r="B523" s="3">
-        <v>6642</v>
+        <v>4430</v>
       </c>
       <c r="C523" s="6">
-        <v>26.8</v>
+        <v>15.25</v>
       </c>
       <c r="D523" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>314</v>
       </c>
-      <c r="B524" s="3" t="s">
+      <c r="B524" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C524" s="6">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D524" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>314</v>
+      </c>
+      <c r="B525" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C525" s="6">
+        <v>26.8</v>
+      </c>
+      <c r="D525" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>314</v>
+      </c>
+      <c r="B526" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C524" s="6">
+      <c r="C526" s="6">
         <v>39.950000000000003</v>
       </c>
-      <c r="D524" t="s">
+      <c r="D526" t="s">
         <v>194</v>
-      </c>
-    </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A527" t="s">
-        <v>315</v>
-      </c>
-      <c r="B527" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C527" s="6">
-        <v>9.92</v>
-      </c>
-      <c r="D527" t="s">
-        <v>317</v>
-      </c>
-      <c r="F527" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A528" t="s">
-        <v>315</v>
-      </c>
-      <c r="B528" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C528" s="6">
-        <v>47.95</v>
-      </c>
-      <c r="D528" t="s">
-        <v>28</v>
-      </c>
-      <c r="F528" s="7" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
@@ -8798,13 +8809,13 @@
         <v>315</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c r="C529" s="6">
-        <v>55.73</v>
+        <v>9.92</v>
       </c>
       <c r="D529" t="s">
-        <v>28</v>
+        <v>317</v>
       </c>
       <c r="F529" s="7" t="s">
         <v>318</v>
@@ -8815,10 +8826,10 @@
         <v>315</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C530" s="6">
-        <v>79.06</v>
+        <v>47.95</v>
       </c>
       <c r="D530" t="s">
         <v>28</v>
@@ -8832,10 +8843,10 @@
         <v>315</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C531" s="6">
-        <v>108.86</v>
+        <v>55.73</v>
       </c>
       <c r="D531" t="s">
         <v>28</v>
@@ -8849,10 +8860,10 @@
         <v>315</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C532" s="6">
-        <v>101.09</v>
+        <v>79.06</v>
       </c>
       <c r="D532" t="s">
         <v>28</v>
@@ -8866,10 +8877,10 @@
         <v>315</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C533" s="6">
-        <v>160.69999999999999</v>
+        <v>108.86</v>
       </c>
       <c r="D533" t="s">
         <v>28</v>
@@ -8883,10 +8894,10 @@
         <v>315</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C534" s="6">
-        <v>121.82</v>
+        <v>101.09</v>
       </c>
       <c r="D534" t="s">
         <v>28</v>
@@ -8900,10 +8911,10 @@
         <v>315</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C535" s="6">
-        <v>122.49</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="D535" t="s">
         <v>28</v>
@@ -8917,7 +8928,10 @@
         <v>315</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="C536" s="6">
+        <v>121.82</v>
       </c>
       <c r="D536" t="s">
         <v>28</v>
@@ -8931,7 +8945,10 @@
         <v>315</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
+      </c>
+      <c r="C537" s="6">
+        <v>122.49</v>
       </c>
       <c r="D537" t="s">
         <v>28</v>
@@ -8945,7 +8962,7 @@
         <v>315</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D538" t="s">
         <v>28</v>
@@ -8959,10 +8976,7 @@
         <v>315</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C539" s="6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D539" t="s">
         <v>28</v>
@@ -8976,10 +8990,7 @@
         <v>315</v>
       </c>
       <c r="B540" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C540" s="6">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D540" t="s">
         <v>28</v>
@@ -8993,10 +9004,10 @@
         <v>315</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C541" s="6">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D541" t="s">
         <v>28</v>
@@ -9010,13 +9021,13 @@
         <v>315</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>158</v>
+        <v>312</v>
       </c>
       <c r="C542" s="6">
-        <v>69.900000000000006</v>
+        <v>67</v>
       </c>
       <c r="D542" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F542" s="7" t="s">
         <v>318</v>
@@ -9026,14 +9037,14 @@
       <c r="A543" t="s">
         <v>315</v>
       </c>
-      <c r="B543" s="3">
-        <v>4430</v>
+      <c r="B543" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="C543" s="6">
-        <v>15.25</v>
+        <v>79</v>
       </c>
       <c r="D543" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="F543" s="7" t="s">
         <v>318</v>
@@ -9043,11 +9054,11 @@
       <c r="A544" t="s">
         <v>315</v>
       </c>
-      <c r="B544" s="3">
-        <v>4442</v>
+      <c r="B544" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="C544" s="6">
-        <v>15</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="D544" t="s">
         <v>156</v>
@@ -9060,11 +9071,11 @@
       <c r="A545" t="s">
         <v>315</v>
       </c>
-      <c r="B545" s="3" t="s">
-        <v>161</v>
+      <c r="B545" s="3">
+        <v>4430</v>
       </c>
       <c r="C545" s="6">
-        <v>171</v>
+        <v>15.25</v>
       </c>
       <c r="D545" t="s">
         <v>156</v>
@@ -9077,8 +9088,11 @@
       <c r="A546" t="s">
         <v>315</v>
       </c>
-      <c r="B546" s="3" t="s">
-        <v>162</v>
+      <c r="B546" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C546" s="6">
+        <v>15</v>
       </c>
       <c r="D546" t="s">
         <v>156</v>
@@ -9091,11 +9105,11 @@
       <c r="A547" t="s">
         <v>315</v>
       </c>
-      <c r="B547" s="3">
-        <v>4642</v>
+      <c r="B547" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="C547" s="6">
-        <v>16.5</v>
+        <v>171</v>
       </c>
       <c r="D547" t="s">
         <v>156</v>
@@ -9109,10 +9123,7 @@
         <v>315</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C548" s="6">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="D548" t="s">
         <v>156</v>
@@ -9126,10 +9137,10 @@
         <v>315</v>
       </c>
       <c r="B549" s="3">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C549" s="6">
-        <v>20.25</v>
+        <v>16.5</v>
       </c>
       <c r="D549" t="s">
         <v>156</v>
@@ -9142,11 +9153,11 @@
       <c r="A550" t="s">
         <v>315</v>
       </c>
-      <c r="B550" s="3">
-        <v>6630</v>
+      <c r="B550" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C550" s="6">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="D550" t="s">
         <v>156</v>
@@ -9160,10 +9171,10 @@
         <v>315</v>
       </c>
       <c r="B551" s="3">
-        <v>6642</v>
+        <v>4660</v>
       </c>
       <c r="C551" s="6">
-        <v>18.5</v>
+        <v>20.25</v>
       </c>
       <c r="D551" t="s">
         <v>156</v>
@@ -9176,11 +9187,11 @@
       <c r="A552" t="s">
         <v>315</v>
       </c>
-      <c r="B552" s="3" t="s">
-        <v>164</v>
+      <c r="B552" s="3">
+        <v>6630</v>
       </c>
       <c r="C552" s="6">
-        <v>103.5</v>
+        <v>20</v>
       </c>
       <c r="D552" t="s">
         <v>156</v>
@@ -9194,10 +9205,10 @@
         <v>315</v>
       </c>
       <c r="B553" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C553" s="6">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="D553" t="s">
         <v>156</v>
@@ -9211,10 +9222,10 @@
         <v>315</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C554" s="6">
-        <v>126</v>
+        <v>103.5</v>
       </c>
       <c r="D554" t="s">
         <v>156</v>
@@ -9228,10 +9239,10 @@
         <v>315</v>
       </c>
       <c r="B555" s="3">
-        <v>8860</v>
+        <v>6660</v>
       </c>
       <c r="C555" s="6">
-        <v>28</v>
+        <v>22.5</v>
       </c>
       <c r="D555" t="s">
         <v>156</v>
@@ -9240,60 +9251,66 @@
         <v>318</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A558" t="s">
-        <v>319</v>
-      </c>
-      <c r="B558" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C558">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="D558" t="s">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>315</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C556" s="6">
+        <v>126</v>
+      </c>
+      <c r="D556" t="s">
         <v>156</v>
       </c>
-      <c r="E558" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A559" t="s">
-        <v>319</v>
-      </c>
-      <c r="B559" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C559" s="6">
-        <v>15.25</v>
-      </c>
-      <c r="D559" t="s">
+      <c r="F556" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>315</v>
+      </c>
+      <c r="B557" s="3">
+        <v>8860</v>
+      </c>
+      <c r="C557" s="6">
+        <v>28</v>
+      </c>
+      <c r="D557" t="s">
         <v>156</v>
+      </c>
+      <c r="F557" s="7" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>319</v>
       </c>
-      <c r="B560" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C560" s="6">
-        <v>15</v>
+      <c r="B560" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C560">
+        <v>69.900000000000006</v>
       </c>
       <c r="D560" t="s">
         <v>156</v>
+      </c>
+      <c r="E560" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>319</v>
       </c>
-      <c r="B561" s="3" t="s">
-        <v>161</v>
+      <c r="B561" s="3">
+        <v>4430</v>
       </c>
       <c r="C561" s="6">
-        <v>171</v>
+        <v>15.25</v>
       </c>
       <c r="D561" t="s">
         <v>156</v>
@@ -9303,11 +9320,11 @@
       <c r="A562" t="s">
         <v>319</v>
       </c>
-      <c r="B562" s="3" t="s">
-        <v>162</v>
+      <c r="B562" s="3">
+        <v>4442</v>
       </c>
       <c r="C562" s="6">
-        <v>972</v>
+        <v>15</v>
       </c>
       <c r="D562" t="s">
         <v>156</v>
@@ -9317,11 +9334,11 @@
       <c r="A563" t="s">
         <v>319</v>
       </c>
-      <c r="B563" s="3">
-        <v>4642</v>
+      <c r="B563" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="C563" s="6">
-        <v>16.5</v>
+        <v>171</v>
       </c>
       <c r="D563" t="s">
         <v>156</v>
@@ -9332,10 +9349,10 @@
         <v>319</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C564" s="6">
-        <v>126</v>
+        <v>972</v>
       </c>
       <c r="D564" t="s">
         <v>156</v>
@@ -9346,10 +9363,10 @@
         <v>319</v>
       </c>
       <c r="B565" s="3">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C565" s="6">
-        <v>20.25</v>
+        <v>16.5</v>
       </c>
       <c r="D565" t="s">
         <v>156</v>
@@ -9360,16 +9377,13 @@
         <v>319</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>357</v>
+        <v>163</v>
       </c>
       <c r="C566" s="6">
-        <v>20.25</v>
+        <v>126</v>
       </c>
       <c r="D566" t="s">
         <v>156</v>
-      </c>
-      <c r="E566" s="3">
-        <v>4660</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
@@ -9377,10 +9391,10 @@
         <v>319</v>
       </c>
       <c r="B567" s="3">
-        <v>6630</v>
+        <v>4660</v>
       </c>
       <c r="C567" s="6">
-        <v>19</v>
+        <v>20.25</v>
       </c>
       <c r="D567" t="s">
         <v>156</v>
@@ -9390,25 +9404,28 @@
       <c r="A568" t="s">
         <v>319</v>
       </c>
-      <c r="B568" s="3">
-        <v>6642</v>
+      <c r="B568" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="C568" s="6">
-        <v>18.5</v>
+        <v>20.25</v>
       </c>
       <c r="D568" t="s">
         <v>156</v>
+      </c>
+      <c r="E568" s="3">
+        <v>4660</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>319</v>
       </c>
-      <c r="B569" s="3" t="s">
-        <v>164</v>
+      <c r="B569" s="3">
+        <v>6630</v>
       </c>
       <c r="C569" s="6">
-        <v>103.5</v>
+        <v>19</v>
       </c>
       <c r="D569" t="s">
         <v>156</v>
@@ -9419,10 +9436,10 @@
         <v>319</v>
       </c>
       <c r="B570" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C570" s="6">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="D570" t="s">
         <v>156</v>
@@ -9433,10 +9450,10 @@
         <v>319</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C571" s="6">
-        <v>126</v>
+        <v>103.5</v>
       </c>
       <c r="D571" t="s">
         <v>156</v>
@@ -9447,10 +9464,10 @@
         <v>319</v>
       </c>
       <c r="B572" s="3">
-        <v>8860</v>
+        <v>6660</v>
       </c>
       <c r="C572" s="6">
-        <v>42.25</v>
+        <v>22.5</v>
       </c>
       <c r="D572" t="s">
         <v>156</v>
@@ -9461,27 +9478,27 @@
         <v>319</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>321</v>
+        <v>165</v>
       </c>
       <c r="C573" s="6">
-        <v>5.75</v>
+        <v>126</v>
       </c>
       <c r="D573" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>319</v>
       </c>
-      <c r="B574" s="3" t="s">
-        <v>168</v>
+      <c r="B574" s="3">
+        <v>8860</v>
       </c>
       <c r="C574" s="6">
-        <v>20</v>
+        <v>42.25</v>
       </c>
       <c r="D574" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -9489,10 +9506,10 @@
         <v>319</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="C575" s="6">
-        <v>12.5</v>
+        <v>5.75</v>
       </c>
       <c r="D575" t="s">
         <v>167</v>
@@ -9503,10 +9520,10 @@
         <v>319</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C576" s="6">
-        <v>77.5</v>
+        <v>20</v>
       </c>
       <c r="D576" t="s">
         <v>167</v>
@@ -9517,41 +9534,41 @@
         <v>319</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C577" s="6">
-        <v>195</v>
+        <v>12.5</v>
       </c>
       <c r="D577" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A581" t="s">
-        <v>322</v>
-      </c>
-      <c r="B581" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C581" s="6">
-        <v>50.35</v>
-      </c>
-      <c r="D581" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A582" t="s">
-        <v>322</v>
-      </c>
-      <c r="B582" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C582" s="6">
-        <v>106.14</v>
-      </c>
-      <c r="D582" t="s">
-        <v>28</v>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>319</v>
+      </c>
+      <c r="B578" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C578" s="6">
+        <v>77.5</v>
+      </c>
+      <c r="D578" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>319</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C579" s="6">
+        <v>195</v>
+      </c>
+      <c r="D579" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
@@ -9559,13 +9576,13 @@
         <v>322</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="C583" s="6">
-        <v>41.99</v>
+        <v>50.35</v>
       </c>
       <c r="D583" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -9573,13 +9590,13 @@
         <v>322</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="C584" s="6">
-        <v>82</v>
+        <v>106.14</v>
       </c>
       <c r="D584" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
@@ -9587,13 +9604,13 @@
         <v>322</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="C585" s="6">
-        <v>28</v>
+        <v>41.99</v>
       </c>
       <c r="D585" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
@@ -9601,13 +9618,13 @@
         <v>322</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>204</v>
+        <v>113</v>
       </c>
       <c r="C586" s="6">
-        <v>28.05</v>
+        <v>82</v>
       </c>
       <c r="D586" t="s">
-        <v>199</v>
+        <v>109</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
@@ -9615,13 +9632,13 @@
         <v>322</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="C587" s="6">
-        <v>28.05</v>
+        <v>28</v>
       </c>
       <c r="D587" t="s">
-        <v>199</v>
+        <v>109</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
@@ -9629,7 +9646,7 @@
         <v>322</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C588" s="6">
         <v>28.05</v>
@@ -9643,41 +9660,41 @@
         <v>322</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C589" s="6">
-        <v>11.2</v>
+        <v>28.05</v>
       </c>
       <c r="D589" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A592" t="s">
-        <v>79</v>
-      </c>
-      <c r="B592" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C592" s="6">
-        <v>29.87</v>
-      </c>
-      <c r="D592" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A593" t="s">
-        <v>79</v>
-      </c>
-      <c r="B593" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C593" s="6">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>322</v>
+      </c>
+      <c r="B590" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C590" s="6">
+        <v>28.05</v>
+      </c>
+      <c r="D590" t="s">
         <v>199</v>
       </c>
-      <c r="D593" t="s">
-        <v>28</v>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>322</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C591" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="D591" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
@@ -9685,13 +9702,13 @@
         <v>79</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C594" s="6">
-        <v>175</v>
+        <v>29.87</v>
       </c>
       <c r="D594" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
@@ -9699,13 +9716,13 @@
         <v>79</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C595" s="6">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D595" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
@@ -9713,10 +9730,10 @@
         <v>79</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C596" s="6">
-        <v>224.1</v>
+        <v>175</v>
       </c>
       <c r="D596" t="s">
         <v>55</v>
@@ -9727,10 +9744,10 @@
         <v>79</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C597" s="6">
-        <v>309</v>
+        <v>189</v>
       </c>
       <c r="D597" t="s">
         <v>55</v>
@@ -9741,10 +9758,10 @@
         <v>79</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C598" s="6">
-        <v>85.5</v>
+        <v>224.1</v>
       </c>
       <c r="D598" t="s">
         <v>55</v>
@@ -9754,14 +9771,14 @@
       <c r="A599" t="s">
         <v>79</v>
       </c>
-      <c r="B599" s="3">
-        <v>6102</v>
+      <c r="B599" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C599" s="6">
-        <v>38.99</v>
+        <v>309</v>
       </c>
       <c r="D599" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
@@ -9769,24 +9786,24 @@
         <v>79</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C600" s="6">
-        <v>175</v>
+        <v>85.5</v>
       </c>
       <c r="D600" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>79</v>
       </c>
-      <c r="B601" s="3" t="s">
-        <v>287</v>
+      <c r="B601" s="3">
+        <v>6102</v>
       </c>
       <c r="C601" s="6">
-        <v>134</v>
+        <v>38.99</v>
       </c>
       <c r="D601" t="s">
         <v>79</v>
@@ -9797,13 +9814,13 @@
         <v>79</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C602" s="6">
-        <v>59.99</v>
+        <v>175</v>
       </c>
       <c r="D602" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
@@ -9811,13 +9828,13 @@
         <v>79</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C603" s="6">
-        <v>32.99</v>
+        <v>134</v>
       </c>
       <c r="D603" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
@@ -9825,10 +9842,10 @@
         <v>79</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C604" s="6">
-        <v>129</v>
+        <v>59.99</v>
       </c>
       <c r="D604" t="s">
         <v>109</v>
@@ -9839,10 +9856,10 @@
         <v>79</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C605" s="6">
-        <v>149.99</v>
+        <v>32.99</v>
       </c>
       <c r="D605" t="s">
         <v>109</v>
@@ -9853,13 +9870,13 @@
         <v>79</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C606" s="6">
-        <v>47.99</v>
+        <v>129</v>
       </c>
       <c r="D606" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
@@ -9867,13 +9884,13 @@
         <v>79</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C607" s="6">
-        <v>39.99</v>
+        <v>149.99</v>
       </c>
       <c r="D607" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
@@ -9881,13 +9898,13 @@
         <v>79</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="C608" s="6">
-        <v>39.99</v>
+        <v>47.99</v>
       </c>
       <c r="D608" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
@@ -9895,10 +9912,13 @@
         <v>79</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>197</v>
+        <v>123</v>
+      </c>
+      <c r="C609" s="6">
+        <v>39.99</v>
       </c>
       <c r="D609" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
@@ -9906,41 +9926,38 @@
         <v>79</v>
       </c>
       <c r="B610" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C610" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D610" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>79</v>
+      </c>
+      <c r="B611" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D611" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>79</v>
+      </c>
+      <c r="B612" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C610" s="6">
+      <c r="C612" s="6">
         <v>36.950000000000003</v>
       </c>
-      <c r="D610" t="s">
+      <c r="D612" t="s">
         <v>238</v>
-      </c>
-    </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A613" t="s">
-        <v>323</v>
-      </c>
-      <c r="B613" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C613" s="6">
-        <v>18</v>
-      </c>
-      <c r="D613" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A614" t="s">
-        <v>323</v>
-      </c>
-      <c r="B614" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C614" s="6">
-        <v>100</v>
-      </c>
-      <c r="D614" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
@@ -9948,10 +9965,10 @@
         <v>323</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C615" s="6">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="D615" t="s">
         <v>28</v>
@@ -9962,10 +9979,10 @@
         <v>323</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C616" s="6">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D616" t="s">
         <v>28</v>
@@ -9976,10 +9993,10 @@
         <v>323</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C617" s="6">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="D617" t="s">
         <v>28</v>
@@ -9990,10 +10007,10 @@
         <v>323</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C618" s="6">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D618" t="s">
         <v>28</v>
@@ -10004,10 +10021,10 @@
         <v>323</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C619" s="6">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="D619" t="s">
         <v>28</v>
@@ -10018,10 +10035,10 @@
         <v>323</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C620" s="6">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="D620" t="s">
         <v>28</v>
@@ -10032,10 +10049,10 @@
         <v>323</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C621" s="6">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="D621" t="s">
         <v>28</v>
@@ -10046,10 +10063,10 @@
         <v>323</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C622" s="6">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D622" t="s">
         <v>28</v>
@@ -10060,10 +10077,10 @@
         <v>323</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C623" s="6">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="D623" t="s">
         <v>28</v>
@@ -10074,10 +10091,10 @@
         <v>323</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C624" s="6">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="D624" t="s">
         <v>28</v>
@@ -10088,13 +10105,13 @@
         <v>323</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C625" s="6">
-        <v>19.989999999999998</v>
+        <v>285</v>
       </c>
       <c r="D625" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
@@ -10102,13 +10119,13 @@
         <v>323</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C626" s="6">
-        <v>29.99</v>
+        <v>250</v>
       </c>
       <c r="D626" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
@@ -10116,13 +10133,13 @@
         <v>323</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C627" s="6">
-        <v>155</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D627" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
@@ -10130,13 +10147,13 @@
         <v>323</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C628" s="6">
-        <v>190</v>
+        <v>29.99</v>
       </c>
       <c r="D628" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
@@ -10144,10 +10161,10 @@
         <v>323</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C629" s="6">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="D629" t="s">
         <v>55</v>
@@ -10158,10 +10175,10 @@
         <v>323</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C630" s="6">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D630" t="s">
         <v>55</v>
@@ -10172,10 +10189,10 @@
         <v>323</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C631" s="6">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D631" t="s">
         <v>55</v>
@@ -10186,10 +10203,10 @@
         <v>323</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C632" s="6">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="D632" t="s">
         <v>55</v>
@@ -10200,10 +10217,10 @@
         <v>323</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C633" s="6">
-        <v>389</v>
+        <v>199</v>
       </c>
       <c r="D633" t="s">
         <v>55</v>
@@ -10214,10 +10231,10 @@
         <v>323</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C634" s="6">
-        <v>399.99</v>
+        <v>260</v>
       </c>
       <c r="D634" t="s">
         <v>55</v>
@@ -10228,10 +10245,10 @@
         <v>323</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C635" s="6">
-        <v>89.23</v>
+        <v>389</v>
       </c>
       <c r="D635" t="s">
         <v>55</v>
@@ -10241,14 +10258,14 @@
       <c r="A636" t="s">
         <v>323</v>
       </c>
-      <c r="B636" s="3">
-        <v>6102</v>
+      <c r="B636" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C636" s="6">
-        <v>44</v>
+        <v>399.99</v>
       </c>
       <c r="D636" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.25">
@@ -10256,27 +10273,27 @@
         <v>323</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>324</v>
+        <v>66</v>
       </c>
       <c r="C637" s="6">
-        <v>64</v>
+        <v>89.23</v>
       </c>
       <c r="D637" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>323</v>
       </c>
-      <c r="B638" s="3" t="s">
-        <v>325</v>
+      <c r="B638" s="3">
+        <v>6102</v>
       </c>
       <c r="C638" s="6">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D638" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
@@ -10284,10 +10301,10 @@
         <v>323</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C639" s="6">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D639" t="s">
         <v>102</v>
@@ -10298,10 +10315,10 @@
         <v>323</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C640" s="6">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D640" t="s">
         <v>102</v>
@@ -10312,10 +10329,10 @@
         <v>323</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C641" s="6">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D641" t="s">
         <v>102</v>
@@ -10326,10 +10343,10 @@
         <v>323</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C642" s="6">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D642" t="s">
         <v>102</v>
@@ -10340,13 +10357,13 @@
         <v>323</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>110</v>
+        <v>328</v>
       </c>
       <c r="C643" s="6">
-        <v>27.99</v>
+        <v>90</v>
       </c>
       <c r="D643" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
@@ -10354,13 +10371,13 @@
         <v>323</v>
       </c>
       <c r="B644" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C644" s="6">
         <v>114</v>
       </c>
-      <c r="C644" s="6">
-        <v>28.99</v>
-      </c>
       <c r="D644" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
@@ -10368,10 +10385,10 @@
         <v>323</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C645" s="6">
-        <v>39.99</v>
+        <v>27.99</v>
       </c>
       <c r="D645" t="s">
         <v>109</v>
@@ -10382,10 +10399,10 @@
         <v>323</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C646" s="6">
-        <v>58</v>
+        <v>28.99</v>
       </c>
       <c r="D646" t="s">
         <v>109</v>
@@ -10396,10 +10413,10 @@
         <v>323</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C647" s="6">
-        <v>42.99</v>
+        <v>39.99</v>
       </c>
       <c r="D647" t="s">
         <v>109</v>
@@ -10410,10 +10427,10 @@
         <v>323</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C648" s="6">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="D648" t="s">
         <v>109</v>
@@ -10424,10 +10441,10 @@
         <v>323</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C649" s="6">
-        <v>180</v>
+        <v>42.99</v>
       </c>
       <c r="D649" t="s">
         <v>109</v>
@@ -10438,13 +10455,13 @@
         <v>323</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C650" s="6">
-        <v>54.5</v>
+        <v>129</v>
       </c>
       <c r="D650" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
@@ -10452,13 +10469,13 @@
         <v>323</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C651" s="6">
-        <v>48.99</v>
+        <v>180</v>
       </c>
       <c r="D651" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
@@ -10466,10 +10483,10 @@
         <v>323</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C652" s="6">
-        <v>39.99</v>
+        <v>54.5</v>
       </c>
       <c r="D652" t="s">
         <v>118</v>
@@ -10480,10 +10497,10 @@
         <v>323</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C653" s="6">
-        <v>64.989999999999995</v>
+        <v>48.99</v>
       </c>
       <c r="D653" t="s">
         <v>118</v>
@@ -10494,16 +10511,13 @@
         <v>323</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>358</v>
+        <v>122</v>
       </c>
       <c r="C654" s="6">
-        <v>29.99</v>
+        <v>39.99</v>
       </c>
       <c r="D654" t="s">
         <v>118</v>
-      </c>
-      <c r="E654" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -10511,10 +10525,10 @@
         <v>323</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C655" s="6">
-        <v>28.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D655" t="s">
         <v>118</v>
@@ -10525,13 +10539,16 @@
         <v>323</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>254</v>
+        <v>358</v>
       </c>
       <c r="C656" s="6">
-        <v>35</v>
+        <v>29.99</v>
       </c>
       <c r="D656" t="s">
         <v>118</v>
+      </c>
+      <c r="E656" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
@@ -10539,10 +10556,10 @@
         <v>323</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C657" s="6">
-        <v>29.99</v>
+        <v>28.99</v>
       </c>
       <c r="D657" t="s">
         <v>118</v>
@@ -10553,10 +10570,10 @@
         <v>323</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="C658" s="6">
-        <v>25.99</v>
+        <v>35</v>
       </c>
       <c r="D658" t="s">
         <v>118</v>
@@ -10566,14 +10583,14 @@
       <c r="A659" t="s">
         <v>323</v>
       </c>
-      <c r="B659" s="3">
-        <v>6642</v>
+      <c r="B659" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="C659" s="6">
-        <v>50</v>
+        <v>29.99</v>
       </c>
       <c r="D659" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.25">
@@ -10581,27 +10598,27 @@
         <v>323</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>209</v>
+        <v>124</v>
       </c>
       <c r="C660" s="6">
-        <v>19.2</v>
+        <v>25.99</v>
       </c>
       <c r="D660" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>323</v>
       </c>
-      <c r="B661" s="3" t="s">
-        <v>201</v>
+      <c r="B661" s="3">
+        <v>6642</v>
       </c>
       <c r="C661" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D661" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.25">
@@ -10609,10 +10626,10 @@
         <v>323</v>
       </c>
       <c r="B662" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C662" s="6">
-        <v>40</v>
+        <v>19.2</v>
       </c>
       <c r="D662" t="s">
         <v>199</v>
@@ -10623,13 +10640,13 @@
         <v>323</v>
       </c>
       <c r="B663" s="3" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="C663" s="6">
-        <v>30.58</v>
+        <v>40</v>
       </c>
       <c r="D663" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
@@ -10637,13 +10654,13 @@
         <v>323</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="C664" s="6">
-        <v>39.99</v>
+        <v>40</v>
       </c>
       <c r="D664" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.25">
@@ -10651,41 +10668,41 @@
         <v>323</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>330</v>
+        <v>224</v>
       </c>
       <c r="C665" s="6">
-        <v>90</v>
+        <v>30.58</v>
       </c>
       <c r="D665" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A668" t="s">
-        <v>331</v>
-      </c>
-      <c r="B668" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C668" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D668" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A669" t="s">
-        <v>331</v>
-      </c>
-      <c r="B669" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C669" s="6">
-        <v>68</v>
-      </c>
-      <c r="D669" t="s">
-        <v>28</v>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>323</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C666" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D666" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>323</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C667" s="6">
+        <v>90</v>
+      </c>
+      <c r="D667" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
@@ -10693,159 +10710,159 @@
         <v>331</v>
       </c>
       <c r="B670" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C670" s="6">
-        <v>82.2</v>
+        <v>42.75</v>
       </c>
       <c r="D670" t="s">
         <v>28</v>
       </c>
     </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>331</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C671" s="6">
+        <v>68</v>
+      </c>
+      <c r="D671" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>42</v>
+        <v>313</v>
       </c>
       <c r="C672" s="6">
-        <v>2.75</v>
+        <v>82.2</v>
       </c>
       <c r="D672" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A673" t="s">
-        <v>332</v>
-      </c>
-      <c r="B673" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C673" s="6">
-        <v>3.25</v>
-      </c>
-      <c r="D673" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>332</v>
       </c>
-      <c r="B674" s="3">
-        <v>4642</v>
+      <c r="B674" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C674" s="6">
-        <v>18.96</v>
+        <v>2.75</v>
       </c>
       <c r="D674" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>332</v>
       </c>
-      <c r="B675" s="3">
-        <v>6642</v>
+      <c r="B675" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C675" s="6">
-        <v>22.37</v>
+        <v>3.25</v>
       </c>
       <c r="D675" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>332</v>
       </c>
-      <c r="B676" s="3" t="s">
-        <v>208</v>
+      <c r="B676" s="3">
+        <v>4642</v>
       </c>
       <c r="C676" s="6">
-        <v>9.1</v>
+        <v>18.96</v>
       </c>
       <c r="D676" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>332</v>
       </c>
-      <c r="B677" s="3" t="s">
+      <c r="B677" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C677" s="6">
+        <v>22.37</v>
+      </c>
+      <c r="D677" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>332</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C678" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D678" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>332</v>
+      </c>
+      <c r="B679" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C677" s="6">
+      <c r="C679" s="6">
         <v>9.1</v>
       </c>
-      <c r="D677" t="s">
+      <c r="D679" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A682" t="s">
+    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
         <v>333</v>
       </c>
-      <c r="B682" s="3" t="s">
+      <c r="B684" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C682" s="6">
+      <c r="C684" s="6">
         <v>2.75</v>
       </c>
-      <c r="D682" t="s">
+      <c r="D684" t="s">
         <v>43</v>
       </c>
-      <c r="F682" s="7" t="s">
+      <c r="F684" s="7" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A683" t="s">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
         <v>333</v>
       </c>
-      <c r="B683" s="3" t="s">
+      <c r="B685" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C683" s="6">
+      <c r="C685" s="6">
         <v>3.25</v>
       </c>
-      <c r="D683" t="s">
+      <c r="D685" t="s">
         <v>43</v>
       </c>
-      <c r="F683" s="7" t="s">
+      <c r="F685" s="7" t="s">
         <v>349</v>
-      </c>
-    </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A687" t="s">
-        <v>334</v>
-      </c>
-      <c r="B687" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C687" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D687" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A688" t="s">
-        <v>334</v>
-      </c>
-      <c r="B688" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C688" s="6">
-        <v>7.65</v>
-      </c>
-      <c r="D688" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
@@ -10853,10 +10870,10 @@
         <v>334</v>
       </c>
       <c r="B689" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C689" s="6">
-        <v>8.1</v>
+        <v>3.15</v>
       </c>
       <c r="D689" t="s">
         <v>336</v>
@@ -10867,10 +10884,10 @@
         <v>334</v>
       </c>
       <c r="B690" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C690" s="6">
-        <v>10.8</v>
+        <v>7.65</v>
       </c>
       <c r="D690" t="s">
         <v>336</v>
@@ -10881,10 +10898,10 @@
         <v>334</v>
       </c>
       <c r="B691" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C691" s="6">
-        <v>12.2</v>
+        <v>8.1</v>
       </c>
       <c r="D691" t="s">
         <v>336</v>
@@ -10895,10 +10912,10 @@
         <v>334</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C692" s="6">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="D692" t="s">
         <v>336</v>
@@ -10909,10 +10926,10 @@
         <v>334</v>
       </c>
       <c r="B693" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C693" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D693" t="s">
         <v>336</v>
@@ -10923,7 +10940,7 @@
         <v>334</v>
       </c>
       <c r="B694" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C694" s="6">
         <v>11.25</v>
@@ -10932,31 +10949,31 @@
         <v>336</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A697" t="s">
-        <v>344</v>
-      </c>
-      <c r="B697" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C697" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D697" t="s">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>334</v>
+      </c>
+      <c r="B695" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C695" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D695" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A698" t="s">
-        <v>344</v>
-      </c>
-      <c r="B698" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C698" s="6">
-        <v>10.19</v>
-      </c>
-      <c r="D698" t="s">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>334</v>
+      </c>
+      <c r="B696" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C696" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D696" t="s">
         <v>336</v>
       </c>
     </row>
@@ -10965,10 +10982,10 @@
         <v>344</v>
       </c>
       <c r="B699" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C699" s="6">
-        <v>14.4</v>
+        <v>3.36</v>
       </c>
       <c r="D699" t="s">
         <v>336</v>
@@ -10979,10 +10996,10 @@
         <v>344</v>
       </c>
       <c r="B700" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C700" s="6">
-        <v>14.39</v>
+        <v>10.19</v>
       </c>
       <c r="D700" t="s">
         <v>336</v>
@@ -10993,10 +11010,10 @@
         <v>344</v>
       </c>
       <c r="B701" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C701" s="6">
-        <v>11.52</v>
+        <v>14.4</v>
       </c>
       <c r="D701" t="s">
         <v>336</v>
@@ -11007,10 +11024,10 @@
         <v>344</v>
       </c>
       <c r="B702" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C702" s="6">
-        <v>12</v>
+        <v>14.39</v>
       </c>
       <c r="D702" t="s">
         <v>336</v>
@@ -11021,10 +11038,10 @@
         <v>344</v>
       </c>
       <c r="B703" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C703" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D703" t="s">
         <v>336</v>
@@ -11035,7 +11052,7 @@
         <v>344</v>
       </c>
       <c r="B704" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C704" s="6">
         <v>12</v>
@@ -11046,81 +11063,81 @@
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>6</v>
-      </c>
-      <c r="B705" t="s">
-        <v>345</v>
-      </c>
-      <c r="C705">
-        <v>23</v>
+        <v>344</v>
+      </c>
+      <c r="B705" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C705" s="6">
+        <v>12</v>
       </c>
       <c r="D705" t="s">
-        <v>118</v>
-      </c>
-      <c r="E705" t="s">
-        <v>123</v>
+        <v>336</v>
       </c>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>249</v>
-      </c>
-      <c r="B706" t="s">
-        <v>346</v>
-      </c>
-      <c r="C706">
+        <v>344</v>
+      </c>
+      <c r="B706" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C706" s="6">
         <v>12</v>
       </c>
       <c r="D706" t="s">
-        <v>109</v>
-      </c>
-      <c r="E706" t="s">
-        <v>110</v>
+        <v>336</v>
       </c>
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" t="s">
+        <v>345</v>
+      </c>
+      <c r="C707">
+        <v>23</v>
+      </c>
+      <c r="D707" t="s">
+        <v>118</v>
+      </c>
+      <c r="E707" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="708" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>249</v>
+      </c>
+      <c r="B708" t="s">
+        <v>346</v>
+      </c>
+      <c r="C708">
+        <v>12</v>
+      </c>
+      <c r="D708" t="s">
+        <v>109</v>
+      </c>
+      <c r="E708" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="709" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
         <v>79</v>
       </c>
-      <c r="B707" t="s">
+      <c r="B709" t="s">
         <v>347</v>
       </c>
-      <c r="C707">
+      <c r="C709">
         <v>126.38</v>
       </c>
-      <c r="D707" t="s">
+      <c r="D709" t="s">
         <v>79</v>
       </c>
-      <c r="E707" t="s">
+      <c r="E709" t="s">
         <v>348</v>
-      </c>
-    </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A710" t="s">
-        <v>350</v>
-      </c>
-      <c r="B710" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C710" s="6">
-        <v>17.489999999999998</v>
-      </c>
-      <c r="D710" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A711" t="s">
-        <v>350</v>
-      </c>
-      <c r="B711" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C711" s="6">
-        <v>199.99</v>
-      </c>
-      <c r="D711" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.25">
@@ -11128,16 +11145,13 @@
         <v>350</v>
       </c>
       <c r="B712" s="3" t="s">
-        <v>351</v>
+        <v>42</v>
       </c>
       <c r="C712" s="6">
-        <v>28.99</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="D712" t="s">
-        <v>118</v>
-      </c>
-      <c r="E712" s="3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.25">
@@ -11145,12 +11159,43 @@
         <v>350</v>
       </c>
       <c r="B713" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C713" s="6">
+        <v>199.99</v>
+      </c>
+      <c r="D713" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>350</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C714" s="6">
+        <v>28.99</v>
+      </c>
+      <c r="D714" t="s">
+        <v>118</v>
+      </c>
+      <c r="E714" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>350</v>
+      </c>
+      <c r="B715" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C713" s="6">
+      <c r="C715" s="6">
         <v>359.99</v>
       </c>
-      <c r="D713" t="s">
+      <c r="D715" t="s">
         <v>55</v>
       </c>
     </row>
